--- a/data/planilha_vendas.xlsx
+++ b/data/planilha_vendas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pedro\repos\indofil_sales\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6549408-ACF9-49E3-A557-1D9A2F6B1153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6088705-4009-4A15-AE87-9509DA1BEF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Planilha1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vendas!$B$1:$P$305</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Vendas!$B$1:$P$300</definedName>
     <definedName name="lista_produtos">Vendas!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1513" uniqueCount="122">
   <si>
     <t>Emissor</t>
   </si>
@@ -470,7 +470,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -492,12 +492,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -601,7 +595,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -655,32 +649,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -997,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:ALZ329"/>
+  <dimension ref="A1:ALZ324"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="28" customWidth="1"/>
@@ -1106,11 +1082,11 @@
         <f t="shared" ref="N2:N28" si="1">M2*H2</f>
         <v>206.4</v>
       </c>
-      <c r="O2" s="48">
+      <c r="O2" s="39">
         <f t="shared" ref="O2:O28" si="2">0.2*N2</f>
         <v>41.28</v>
       </c>
-      <c r="P2" s="48">
+      <c r="P2" s="39">
         <f t="shared" ref="P2:P28" si="3">0.8*N2</f>
         <v>165.12</v>
       </c>
@@ -1156,11 +1132,11 @@
         <f t="shared" si="1"/>
         <v>121.5</v>
       </c>
-      <c r="O3" s="48">
+      <c r="O3" s="39">
         <f t="shared" si="2"/>
         <v>24.3</v>
       </c>
-      <c r="P3" s="48">
+      <c r="P3" s="39">
         <f t="shared" si="3"/>
         <v>97.2</v>
       </c>
@@ -1206,11 +1182,11 @@
         <f t="shared" si="1"/>
         <v>295.2</v>
       </c>
-      <c r="O4" s="48">
+      <c r="O4" s="39">
         <f t="shared" si="2"/>
         <v>59.04</v>
       </c>
-      <c r="P4" s="48">
+      <c r="P4" s="39">
         <f t="shared" si="3"/>
         <v>236.16</v>
       </c>
@@ -1256,11 +1232,11 @@
         <f t="shared" si="1"/>
         <v>825.6</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="39">
         <f t="shared" si="2"/>
         <v>165.12</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="39">
         <f t="shared" si="3"/>
         <v>660.48</v>
       </c>
@@ -1306,11 +1282,11 @@
         <f t="shared" si="1"/>
         <v>372.59999999999997</v>
       </c>
-      <c r="O6" s="48">
+      <c r="O6" s="39">
         <f t="shared" si="2"/>
         <v>74.52</v>
       </c>
-      <c r="P6" s="48">
+      <c r="P6" s="39">
         <f t="shared" si="3"/>
         <v>298.08</v>
       </c>
@@ -1356,11 +1332,11 @@
         <f t="shared" si="1"/>
         <v>1792.8</v>
       </c>
-      <c r="O7" s="48">
+      <c r="O7" s="39">
         <f t="shared" si="2"/>
         <v>358.56</v>
       </c>
-      <c r="P7" s="48">
+      <c r="P7" s="39">
         <f t="shared" si="3"/>
         <v>1434.24</v>
       </c>
@@ -1408,11 +1384,11 @@
         <f t="shared" si="1"/>
         <v>302.40000000000003</v>
       </c>
-      <c r="O8" s="48">
+      <c r="O8" s="39">
         <f t="shared" si="2"/>
         <v>60.480000000000011</v>
       </c>
-      <c r="P8" s="48">
+      <c r="P8" s="39">
         <f t="shared" si="3"/>
         <v>241.92000000000004</v>
       </c>
@@ -1460,11 +1436,11 @@
         <f t="shared" si="1"/>
         <v>921.59999999999991</v>
       </c>
-      <c r="O9" s="48">
+      <c r="O9" s="39">
         <f t="shared" si="2"/>
         <v>184.32</v>
       </c>
-      <c r="P9" s="48">
+      <c r="P9" s="39">
         <f t="shared" si="3"/>
         <v>737.28</v>
       </c>
@@ -1510,11 +1486,11 @@
         <f t="shared" si="1"/>
         <v>985.6</v>
       </c>
-      <c r="O10" s="48">
+      <c r="O10" s="39">
         <f t="shared" si="2"/>
         <v>197.12</v>
       </c>
-      <c r="P10" s="48">
+      <c r="P10" s="39">
         <f t="shared" si="3"/>
         <v>788.48</v>
       </c>
@@ -1560,11 +1536,11 @@
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
-      <c r="O11" s="48">
+      <c r="O11" s="39">
         <f t="shared" si="2"/>
         <v>224</v>
       </c>
-      <c r="P11" s="48">
+      <c r="P11" s="39">
         <f t="shared" si="3"/>
         <v>896</v>
       </c>
@@ -1610,11 +1586,11 @@
         <f t="shared" si="1"/>
         <v>368.64</v>
       </c>
-      <c r="O12" s="48">
+      <c r="O12" s="39">
         <f t="shared" si="2"/>
         <v>73.727999999999994</v>
       </c>
-      <c r="P12" s="48">
+      <c r="P12" s="39">
         <f t="shared" si="3"/>
         <v>294.91199999999998</v>
       </c>
@@ -1660,11 +1636,11 @@
         <f t="shared" si="1"/>
         <v>2332.8000000000002</v>
       </c>
-      <c r="O13" s="48">
+      <c r="O13" s="39">
         <f t="shared" si="2"/>
         <v>466.56000000000006</v>
       </c>
-      <c r="P13" s="48">
+      <c r="P13" s="39">
         <f t="shared" si="3"/>
         <v>1866.2400000000002</v>
       </c>
@@ -1710,11 +1686,11 @@
         <f t="shared" si="1"/>
         <v>3328</v>
       </c>
-      <c r="O14" s="48">
+      <c r="O14" s="39">
         <f t="shared" si="2"/>
         <v>665.6</v>
       </c>
-      <c r="P14" s="48">
+      <c r="P14" s="39">
         <f t="shared" si="3"/>
         <v>2662.4</v>
       </c>
@@ -1762,11 +1738,11 @@
         <f t="shared" si="1"/>
         <v>295.2</v>
       </c>
-      <c r="O15" s="48">
+      <c r="O15" s="39">
         <f t="shared" si="2"/>
         <v>59.04</v>
       </c>
-      <c r="P15" s="48">
+      <c r="P15" s="39">
         <f t="shared" si="3"/>
         <v>236.16</v>
       </c>
@@ -1814,11 +1790,11 @@
         <f t="shared" si="1"/>
         <v>295.2</v>
       </c>
-      <c r="O16" s="48">
+      <c r="O16" s="39">
         <f t="shared" si="2"/>
         <v>59.04</v>
       </c>
-      <c r="P16" s="48">
+      <c r="P16" s="39">
         <f t="shared" si="3"/>
         <v>236.16</v>
       </c>
@@ -1860,11 +1836,11 @@
         <f t="shared" si="1"/>
         <v>1286.25</v>
       </c>
-      <c r="O17" s="48">
+      <c r="O17" s="39">
         <f t="shared" si="2"/>
         <v>257.25</v>
       </c>
-      <c r="P17" s="48">
+      <c r="P17" s="39">
         <f t="shared" si="3"/>
         <v>1029</v>
       </c>
@@ -1910,11 +1886,11 @@
         <f t="shared" si="1"/>
         <v>497.7</v>
       </c>
-      <c r="O18" s="48">
+      <c r="O18" s="39">
         <f t="shared" si="2"/>
         <v>99.54</v>
       </c>
-      <c r="P18" s="48">
+      <c r="P18" s="39">
         <f t="shared" si="3"/>
         <v>398.16</v>
       </c>
@@ -1960,11 +1936,11 @@
         <f t="shared" si="1"/>
         <v>844.19999999999993</v>
       </c>
-      <c r="O19" s="48">
+      <c r="O19" s="39">
         <f t="shared" si="2"/>
         <v>168.84</v>
       </c>
-      <c r="P19" s="48">
+      <c r="P19" s="39">
         <f t="shared" si="3"/>
         <v>675.36</v>
       </c>
@@ -2512,11 +2488,11 @@
         <f t="shared" si="1"/>
         <v>441</v>
       </c>
-      <c r="O20" s="48">
+      <c r="O20" s="39">
         <f t="shared" si="2"/>
         <v>88.2</v>
       </c>
-      <c r="P20" s="48">
+      <c r="P20" s="39">
         <f t="shared" si="3"/>
         <v>352.8</v>
       </c>
@@ -2564,11 +2540,11 @@
         <f t="shared" si="1"/>
         <v>518.4</v>
       </c>
-      <c r="O21" s="48">
+      <c r="O21" s="39">
         <f t="shared" si="2"/>
         <v>103.68</v>
       </c>
-      <c r="P21" s="48">
+      <c r="P21" s="39">
         <f t="shared" si="3"/>
         <v>414.72</v>
       </c>
@@ -2616,11 +2592,11 @@
         <f t="shared" si="1"/>
         <v>2144</v>
       </c>
-      <c r="O22" s="48">
+      <c r="O22" s="39">
         <f t="shared" si="2"/>
         <v>428.8</v>
       </c>
-      <c r="P22" s="48">
+      <c r="P22" s="39">
         <f t="shared" si="3"/>
         <v>1715.2</v>
       </c>
@@ -2668,11 +2644,11 @@
         <f t="shared" si="1"/>
         <v>460.8</v>
       </c>
-      <c r="O23" s="48">
+      <c r="O23" s="39">
         <f t="shared" si="2"/>
         <v>92.160000000000011</v>
       </c>
-      <c r="P23" s="48">
+      <c r="P23" s="39">
         <f t="shared" si="3"/>
         <v>368.64000000000004</v>
       </c>
@@ -2720,11 +2696,11 @@
         <f t="shared" si="1"/>
         <v>870.4</v>
       </c>
-      <c r="O24" s="48">
+      <c r="O24" s="39">
         <f t="shared" si="2"/>
         <v>174.08</v>
       </c>
-      <c r="P24" s="48">
+      <c r="P24" s="39">
         <f t="shared" si="3"/>
         <v>696.32</v>
       </c>
@@ -2772,11 +2748,11 @@
         <f t="shared" si="1"/>
         <v>756</v>
       </c>
-      <c r="O25" s="48">
+      <c r="O25" s="39">
         <f t="shared" si="2"/>
         <v>151.20000000000002</v>
       </c>
-      <c r="P25" s="48">
+      <c r="P25" s="39">
         <f t="shared" si="3"/>
         <v>604.80000000000007</v>
       </c>
@@ -2824,11 +2800,11 @@
         <f t="shared" si="1"/>
         <v>475.02</v>
       </c>
-      <c r="O26" s="48">
+      <c r="O26" s="39">
         <f t="shared" si="2"/>
         <v>95.004000000000005</v>
       </c>
-      <c r="P26" s="48">
+      <c r="P26" s="39">
         <f t="shared" si="3"/>
         <v>380.01600000000002</v>
       </c>
@@ -2876,11 +2852,11 @@
         <f t="shared" si="1"/>
         <v>241.20000000000002</v>
       </c>
-      <c r="O27" s="48">
+      <c r="O27" s="39">
         <f t="shared" si="2"/>
         <v>48.240000000000009</v>
       </c>
-      <c r="P27" s="48">
+      <c r="P27" s="39">
         <f t="shared" si="3"/>
         <v>192.96000000000004</v>
       </c>
@@ -2928,11 +2904,11 @@
         <f t="shared" si="1"/>
         <v>428.8</v>
       </c>
-      <c r="O28" s="48">
+      <c r="O28" s="39">
         <f t="shared" si="2"/>
         <v>85.76</v>
       </c>
-      <c r="P28" s="48">
+      <c r="P28" s="39">
         <f t="shared" si="3"/>
         <v>343.04</v>
       </c>
@@ -2980,11 +2956,11 @@
         <f t="shared" ref="N29:N60" si="5">M29*H29</f>
         <v>3328</v>
       </c>
-      <c r="O29" s="48">
+      <c r="O29" s="39">
         <f t="shared" ref="O29:O60" si="6">0.2*N29</f>
         <v>665.6</v>
       </c>
-      <c r="P29" s="48">
+      <c r="P29" s="39">
         <f t="shared" ref="P29:P60" si="7">0.8*N29</f>
         <v>2662.4</v>
       </c>
@@ -3032,11 +3008,11 @@
         <f t="shared" si="5"/>
         <v>840</v>
       </c>
-      <c r="O30" s="48">
+      <c r="O30" s="39">
         <f t="shared" si="6"/>
         <v>168</v>
       </c>
-      <c r="P30" s="48">
+      <c r="P30" s="39">
         <f t="shared" si="7"/>
         <v>672</v>
       </c>
@@ -3084,11 +3060,11 @@
         <f t="shared" si="5"/>
         <v>1248</v>
       </c>
-      <c r="O31" s="48">
+      <c r="O31" s="39">
         <f t="shared" si="6"/>
         <v>249.60000000000002</v>
       </c>
-      <c r="P31" s="48">
+      <c r="P31" s="39">
         <f t="shared" si="7"/>
         <v>998.40000000000009</v>
       </c>
@@ -3136,11 +3112,11 @@
         <f t="shared" si="5"/>
         <v>1170</v>
       </c>
-      <c r="O32" s="48">
+      <c r="O32" s="39">
         <f t="shared" si="6"/>
         <v>234</v>
       </c>
-      <c r="P32" s="48">
+      <c r="P32" s="39">
         <f t="shared" si="7"/>
         <v>936</v>
       </c>
@@ -3188,11 +3164,11 @@
         <f t="shared" si="5"/>
         <v>504</v>
       </c>
-      <c r="O33" s="48">
+      <c r="O33" s="39">
         <f t="shared" si="6"/>
         <v>100.80000000000001</v>
       </c>
-      <c r="P33" s="48">
+      <c r="P33" s="39">
         <f t="shared" si="7"/>
         <v>403.20000000000005</v>
       </c>
@@ -3240,11 +3216,11 @@
         <f t="shared" si="5"/>
         <v>1638.4</v>
       </c>
-      <c r="O34" s="48">
+      <c r="O34" s="39">
         <f t="shared" si="6"/>
         <v>327.68000000000006</v>
       </c>
-      <c r="P34" s="48">
+      <c r="P34" s="39">
         <f t="shared" si="7"/>
         <v>1310.7200000000003</v>
       </c>
@@ -3292,11 +3268,11 @@
         <f t="shared" si="5"/>
         <v>819.2</v>
       </c>
-      <c r="O35" s="48">
+      <c r="O35" s="39">
         <f t="shared" si="6"/>
         <v>163.84000000000003</v>
       </c>
-      <c r="P35" s="48">
+      <c r="P35" s="39">
         <f t="shared" si="7"/>
         <v>655.36000000000013</v>
       </c>
@@ -3344,11 +3320,11 @@
         <f t="shared" si="5"/>
         <v>468</v>
       </c>
-      <c r="O36" s="48">
+      <c r="O36" s="39">
         <f t="shared" si="6"/>
         <v>93.600000000000009</v>
       </c>
-      <c r="P36" s="48">
+      <c r="P36" s="39">
         <f t="shared" si="7"/>
         <v>374.40000000000003</v>
       </c>
@@ -3396,11 +3372,11 @@
         <f t="shared" si="5"/>
         <v>661.5</v>
       </c>
-      <c r="O37" s="48">
+      <c r="O37" s="39">
         <f t="shared" si="6"/>
         <v>132.30000000000001</v>
       </c>
-      <c r="P37" s="48">
+      <c r="P37" s="39">
         <f t="shared" si="7"/>
         <v>529.20000000000005</v>
       </c>
@@ -3448,11 +3424,11 @@
         <f t="shared" si="5"/>
         <v>1050</v>
       </c>
-      <c r="O38" s="48">
+      <c r="O38" s="39">
         <f t="shared" si="6"/>
         <v>210</v>
       </c>
-      <c r="P38" s="48">
+      <c r="P38" s="39">
         <f t="shared" si="7"/>
         <v>840</v>
       </c>
@@ -3500,11 +3476,11 @@
         <f t="shared" si="5"/>
         <v>210</v>
       </c>
-      <c r="O39" s="48">
+      <c r="O39" s="39">
         <f t="shared" si="6"/>
         <v>42</v>
       </c>
-      <c r="P39" s="48">
+      <c r="P39" s="39">
         <f t="shared" si="7"/>
         <v>168</v>
       </c>
@@ -3552,11 +3528,11 @@
         <f t="shared" si="5"/>
         <v>435.2</v>
       </c>
-      <c r="O40" s="48">
+      <c r="O40" s="39">
         <f t="shared" si="6"/>
         <v>87.04</v>
       </c>
-      <c r="P40" s="48">
+      <c r="P40" s="39">
         <f t="shared" si="7"/>
         <v>348.16</v>
       </c>
@@ -3604,11 +3580,11 @@
         <f t="shared" si="5"/>
         <v>1795.5</v>
       </c>
-      <c r="O41" s="48">
+      <c r="O41" s="39">
         <f t="shared" si="6"/>
         <v>359.1</v>
       </c>
-      <c r="P41" s="48">
+      <c r="P41" s="39">
         <f t="shared" si="7"/>
         <v>1436.4</v>
       </c>
@@ -3656,11 +3632,11 @@
         <f t="shared" si="5"/>
         <v>666.5625</v>
       </c>
-      <c r="O42" s="48">
+      <c r="O42" s="39">
         <f t="shared" si="6"/>
         <v>133.3125</v>
       </c>
-      <c r="P42" s="48">
+      <c r="P42" s="39">
         <f t="shared" si="7"/>
         <v>533.25</v>
       </c>
@@ -3708,11 +3684,11 @@
         <f t="shared" si="5"/>
         <v>598.5</v>
       </c>
-      <c r="O43" s="48">
+      <c r="O43" s="39">
         <f t="shared" si="6"/>
         <v>119.7</v>
       </c>
-      <c r="P43" s="48">
+      <c r="P43" s="39">
         <f t="shared" si="7"/>
         <v>478.8</v>
       </c>
@@ -3760,11 +3736,11 @@
         <f t="shared" si="5"/>
         <v>997.5</v>
       </c>
-      <c r="O44" s="48">
+      <c r="O44" s="39">
         <f t="shared" si="6"/>
         <v>199.5</v>
       </c>
-      <c r="P44" s="48">
+      <c r="P44" s="39">
         <f t="shared" si="7"/>
         <v>798</v>
       </c>
@@ -3812,11 +3788,11 @@
         <f t="shared" si="5"/>
         <v>598.5</v>
       </c>
-      <c r="O45" s="48">
+      <c r="O45" s="39">
         <f t="shared" si="6"/>
         <v>119.7</v>
       </c>
-      <c r="P45" s="48">
+      <c r="P45" s="39">
         <f t="shared" si="7"/>
         <v>478.8</v>
       </c>
@@ -3864,11 +3840,11 @@
         <f t="shared" si="5"/>
         <v>2992.5</v>
       </c>
-      <c r="O46" s="48">
+      <c r="O46" s="39">
         <f t="shared" si="6"/>
         <v>598.5</v>
       </c>
-      <c r="P46" s="48">
+      <c r="P46" s="39">
         <f t="shared" si="7"/>
         <v>2394</v>
       </c>
@@ -3916,11 +3892,11 @@
         <f t="shared" si="5"/>
         <v>997.5</v>
       </c>
-      <c r="O47" s="48">
+      <c r="O47" s="39">
         <f t="shared" si="6"/>
         <v>199.5</v>
       </c>
-      <c r="P47" s="48">
+      <c r="P47" s="39">
         <f t="shared" si="7"/>
         <v>798</v>
       </c>
@@ -3968,11 +3944,11 @@
         <f t="shared" si="5"/>
         <v>997.5</v>
       </c>
-      <c r="O48" s="48">
+      <c r="O48" s="39">
         <f t="shared" si="6"/>
         <v>199.5</v>
       </c>
-      <c r="P48" s="48">
+      <c r="P48" s="39">
         <f t="shared" si="7"/>
         <v>798</v>
       </c>
@@ -4020,11 +3996,11 @@
         <f t="shared" si="5"/>
         <v>1512</v>
       </c>
-      <c r="O49" s="48">
+      <c r="O49" s="39">
         <f t="shared" si="6"/>
         <v>302.40000000000003</v>
       </c>
-      <c r="P49" s="48">
+      <c r="P49" s="39">
         <f t="shared" si="7"/>
         <v>1209.6000000000001</v>
       </c>
@@ -4072,11 +4048,11 @@
         <f t="shared" si="5"/>
         <v>1197</v>
       </c>
-      <c r="O50" s="48">
+      <c r="O50" s="39">
         <f t="shared" si="6"/>
         <v>239.4</v>
       </c>
-      <c r="P50" s="48">
+      <c r="P50" s="39">
         <f t="shared" si="7"/>
         <v>957.6</v>
       </c>
@@ -4124,11 +4100,11 @@
         <f t="shared" si="5"/>
         <v>997.5</v>
       </c>
-      <c r="O51" s="48">
+      <c r="O51" s="39">
         <f t="shared" si="6"/>
         <v>199.5</v>
       </c>
-      <c r="P51" s="48">
+      <c r="P51" s="39">
         <f t="shared" si="7"/>
         <v>798</v>
       </c>
@@ -4176,11 +4152,11 @@
         <f t="shared" si="5"/>
         <v>1323</v>
       </c>
-      <c r="O52" s="48">
+      <c r="O52" s="39">
         <f t="shared" si="6"/>
         <v>264.60000000000002</v>
       </c>
-      <c r="P52" s="48">
+      <c r="P52" s="39">
         <f t="shared" si="7"/>
         <v>1058.4000000000001</v>
       </c>
@@ -4228,11 +4204,11 @@
         <f t="shared" si="5"/>
         <v>6553.6</v>
       </c>
-      <c r="O53" s="48">
+      <c r="O53" s="39">
         <f t="shared" si="6"/>
         <v>1310.7200000000003</v>
       </c>
-      <c r="P53" s="48">
+      <c r="P53" s="39">
         <f t="shared" si="7"/>
         <v>5242.880000000001</v>
       </c>
@@ -4280,11 +4256,11 @@
         <f t="shared" si="5"/>
         <v>2956.8</v>
       </c>
-      <c r="O54" s="48">
+      <c r="O54" s="39">
         <f t="shared" si="6"/>
         <v>591.36</v>
       </c>
-      <c r="P54" s="48">
+      <c r="P54" s="39">
         <f t="shared" si="7"/>
         <v>2365.44</v>
       </c>
@@ -4332,11 +4308,11 @@
         <f t="shared" si="5"/>
         <v>598.5</v>
       </c>
-      <c r="O55" s="48">
+      <c r="O55" s="39">
         <f t="shared" si="6"/>
         <v>119.7</v>
       </c>
-      <c r="P55" s="48">
+      <c r="P55" s="39">
         <f t="shared" si="7"/>
         <v>478.8</v>
       </c>
@@ -4384,11 +4360,11 @@
         <f t="shared" si="5"/>
         <v>567</v>
       </c>
-      <c r="O56" s="48">
+      <c r="O56" s="39">
         <f t="shared" si="6"/>
         <v>113.4</v>
       </c>
-      <c r="P56" s="48">
+      <c r="P56" s="39">
         <f t="shared" si="7"/>
         <v>453.6</v>
       </c>
@@ -4436,11 +4412,11 @@
         <f t="shared" si="5"/>
         <v>378</v>
       </c>
-      <c r="O57" s="48">
+      <c r="O57" s="39">
         <f t="shared" si="6"/>
         <v>75.600000000000009</v>
       </c>
-      <c r="P57" s="48">
+      <c r="P57" s="39">
         <f t="shared" si="7"/>
         <v>302.40000000000003</v>
       </c>
@@ -4488,11 +4464,11 @@
         <f t="shared" si="5"/>
         <v>598.5</v>
       </c>
-      <c r="O58" s="48">
+      <c r="O58" s="39">
         <f t="shared" si="6"/>
         <v>119.7</v>
       </c>
-      <c r="P58" s="48">
+      <c r="P58" s="39">
         <f t="shared" si="7"/>
         <v>478.8</v>
       </c>
@@ -4540,11 +4516,11 @@
         <f t="shared" si="5"/>
         <v>411.6</v>
       </c>
-      <c r="O59" s="48">
+      <c r="O59" s="39">
         <f t="shared" si="6"/>
         <v>82.320000000000007</v>
       </c>
-      <c r="P59" s="48">
+      <c r="P59" s="39">
         <f t="shared" si="7"/>
         <v>329.28000000000003</v>
       </c>
@@ -4592,11 +4568,11 @@
         <f t="shared" si="5"/>
         <v>3379.2000000000003</v>
       </c>
-      <c r="O60" s="48">
+      <c r="O60" s="39">
         <f t="shared" si="6"/>
         <v>675.84000000000015</v>
       </c>
-      <c r="P60" s="48">
+      <c r="P60" s="39">
         <f t="shared" si="7"/>
         <v>2703.3600000000006</v>
       </c>
@@ -4644,11 +4620,11 @@
         <f t="shared" ref="N61:N92" si="9">M61*H61</f>
         <v>399</v>
       </c>
-      <c r="O61" s="48">
+      <c r="O61" s="39">
         <f t="shared" ref="O61:O92" si="10">0.2*N61</f>
         <v>79.800000000000011</v>
       </c>
-      <c r="P61" s="48">
+      <c r="P61" s="39">
         <f t="shared" ref="P61:P92" si="11">0.8*N61</f>
         <v>319.20000000000005</v>
       </c>
@@ -4696,11 +4672,11 @@
         <f t="shared" si="9"/>
         <v>399</v>
       </c>
-      <c r="O62" s="48">
+      <c r="O62" s="39">
         <f t="shared" si="10"/>
         <v>79.800000000000011</v>
       </c>
-      <c r="P62" s="48">
+      <c r="P62" s="39">
         <f t="shared" si="11"/>
         <v>319.20000000000005</v>
       </c>
@@ -4748,11 +4724,11 @@
         <f t="shared" si="9"/>
         <v>1363.2</v>
       </c>
-      <c r="O63" s="48">
+      <c r="O63" s="39">
         <f t="shared" si="10"/>
         <v>272.64000000000004</v>
       </c>
-      <c r="P63" s="48">
+      <c r="P63" s="39">
         <f t="shared" si="11"/>
         <v>1090.5600000000002</v>
       </c>
@@ -4800,11 +4776,11 @@
         <f t="shared" si="9"/>
         <v>908.80000000000007</v>
       </c>
-      <c r="O64" s="48">
+      <c r="O64" s="39">
         <f t="shared" si="10"/>
         <v>181.76000000000002</v>
       </c>
-      <c r="P64" s="48">
+      <c r="P64" s="39">
         <f t="shared" si="11"/>
         <v>727.04000000000008</v>
       </c>
@@ -4852,11 +4828,11 @@
         <f t="shared" si="9"/>
         <v>908.80000000000007</v>
       </c>
-      <c r="O65" s="48">
+      <c r="O65" s="39">
         <f t="shared" si="10"/>
         <v>181.76000000000002</v>
       </c>
-      <c r="P65" s="48">
+      <c r="P65" s="39">
         <f t="shared" si="11"/>
         <v>727.04000000000008</v>
       </c>
@@ -4904,11 +4880,11 @@
         <f t="shared" si="9"/>
         <v>1363.2</v>
       </c>
-      <c r="O66" s="48">
+      <c r="O66" s="39">
         <f t="shared" si="10"/>
         <v>272.64000000000004</v>
       </c>
-      <c r="P66" s="48">
+      <c r="P66" s="39">
         <f t="shared" si="11"/>
         <v>1090.5600000000002</v>
       </c>
@@ -4956,11 +4932,11 @@
         <f t="shared" si="9"/>
         <v>908.80000000000007</v>
       </c>
-      <c r="O67" s="48">
+      <c r="O67" s="39">
         <f t="shared" si="10"/>
         <v>181.76000000000002</v>
       </c>
-      <c r="P67" s="48">
+      <c r="P67" s="39">
         <f t="shared" si="11"/>
         <v>727.04000000000008</v>
       </c>
@@ -5008,11 +4984,11 @@
         <f t="shared" si="9"/>
         <v>598.5</v>
       </c>
-      <c r="O68" s="48">
+      <c r="O68" s="39">
         <f t="shared" si="10"/>
         <v>119.7</v>
       </c>
-      <c r="P68" s="48">
+      <c r="P68" s="39">
         <f t="shared" si="11"/>
         <v>478.8</v>
       </c>
@@ -5060,11 +5036,11 @@
         <f t="shared" si="9"/>
         <v>908.80000000000007</v>
       </c>
-      <c r="O69" s="48">
+      <c r="O69" s="39">
         <f t="shared" si="10"/>
         <v>181.76000000000002</v>
       </c>
-      <c r="P69" s="48">
+      <c r="P69" s="39">
         <f t="shared" si="11"/>
         <v>727.04000000000008</v>
       </c>
@@ -5112,11 +5088,11 @@
         <f t="shared" si="9"/>
         <v>3168</v>
       </c>
-      <c r="O70" s="48">
+      <c r="O70" s="39">
         <f t="shared" si="10"/>
         <v>633.6</v>
       </c>
-      <c r="P70" s="48">
+      <c r="P70" s="39">
         <f t="shared" si="11"/>
         <v>2534.4</v>
       </c>
@@ -5164,11 +5140,11 @@
         <f t="shared" si="9"/>
         <v>422.40000000000003</v>
       </c>
-      <c r="O71" s="48">
+      <c r="O71" s="39">
         <f t="shared" si="10"/>
         <v>84.480000000000018</v>
       </c>
-      <c r="P71" s="48">
+      <c r="P71" s="39">
         <f t="shared" si="11"/>
         <v>337.92000000000007</v>
       </c>
@@ -5214,11 +5190,11 @@
         <f t="shared" si="9"/>
         <v>438.89999999999992</v>
       </c>
-      <c r="O72" s="48">
+      <c r="O72" s="39">
         <f t="shared" si="10"/>
         <v>87.779999999999987</v>
       </c>
-      <c r="P72" s="48">
+      <c r="P72" s="39">
         <f t="shared" si="11"/>
         <v>351.11999999999995</v>
       </c>
@@ -5314,11 +5290,11 @@
         <f t="shared" si="9"/>
         <v>2086.4</v>
       </c>
-      <c r="O74" s="48">
+      <c r="O74" s="39">
         <f t="shared" si="10"/>
         <v>417.28000000000003</v>
       </c>
-      <c r="P74" s="48">
+      <c r="P74" s="39">
         <f t="shared" si="11"/>
         <v>1669.1200000000001</v>
       </c>
@@ -5364,11 +5340,11 @@
         <f t="shared" si="9"/>
         <v>931.84</v>
       </c>
-      <c r="O75" s="48">
+      <c r="O75" s="39">
         <f t="shared" si="10"/>
         <v>186.36800000000002</v>
       </c>
-      <c r="P75" s="48">
+      <c r="P75" s="39">
         <f t="shared" si="11"/>
         <v>745.47200000000009</v>
       </c>
@@ -5414,11 +5390,11 @@
         <f t="shared" si="9"/>
         <v>558.71999999999991</v>
       </c>
-      <c r="O76" s="48">
+      <c r="O76" s="39">
         <f t="shared" si="10"/>
         <v>111.74399999999999</v>
       </c>
-      <c r="P76" s="48">
+      <c r="P76" s="39">
         <f t="shared" si="11"/>
         <v>446.97599999999994</v>
       </c>
@@ -5464,11 +5440,11 @@
         <f t="shared" si="9"/>
         <v>1432.8</v>
       </c>
-      <c r="O77" s="48">
+      <c r="O77" s="39">
         <f t="shared" si="10"/>
         <v>286.56</v>
       </c>
-      <c r="P77" s="48">
+      <c r="P77" s="39">
         <f t="shared" si="11"/>
         <v>1146.24</v>
       </c>
@@ -5514,11 +5490,11 @@
         <f t="shared" si="9"/>
         <v>465.92</v>
       </c>
-      <c r="O78" s="48">
+      <c r="O78" s="39">
         <f t="shared" si="10"/>
         <v>93.184000000000012</v>
       </c>
-      <c r="P78" s="48">
+      <c r="P78" s="39">
         <f t="shared" si="11"/>
         <v>372.73600000000005</v>
       </c>
@@ -5564,11 +5540,11 @@
         <f t="shared" si="9"/>
         <v>457.2</v>
       </c>
-      <c r="O79" s="48">
+      <c r="O79" s="39">
         <f t="shared" si="10"/>
         <v>91.44</v>
       </c>
-      <c r="P79" s="48">
+      <c r="P79" s="39">
         <f t="shared" si="11"/>
         <v>365.76</v>
       </c>
@@ -5614,11 +5590,11 @@
         <f t="shared" si="9"/>
         <v>1228.8</v>
       </c>
-      <c r="O80" s="48">
+      <c r="O80" s="39">
         <f t="shared" si="10"/>
         <v>245.76</v>
       </c>
-      <c r="P80" s="48">
+      <c r="P80" s="39">
         <f t="shared" si="11"/>
         <v>983.04</v>
       </c>
@@ -5662,11 +5638,11 @@
         <f t="shared" si="9"/>
         <v>4536</v>
       </c>
-      <c r="O81" s="48">
+      <c r="O81" s="39">
         <f t="shared" si="10"/>
         <v>907.2</v>
       </c>
-      <c r="P81" s="48">
+      <c r="P81" s="39">
         <f t="shared" si="11"/>
         <v>3628.8</v>
       </c>
@@ -5710,11 +5686,11 @@
         <f t="shared" si="9"/>
         <v>8576</v>
       </c>
-      <c r="O82" s="48">
+      <c r="O82" s="39">
         <f t="shared" si="10"/>
         <v>1715.2</v>
       </c>
-      <c r="P82" s="48">
+      <c r="P82" s="39">
         <f t="shared" si="11"/>
         <v>6860.8</v>
       </c>
@@ -5758,11 +5734,11 @@
         <f t="shared" si="9"/>
         <v>12480</v>
       </c>
-      <c r="O83" s="48">
+      <c r="O83" s="39">
         <f t="shared" si="10"/>
         <v>2496</v>
       </c>
-      <c r="P83" s="48">
+      <c r="P83" s="39">
         <f t="shared" si="11"/>
         <v>9984</v>
       </c>
@@ -5808,11 +5784,11 @@
         <f t="shared" si="9"/>
         <v>799.2</v>
       </c>
-      <c r="O84" s="48">
+      <c r="O84" s="39">
         <f t="shared" si="10"/>
         <v>159.84000000000003</v>
       </c>
-      <c r="P84" s="48">
+      <c r="P84" s="39">
         <f t="shared" si="11"/>
         <v>639.36000000000013</v>
       </c>
@@ -5858,11 +5834,11 @@
         <f t="shared" si="9"/>
         <v>865.28</v>
       </c>
-      <c r="O85" s="48">
+      <c r="O85" s="39">
         <f t="shared" si="10"/>
         <v>173.05600000000001</v>
       </c>
-      <c r="P85" s="48">
+      <c r="P85" s="39">
         <f t="shared" si="11"/>
         <v>692.22400000000005</v>
       </c>
@@ -5908,11 +5884,11 @@
         <f t="shared" si="9"/>
         <v>1975.05</v>
       </c>
-      <c r="O86" s="48">
+      <c r="O86" s="39">
         <f t="shared" si="10"/>
         <v>395.01</v>
       </c>
-      <c r="P86" s="48">
+      <c r="P86" s="39">
         <f t="shared" si="11"/>
         <v>1580.04</v>
       </c>
@@ -5958,11 +5934,11 @@
         <f t="shared" si="9"/>
         <v>658.35</v>
       </c>
-      <c r="O87" s="48">
+      <c r="O87" s="39">
         <f t="shared" si="10"/>
         <v>131.67000000000002</v>
       </c>
-      <c r="P87" s="48">
+      <c r="P87" s="39">
         <f t="shared" si="11"/>
         <v>526.68000000000006</v>
       </c>
@@ -6008,11 +5984,11 @@
         <f t="shared" si="9"/>
         <v>424.96000000000004</v>
       </c>
-      <c r="O88" s="48">
+      <c r="O88" s="39">
         <f t="shared" si="10"/>
         <v>84.992000000000019</v>
       </c>
-      <c r="P88" s="48">
+      <c r="P88" s="39">
         <f t="shared" si="11"/>
         <v>339.96800000000007</v>
       </c>
@@ -6058,11 +6034,11 @@
         <f t="shared" si="9"/>
         <v>777.6</v>
       </c>
-      <c r="O89" s="48">
+      <c r="O89" s="39">
         <f t="shared" si="10"/>
         <v>155.52000000000001</v>
       </c>
-      <c r="P89" s="48">
+      <c r="P89" s="39">
         <f t="shared" si="11"/>
         <v>622.08000000000004</v>
       </c>
@@ -6108,11 +6084,11 @@
         <f t="shared" si="9"/>
         <v>438.89999999999992</v>
       </c>
-      <c r="O90" s="48">
+      <c r="O90" s="39">
         <f t="shared" si="10"/>
         <v>87.779999999999987</v>
       </c>
-      <c r="P90" s="48">
+      <c r="P90" s="39">
         <f t="shared" si="11"/>
         <v>351.11999999999995</v>
       </c>
@@ -6158,11 +6134,11 @@
         <f t="shared" si="9"/>
         <v>1612.8</v>
       </c>
-      <c r="O91" s="48">
+      <c r="O91" s="39">
         <f t="shared" si="10"/>
         <v>322.56</v>
       </c>
-      <c r="P91" s="48">
+      <c r="P91" s="39">
         <f t="shared" si="11"/>
         <v>1290.24</v>
       </c>
@@ -6210,11 +6186,11 @@
         <f t="shared" si="9"/>
         <v>476.7</v>
       </c>
-      <c r="O92" s="48">
+      <c r="O92" s="39">
         <f t="shared" si="10"/>
         <v>95.34</v>
       </c>
-      <c r="P92" s="48">
+      <c r="P92" s="39">
         <f t="shared" si="11"/>
         <v>381.36</v>
       </c>
@@ -6262,11 +6238,11 @@
         <f t="shared" ref="N93:N124" si="13">M93*H93</f>
         <v>1248.3</v>
       </c>
-      <c r="O93" s="48">
+      <c r="O93" s="39">
         <f t="shared" ref="O93:O124" si="14">0.2*N93</f>
         <v>249.66</v>
       </c>
-      <c r="P93" s="48">
+      <c r="P93" s="39">
         <f t="shared" ref="P93:P124" si="15">0.8*N93</f>
         <v>998.64</v>
       </c>
@@ -6314,11 +6290,11 @@
         <f t="shared" si="13"/>
         <v>1265.4000000000001</v>
       </c>
-      <c r="O94" s="48">
+      <c r="O94" s="39">
         <f t="shared" si="14"/>
         <v>253.08000000000004</v>
       </c>
-      <c r="P94" s="48">
+      <c r="P94" s="39">
         <f t="shared" si="15"/>
         <v>1012.3200000000002</v>
       </c>
@@ -6364,11 +6340,11 @@
         <f t="shared" si="13"/>
         <v>518.69999999999993</v>
       </c>
-      <c r="O95" s="48">
+      <c r="O95" s="39">
         <f t="shared" si="14"/>
         <v>103.74</v>
       </c>
-      <c r="P95" s="48">
+      <c r="P95" s="39">
         <f t="shared" si="15"/>
         <v>414.96</v>
       </c>
@@ -6416,11 +6392,11 @@
         <f t="shared" si="13"/>
         <v>934.4</v>
       </c>
-      <c r="O96" s="48">
+      <c r="O96" s="39">
         <f t="shared" si="14"/>
         <v>186.88</v>
       </c>
-      <c r="P96" s="48">
+      <c r="P96" s="39">
         <f t="shared" si="15"/>
         <v>747.52</v>
       </c>
@@ -6470,11 +6446,11 @@
         <f t="shared" si="13"/>
         <v>454.40000000000003</v>
       </c>
-      <c r="O97" s="48">
+      <c r="O97" s="39">
         <f t="shared" si="14"/>
         <v>90.88000000000001</v>
       </c>
-      <c r="P97" s="48">
+      <c r="P97" s="39">
         <f t="shared" si="15"/>
         <v>363.52000000000004</v>
       </c>
@@ -6524,11 +6500,11 @@
         <f t="shared" si="13"/>
         <v>278.64000000000004</v>
       </c>
-      <c r="O98" s="48">
+      <c r="O98" s="39">
         <f t="shared" si="14"/>
         <v>55.728000000000009</v>
       </c>
-      <c r="P98" s="48">
+      <c r="P98" s="39">
         <f t="shared" si="15"/>
         <v>222.91200000000003</v>
       </c>
@@ -6578,11 +6554,11 @@
         <f t="shared" si="13"/>
         <v>600.07499999999993</v>
       </c>
-      <c r="O99" s="48">
+      <c r="O99" s="39">
         <f t="shared" si="14"/>
         <v>120.01499999999999</v>
       </c>
-      <c r="P99" s="48">
+      <c r="P99" s="39">
         <f t="shared" si="15"/>
         <v>480.05999999999995</v>
       </c>
@@ -6632,11 +6608,11 @@
         <f t="shared" si="13"/>
         <v>518.4</v>
       </c>
-      <c r="O100" s="48">
+      <c r="O100" s="39">
         <f t="shared" si="14"/>
         <v>103.68</v>
       </c>
-      <c r="P100" s="48">
+      <c r="P100" s="39">
         <f t="shared" si="15"/>
         <v>414.72</v>
       </c>
@@ -6686,11 +6662,11 @@
         <f t="shared" si="13"/>
         <v>441.6</v>
       </c>
-      <c r="O101" s="48">
+      <c r="O101" s="39">
         <f t="shared" si="14"/>
         <v>88.320000000000007</v>
       </c>
-      <c r="P101" s="48">
+      <c r="P101" s="39">
         <f t="shared" si="15"/>
         <v>353.28000000000003</v>
       </c>
@@ -6738,11 +6714,11 @@
         <f t="shared" si="13"/>
         <v>3534.2999999999997</v>
       </c>
-      <c r="O102" s="48">
+      <c r="O102" s="39">
         <f t="shared" si="14"/>
         <v>706.86</v>
       </c>
-      <c r="P102" s="48">
+      <c r="P102" s="39">
         <f t="shared" si="15"/>
         <v>2827.44</v>
       </c>
@@ -6792,11 +6768,11 @@
         <f t="shared" si="13"/>
         <v>858.48</v>
       </c>
-      <c r="O103" s="48">
+      <c r="O103" s="39">
         <f t="shared" si="14"/>
         <v>171.69600000000003</v>
       </c>
-      <c r="P103" s="49">
+      <c r="P103" s="40">
         <f t="shared" si="15"/>
         <v>686.78400000000011</v>
       </c>
@@ -6846,11 +6822,11 @@
         <f t="shared" si="13"/>
         <v>404.25</v>
       </c>
-      <c r="O104" s="48">
+      <c r="O104" s="39">
         <f t="shared" si="14"/>
         <v>80.850000000000009</v>
       </c>
-      <c r="P104" s="48">
+      <c r="P104" s="39">
         <f t="shared" si="15"/>
         <v>323.40000000000003</v>
       </c>
@@ -6900,11 +6876,11 @@
         <f t="shared" si="13"/>
         <v>847.36</v>
       </c>
-      <c r="O105" s="48">
+      <c r="O105" s="39">
         <f t="shared" si="14"/>
         <v>169.47200000000001</v>
       </c>
-      <c r="P105" s="48">
+      <c r="P105" s="39">
         <f t="shared" si="15"/>
         <v>677.88800000000003</v>
       </c>
@@ -6954,11 +6930,11 @@
         <f t="shared" si="13"/>
         <v>883.2</v>
       </c>
-      <c r="O106" s="48">
+      <c r="O106" s="39">
         <f t="shared" si="14"/>
         <v>176.64000000000001</v>
       </c>
-      <c r="P106" s="48">
+      <c r="P106" s="39">
         <f t="shared" si="15"/>
         <v>706.56000000000006</v>
       </c>
@@ -7008,11 +6984,11 @@
         <f t="shared" si="13"/>
         <v>518.4</v>
       </c>
-      <c r="O107" s="48">
+      <c r="O107" s="39">
         <f t="shared" si="14"/>
         <v>103.68</v>
       </c>
-      <c r="P107" s="48">
+      <c r="P107" s="39">
         <f t="shared" si="15"/>
         <v>414.72</v>
       </c>
@@ -7060,11 +7036,11 @@
         <f t="shared" si="13"/>
         <v>659.92499999999995</v>
       </c>
-      <c r="O108" s="48">
+      <c r="O108" s="39">
         <f t="shared" si="14"/>
         <v>131.98499999999999</v>
       </c>
-      <c r="P108" s="48">
+      <c r="P108" s="39">
         <f t="shared" si="15"/>
         <v>527.93999999999994</v>
       </c>
@@ -7114,11 +7090,11 @@
         <f t="shared" si="13"/>
         <v>518.4</v>
       </c>
-      <c r="O109" s="48">
+      <c r="O109" s="39">
         <f t="shared" si="14"/>
         <v>103.68</v>
       </c>
-      <c r="P109" s="48">
+      <c r="P109" s="39">
         <f t="shared" si="15"/>
         <v>414.72</v>
       </c>
@@ -7168,11 +7144,11 @@
         <f t="shared" si="13"/>
         <v>560.16</v>
       </c>
-      <c r="O110" s="48">
+      <c r="O110" s="39">
         <f t="shared" si="14"/>
         <v>112.032</v>
       </c>
-      <c r="P110" s="48">
+      <c r="P110" s="39">
         <f t="shared" si="15"/>
         <v>448.12799999999999</v>
       </c>
@@ -7222,11 +7198,11 @@
         <f t="shared" si="13"/>
         <v>837.6</v>
       </c>
-      <c r="O111" s="48">
+      <c r="O111" s="39">
         <f t="shared" si="14"/>
         <v>167.52</v>
       </c>
-      <c r="P111" s="48">
+      <c r="P111" s="39">
         <f t="shared" si="15"/>
         <v>670.08</v>
       </c>
@@ -7276,11 +7252,11 @@
         <f t="shared" si="13"/>
         <v>411.6</v>
       </c>
-      <c r="O112" s="48">
+      <c r="O112" s="39">
         <f t="shared" si="14"/>
         <v>82.320000000000007</v>
       </c>
-      <c r="P112" s="48">
+      <c r="P112" s="39">
         <f t="shared" si="15"/>
         <v>329.28000000000003</v>
       </c>
@@ -7330,11 +7306,11 @@
         <f t="shared" si="13"/>
         <v>2094</v>
       </c>
-      <c r="O113" s="48">
+      <c r="O113" s="39">
         <f t="shared" si="14"/>
         <v>418.8</v>
       </c>
-      <c r="P113" s="48">
+      <c r="P113" s="39">
         <f t="shared" si="15"/>
         <v>1675.2</v>
       </c>
@@ -7384,11 +7360,11 @@
         <f t="shared" si="13"/>
         <v>924</v>
       </c>
-      <c r="O114" s="48">
+      <c r="O114" s="39">
         <f t="shared" si="14"/>
         <v>184.8</v>
       </c>
-      <c r="P114" s="48">
+      <c r="P114" s="39">
         <f t="shared" si="15"/>
         <v>739.2</v>
       </c>
@@ -7438,11 +7414,11 @@
         <f t="shared" si="13"/>
         <v>617.4</v>
       </c>
-      <c r="O115" s="48">
+      <c r="O115" s="39">
         <f t="shared" si="14"/>
         <v>123.48</v>
       </c>
-      <c r="P115" s="48">
+      <c r="P115" s="39">
         <f t="shared" si="15"/>
         <v>493.92</v>
       </c>
@@ -7492,11 +7468,11 @@
         <f t="shared" si="13"/>
         <v>565.20000000000005</v>
       </c>
-      <c r="O116" s="48">
+      <c r="O116" s="39">
         <f t="shared" si="14"/>
         <v>113.04000000000002</v>
       </c>
-      <c r="P116" s="48">
+      <c r="P116" s="39">
         <f t="shared" si="15"/>
         <v>452.16000000000008</v>
       </c>
@@ -7546,11 +7522,11 @@
         <f t="shared" si="13"/>
         <v>282.60000000000002</v>
       </c>
-      <c r="O117" s="48">
+      <c r="O117" s="39">
         <f t="shared" si="14"/>
         <v>56.52000000000001</v>
       </c>
-      <c r="P117" s="49">
+      <c r="P117" s="40">
         <f t="shared" si="15"/>
         <v>226.08000000000004</v>
       </c>
@@ -7600,11 +7576,11 @@
         <f t="shared" si="13"/>
         <v>441</v>
       </c>
-      <c r="O118" s="48">
+      <c r="O118" s="39">
         <f t="shared" si="14"/>
         <v>88.2</v>
       </c>
-      <c r="P118" s="48">
+      <c r="P118" s="39">
         <f t="shared" si="15"/>
         <v>352.8</v>
       </c>
@@ -7654,11 +7630,11 @@
         <f t="shared" si="13"/>
         <v>266.76</v>
       </c>
-      <c r="O119" s="48">
+      <c r="O119" s="39">
         <f t="shared" si="14"/>
         <v>53.352000000000004</v>
       </c>
-      <c r="P119" s="48">
+      <c r="P119" s="39">
         <f t="shared" si="15"/>
         <v>213.40800000000002</v>
       </c>
@@ -7708,11 +7684,11 @@
         <f t="shared" si="13"/>
         <v>460.8</v>
       </c>
-      <c r="O120" s="48">
+      <c r="O120" s="39">
         <f t="shared" si="14"/>
         <v>92.160000000000011</v>
       </c>
-      <c r="P120" s="49">
+      <c r="P120" s="40">
         <f t="shared" si="15"/>
         <v>368.64000000000004</v>
       </c>
@@ -7762,11 +7738,11 @@
         <f t="shared" si="13"/>
         <v>666.9</v>
       </c>
-      <c r="O121" s="48">
+      <c r="O121" s="39">
         <f t="shared" si="14"/>
         <v>133.38</v>
       </c>
-      <c r="P121" s="48">
+      <c r="P121" s="39">
         <f t="shared" si="15"/>
         <v>533.52</v>
       </c>
@@ -7816,11 +7792,11 @@
         <f t="shared" si="13"/>
         <v>1543.5</v>
       </c>
-      <c r="O122" s="48">
+      <c r="O122" s="39">
         <f t="shared" si="14"/>
         <v>308.70000000000005</v>
       </c>
-      <c r="P122" s="49">
+      <c r="P122" s="40">
         <f t="shared" si="15"/>
         <v>1234.8000000000002</v>
       </c>
@@ -7870,11 +7846,11 @@
         <f t="shared" si="13"/>
         <v>248.39999999999998</v>
       </c>
-      <c r="O123" s="48">
+      <c r="O123" s="39">
         <f t="shared" si="14"/>
         <v>49.68</v>
       </c>
-      <c r="P123" s="48">
+      <c r="P123" s="39">
         <f t="shared" si="15"/>
         <v>198.72</v>
       </c>
@@ -7924,11 +7900,11 @@
         <f t="shared" si="13"/>
         <v>1543.5</v>
       </c>
-      <c r="O124" s="48">
+      <c r="O124" s="39">
         <f t="shared" si="14"/>
         <v>308.70000000000005</v>
       </c>
-      <c r="P124" s="48">
+      <c r="P124" s="39">
         <f t="shared" si="15"/>
         <v>1234.8000000000002</v>
       </c>
@@ -7978,11 +7954,11 @@
         <f t="shared" ref="N125:N158" si="17">M125*H125</f>
         <v>441</v>
       </c>
-      <c r="O125" s="48">
+      <c r="O125" s="39">
         <f t="shared" ref="O125:O158" si="18">0.2*N125</f>
         <v>88.2</v>
       </c>
-      <c r="P125" s="48">
+      <c r="P125" s="39">
         <f t="shared" ref="P125:P158" si="19">0.8*N125</f>
         <v>352.8</v>
       </c>
@@ -8032,11 +8008,11 @@
         <f t="shared" si="17"/>
         <v>248.39999999999998</v>
       </c>
-      <c r="O126" s="48">
+      <c r="O126" s="39">
         <f t="shared" si="18"/>
         <v>49.68</v>
       </c>
-      <c r="P126" s="48">
+      <c r="P126" s="39">
         <f t="shared" si="19"/>
         <v>198.72</v>
       </c>
@@ -8086,11 +8062,11 @@
         <f t="shared" si="17"/>
         <v>372.59999999999997</v>
       </c>
-      <c r="O127" s="48">
+      <c r="O127" s="39">
         <f t="shared" si="18"/>
         <v>74.52</v>
       </c>
-      <c r="P127" s="48">
+      <c r="P127" s="39">
         <f t="shared" si="19"/>
         <v>298.08</v>
       </c>
@@ -8140,11 +8116,11 @@
         <f t="shared" si="17"/>
         <v>411.6</v>
       </c>
-      <c r="O128" s="48">
+      <c r="O128" s="39">
         <f t="shared" si="18"/>
         <v>82.320000000000007</v>
       </c>
-      <c r="P128" s="48">
+      <c r="P128" s="39">
         <f t="shared" si="19"/>
         <v>329.28000000000003</v>
       </c>
@@ -8194,11 +8170,11 @@
         <f t="shared" si="17"/>
         <v>372.59999999999997</v>
       </c>
-      <c r="O129" s="48">
+      <c r="O129" s="39">
         <f t="shared" si="18"/>
         <v>74.52</v>
       </c>
-      <c r="P129" s="48">
+      <c r="P129" s="39">
         <f t="shared" si="19"/>
         <v>298.08</v>
       </c>
@@ -8248,11 +8224,11 @@
         <f t="shared" si="17"/>
         <v>621</v>
       </c>
-      <c r="O130" s="48">
+      <c r="O130" s="39">
         <f t="shared" si="18"/>
         <v>124.2</v>
       </c>
-      <c r="P130" s="48">
+      <c r="P130" s="39">
         <f t="shared" si="19"/>
         <v>496.8</v>
       </c>
@@ -8302,11 +8278,11 @@
         <f t="shared" si="17"/>
         <v>617.4</v>
       </c>
-      <c r="O131" s="48">
+      <c r="O131" s="39">
         <f t="shared" si="18"/>
         <v>123.48</v>
       </c>
-      <c r="P131" s="48">
+      <c r="P131" s="39">
         <f t="shared" si="19"/>
         <v>493.92</v>
       </c>
@@ -8356,11 +8332,11 @@
         <f t="shared" si="17"/>
         <v>248.39999999999998</v>
       </c>
-      <c r="O132" s="48">
+      <c r="O132" s="39">
         <f t="shared" si="18"/>
         <v>49.68</v>
       </c>
-      <c r="P132" s="48">
+      <c r="P132" s="39">
         <f t="shared" si="19"/>
         <v>198.72</v>
       </c>
@@ -8410,11 +8386,11 @@
         <f t="shared" si="17"/>
         <v>1280.1599999999999</v>
       </c>
-      <c r="O133" s="48">
+      <c r="O133" s="39">
         <f t="shared" si="18"/>
         <v>256.03199999999998</v>
       </c>
-      <c r="P133" s="49">
+      <c r="P133" s="40">
         <f t="shared" si="19"/>
         <v>1024.1279999999999</v>
       </c>
@@ -8464,11 +8440,11 @@
         <f t="shared" si="17"/>
         <v>992.25</v>
       </c>
-      <c r="O134" s="48">
+      <c r="O134" s="39">
         <f t="shared" si="18"/>
         <v>198.45000000000002</v>
       </c>
-      <c r="P134" s="48">
+      <c r="P134" s="39">
         <f t="shared" si="19"/>
         <v>793.80000000000007</v>
       </c>
@@ -8518,11 +8494,11 @@
         <f t="shared" si="17"/>
         <v>1294.0800000000002</v>
       </c>
-      <c r="O135" s="48">
+      <c r="O135" s="39">
         <f t="shared" si="18"/>
         <v>258.81600000000003</v>
       </c>
-      <c r="P135" s="48">
+      <c r="P135" s="39">
         <f t="shared" si="19"/>
         <v>1035.2640000000001</v>
       </c>
@@ -8572,11 +8548,11 @@
         <f t="shared" si="17"/>
         <v>992.25</v>
       </c>
-      <c r="O136" s="48">
+      <c r="O136" s="39">
         <f t="shared" si="18"/>
         <v>198.45000000000002</v>
       </c>
-      <c r="P136" s="48">
+      <c r="P136" s="39">
         <f t="shared" si="19"/>
         <v>793.80000000000007</v>
       </c>
@@ -8626,11 +8602,11 @@
         <f t="shared" si="17"/>
         <v>595.35</v>
       </c>
-      <c r="O137" s="48">
+      <c r="O137" s="39">
         <f t="shared" si="18"/>
         <v>119.07000000000001</v>
       </c>
-      <c r="P137" s="48">
+      <c r="P137" s="39">
         <f t="shared" si="19"/>
         <v>476.28000000000003</v>
       </c>
@@ -8680,11 +8656,11 @@
         <f t="shared" si="17"/>
         <v>272.26800000000003</v>
       </c>
-      <c r="O138" s="48">
+      <c r="O138" s="39">
         <f t="shared" si="18"/>
         <v>54.453600000000009</v>
       </c>
-      <c r="P138" s="49">
+      <c r="P138" s="40">
         <f t="shared" si="19"/>
         <v>217.81440000000003</v>
       </c>
@@ -8734,11 +8710,11 @@
         <f t="shared" si="17"/>
         <v>396.89999999999992</v>
       </c>
-      <c r="O139" s="48">
+      <c r="O139" s="39">
         <f t="shared" si="18"/>
         <v>79.38</v>
       </c>
-      <c r="P139" s="48">
+      <c r="P139" s="39">
         <f t="shared" si="19"/>
         <v>317.52</v>
       </c>
@@ -8788,11 +8764,11 @@
         <f t="shared" si="17"/>
         <v>195.51</v>
       </c>
-      <c r="O140" s="48">
+      <c r="O140" s="39">
         <f t="shared" si="18"/>
         <v>39.102000000000004</v>
       </c>
-      <c r="P140" s="48">
+      <c r="P140" s="39">
         <f t="shared" si="19"/>
         <v>156.40800000000002</v>
       </c>
@@ -8842,11 +8818,11 @@
         <f t="shared" si="17"/>
         <v>1777.664</v>
       </c>
-      <c r="O141" s="48">
+      <c r="O141" s="39">
         <f t="shared" si="18"/>
         <v>355.53280000000001</v>
       </c>
-      <c r="P141" s="48">
+      <c r="P141" s="39">
         <f t="shared" si="19"/>
         <v>1422.1312</v>
       </c>
@@ -8896,11 +8872,11 @@
         <f t="shared" si="17"/>
         <v>463.74399999999997</v>
       </c>
-      <c r="O142" s="48">
+      <c r="O142" s="39">
         <f t="shared" si="18"/>
         <v>92.748800000000003</v>
       </c>
-      <c r="P142" s="49">
+      <c r="P142" s="40">
         <f t="shared" si="19"/>
         <v>370.99520000000001</v>
       </c>
@@ -8950,11 +8926,11 @@
         <f t="shared" si="17"/>
         <v>400.05</v>
       </c>
-      <c r="O143" s="48">
+      <c r="O143" s="39">
         <f t="shared" si="18"/>
         <v>80.010000000000005</v>
       </c>
-      <c r="P143" s="48">
+      <c r="P143" s="39">
         <f t="shared" si="19"/>
         <v>320.04000000000002</v>
       </c>
@@ -9004,11 +8980,11 @@
         <f t="shared" si="17"/>
         <v>285.98399999999998</v>
       </c>
-      <c r="O144" s="49">
+      <c r="O144" s="40">
         <f t="shared" si="18"/>
         <v>57.196799999999996</v>
       </c>
-      <c r="P144" s="49">
+      <c r="P144" s="40">
         <f t="shared" si="19"/>
         <v>228.78719999999998</v>
       </c>
@@ -9058,11 +9034,11 @@
         <f t="shared" si="17"/>
         <v>456.49799999999999</v>
       </c>
-      <c r="O145" s="49">
+      <c r="O145" s="40">
         <f t="shared" si="18"/>
         <v>91.299599999999998</v>
       </c>
-      <c r="P145" s="49">
+      <c r="P145" s="40">
         <f t="shared" si="19"/>
         <v>365.19839999999999</v>
       </c>
@@ -9116,7 +9092,7 @@
         <f t="shared" si="18"/>
         <v>114.39359999999999</v>
       </c>
-      <c r="P146" s="49">
+      <c r="P146" s="40">
         <f t="shared" si="19"/>
         <v>457.57439999999997</v>
       </c>
@@ -9166,11 +9142,11 @@
         <f t="shared" si="17"/>
         <v>463.74399999999997</v>
       </c>
-      <c r="O147" s="49">
+      <c r="O147" s="40">
         <f t="shared" si="18"/>
         <v>92.748800000000003</v>
       </c>
-      <c r="P147" s="49">
+      <c r="P147" s="40">
         <f t="shared" si="19"/>
         <v>370.99520000000001</v>
       </c>
@@ -9220,11 +9196,11 @@
         <f t="shared" si="17"/>
         <v>285.98399999999998</v>
       </c>
-      <c r="O148" s="48">
+      <c r="O148" s="39">
         <f t="shared" si="18"/>
         <v>57.196799999999996</v>
       </c>
-      <c r="P148" s="49">
+      <c r="P148" s="40">
         <f t="shared" si="19"/>
         <v>228.78719999999998</v>
       </c>
@@ -9274,11 +9250,11 @@
         <f t="shared" si="17"/>
         <v>463.74399999999997</v>
       </c>
-      <c r="O149" s="48">
+      <c r="O149" s="39">
         <f t="shared" si="18"/>
         <v>92.748800000000003</v>
       </c>
-      <c r="P149" s="49">
+      <c r="P149" s="40">
         <f t="shared" si="19"/>
         <v>370.99520000000001</v>
       </c>
@@ -9328,11 +9304,11 @@
         <f t="shared" si="17"/>
         <v>285.98399999999998</v>
       </c>
-      <c r="O150" s="49">
+      <c r="O150" s="40">
         <f t="shared" si="18"/>
         <v>57.196799999999996</v>
       </c>
-      <c r="P150" s="49">
+      <c r="P150" s="40">
         <f t="shared" si="19"/>
         <v>228.78719999999998</v>
       </c>
@@ -9382,11 +9358,11 @@
         <f t="shared" si="17"/>
         <v>442.00599999999997</v>
       </c>
-      <c r="O151" s="49">
+      <c r="O151" s="40">
         <f t="shared" si="18"/>
         <v>88.401200000000003</v>
       </c>
-      <c r="P151" s="49">
+      <c r="P151" s="40">
         <f t="shared" si="19"/>
         <v>353.60480000000001</v>
       </c>
@@ -9436,11 +9412,11 @@
         <f t="shared" si="17"/>
         <v>435.96000000000004</v>
       </c>
-      <c r="O152" s="48">
+      <c r="O152" s="39">
         <f t="shared" si="18"/>
         <v>87.192000000000007</v>
       </c>
-      <c r="P152" s="49">
+      <c r="P152" s="40">
         <f t="shared" si="19"/>
         <v>348.76800000000003</v>
       </c>
@@ -9490,11 +9466,11 @@
         <f t="shared" si="17"/>
         <v>259.77</v>
       </c>
-      <c r="O153" s="48">
+      <c r="O153" s="39">
         <f t="shared" si="18"/>
         <v>51.954000000000001</v>
       </c>
-      <c r="P153" s="49">
+      <c r="P153" s="40">
         <f t="shared" si="19"/>
         <v>207.816</v>
       </c>
@@ -9544,11 +9520,11 @@
         <f t="shared" si="17"/>
         <v>266.04000000000002</v>
       </c>
-      <c r="O154" s="48">
+      <c r="O154" s="39">
         <f t="shared" si="18"/>
         <v>53.208000000000006</v>
       </c>
-      <c r="P154" s="48">
+      <c r="P154" s="39">
         <f t="shared" si="19"/>
         <v>212.83200000000002</v>
       </c>
@@ -9598,11 +9574,11 @@
         <f t="shared" si="17"/>
         <v>431.36</v>
       </c>
-      <c r="O155" s="48">
+      <c r="O155" s="39">
         <f t="shared" si="18"/>
         <v>86.272000000000006</v>
       </c>
-      <c r="P155" s="48">
+      <c r="P155" s="39">
         <f t="shared" si="19"/>
         <v>345.08800000000002</v>
       </c>
@@ -9652,11 +9628,11 @@
         <f t="shared" si="17"/>
         <v>200.02500000000001</v>
       </c>
-      <c r="O156" s="48">
+      <c r="O156" s="39">
         <f t="shared" si="18"/>
         <v>40.005000000000003</v>
       </c>
-      <c r="P156" s="48">
+      <c r="P156" s="39">
         <f t="shared" si="19"/>
         <v>160.02000000000001</v>
       </c>
@@ -9706,11 +9682,11 @@
         <f t="shared" si="17"/>
         <v>431.36</v>
       </c>
-      <c r="O157" s="48">
+      <c r="O157" s="39">
         <f t="shared" si="18"/>
         <v>86.272000000000006</v>
       </c>
-      <c r="P157" s="48">
+      <c r="P157" s="39">
         <f t="shared" si="19"/>
         <v>345.08800000000002</v>
       </c>
@@ -9760,11 +9736,11 @@
         <f t="shared" si="17"/>
         <v>2156.8000000000002</v>
       </c>
-      <c r="O158" s="48">
+      <c r="O158" s="39">
         <f t="shared" si="18"/>
         <v>431.36000000000007</v>
       </c>
-      <c r="P158" s="48">
+      <c r="P158" s="39">
         <f t="shared" si="19"/>
         <v>1725.4400000000003</v>
       </c>
@@ -9792,7 +9768,7 @@
         <v>33.700000000000003</v>
       </c>
       <c r="H159" s="12">
-        <f t="shared" ref="H159:H232" si="20">F159*G159</f>
+        <f t="shared" ref="H159:H231" si="20">F159*G159</f>
         <v>21568</v>
       </c>
       <c r="I159" s="29">
@@ -9814,11 +9790,11 @@
         <f t="shared" ref="N159:N165" si="21">M159*H159</f>
         <v>431.36</v>
       </c>
-      <c r="O159" s="48">
+      <c r="O159" s="39">
         <f t="shared" ref="O159:O165" si="22">0.2*N159</f>
         <v>86.272000000000006</v>
       </c>
-      <c r="P159" s="48">
+      <c r="P159" s="39">
         <f t="shared" ref="P159:P165" si="23">0.8*N159</f>
         <v>345.08800000000002</v>
       </c>
@@ -9868,11 +9844,11 @@
         <f t="shared" si="21"/>
         <v>431.36</v>
       </c>
-      <c r="O160" s="48">
+      <c r="O160" s="39">
         <f t="shared" si="22"/>
         <v>86.272000000000006</v>
       </c>
-      <c r="P160" s="48">
+      <c r="P160" s="39">
         <f t="shared" si="23"/>
         <v>345.08800000000002</v>
       </c>
@@ -9922,11 +9898,11 @@
         <f t="shared" si="21"/>
         <v>266.04000000000002</v>
       </c>
-      <c r="O161" s="48">
+      <c r="O161" s="39">
         <f t="shared" si="22"/>
         <v>53.208000000000006</v>
       </c>
-      <c r="P161" s="48">
+      <c r="P161" s="39">
         <f t="shared" si="23"/>
         <v>212.83200000000002</v>
       </c>
@@ -9976,11 +9952,11 @@
         <f t="shared" si="21"/>
         <v>888.83199999999999</v>
       </c>
-      <c r="O162" s="48">
+      <c r="O162" s="39">
         <f t="shared" si="22"/>
         <v>177.7664</v>
       </c>
-      <c r="P162" s="49">
+      <c r="P162" s="40">
         <f t="shared" si="23"/>
         <v>711.06560000000002</v>
       </c>
@@ -10030,11 +10006,11 @@
         <f t="shared" si="21"/>
         <v>444.416</v>
       </c>
-      <c r="O163" s="48">
+      <c r="O163" s="39">
         <f t="shared" si="22"/>
         <v>88.883200000000002</v>
       </c>
-      <c r="P163" s="49">
+      <c r="P163" s="40">
         <f t="shared" si="23"/>
         <v>355.53280000000001</v>
       </c>
@@ -10084,11 +10060,11 @@
         <f t="shared" si="21"/>
         <v>467.2</v>
       </c>
-      <c r="O164" s="48">
+      <c r="O164" s="39">
         <f t="shared" si="22"/>
         <v>93.44</v>
       </c>
-      <c r="P164" s="48">
+      <c r="P164" s="39">
         <f t="shared" si="23"/>
         <v>373.76</v>
       </c>
@@ -10138,11 +10114,11 @@
         <f t="shared" si="21"/>
         <v>1977.856</v>
       </c>
-      <c r="O165" s="49">
+      <c r="O165" s="40">
         <f t="shared" si="22"/>
         <v>395.57120000000003</v>
       </c>
-      <c r="P165" s="49">
+      <c r="P165" s="40">
         <f t="shared" si="23"/>
         <v>1582.2848000000001</v>
       </c>
@@ -10192,11 +10168,11 @@
         <f t="shared" ref="N166:N191" si="24">M166*H166</f>
         <v>960</v>
       </c>
-      <c r="O166" s="48">
+      <c r="O166" s="39">
         <f t="shared" ref="O166:O191" si="25">0.2*N166</f>
         <v>192</v>
       </c>
-      <c r="P166" s="48">
+      <c r="P166" s="39">
         <f t="shared" ref="P166:P191" si="26">0.8*N166</f>
         <v>768</v>
       </c>
@@ -10246,11 +10222,11 @@
         <f t="shared" si="24"/>
         <v>1018.32</v>
       </c>
-      <c r="O167" s="48">
+      <c r="O167" s="39">
         <f t="shared" si="25"/>
         <v>203.66400000000002</v>
       </c>
-      <c r="P167" s="49">
+      <c r="P167" s="40">
         <f t="shared" si="26"/>
         <v>814.65600000000006</v>
       </c>
@@ -10300,11 +10276,11 @@
         <f t="shared" si="24"/>
         <v>515.96800000000007</v>
       </c>
-      <c r="O168" s="48">
+      <c r="O168" s="39">
         <f t="shared" si="25"/>
         <v>103.19360000000002</v>
       </c>
-      <c r="P168" s="49">
+      <c r="P168" s="40">
         <f t="shared" si="26"/>
         <v>412.77440000000007</v>
       </c>
@@ -10354,11 +10330,11 @@
         <f t="shared" si="24"/>
         <v>639.36</v>
       </c>
-      <c r="O169" s="48">
+      <c r="O169" s="39">
         <f t="shared" si="25"/>
         <v>127.87200000000001</v>
       </c>
-      <c r="P169" s="49">
+      <c r="P169" s="40">
         <f t="shared" si="26"/>
         <v>511.48800000000006</v>
       </c>
@@ -10408,11 +10384,11 @@
         <f t="shared" si="24"/>
         <v>1996.8</v>
       </c>
-      <c r="O170" s="48">
+      <c r="O170" s="39">
         <f t="shared" si="25"/>
         <v>399.36</v>
       </c>
-      <c r="P170" s="49">
+      <c r="P170" s="40">
         <f t="shared" si="26"/>
         <v>1597.44</v>
       </c>
@@ -10462,11 +10438,11 @@
         <f t="shared" si="24"/>
         <v>998.4</v>
       </c>
-      <c r="O171" s="48">
+      <c r="O171" s="39">
         <f t="shared" si="25"/>
         <v>199.68</v>
       </c>
-      <c r="P171" s="49">
+      <c r="P171" s="40">
         <f t="shared" si="26"/>
         <v>798.72</v>
       </c>
@@ -10516,11 +10492,11 @@
         <f t="shared" si="24"/>
         <v>998.4</v>
       </c>
-      <c r="O172" s="49">
+      <c r="O172" s="40">
         <f t="shared" si="25"/>
         <v>199.68</v>
       </c>
-      <c r="P172" s="49">
+      <c r="P172" s="40">
         <f t="shared" si="26"/>
         <v>798.72</v>
       </c>
@@ -10570,11 +10546,11 @@
         <f t="shared" si="24"/>
         <v>1612.8</v>
       </c>
-      <c r="O173" s="49">
+      <c r="O173" s="40">
         <f t="shared" si="25"/>
         <v>322.56</v>
       </c>
-      <c r="P173" s="49">
+      <c r="P173" s="40">
         <f t="shared" si="26"/>
         <v>1290.24</v>
       </c>
@@ -10624,11 +10600,11 @@
         <f t="shared" si="24"/>
         <v>537.6</v>
       </c>
-      <c r="O174" s="49">
+      <c r="O174" s="40">
         <f t="shared" si="25"/>
         <v>107.52000000000001</v>
       </c>
-      <c r="P174" s="49">
+      <c r="P174" s="40">
         <f t="shared" si="26"/>
         <v>430.08000000000004</v>
       </c>
@@ -10678,11 +10654,11 @@
         <f t="shared" si="24"/>
         <v>1965.6000000000001</v>
       </c>
-      <c r="O175" s="49">
+      <c r="O175" s="40">
         <f t="shared" si="25"/>
         <v>393.12000000000006</v>
       </c>
-      <c r="P175" s="49">
+      <c r="P175" s="40">
         <f t="shared" si="26"/>
         <v>1572.4800000000002</v>
       </c>
@@ -10732,11 +10708,11 @@
         <f t="shared" si="24"/>
         <v>639.36</v>
       </c>
-      <c r="O176" s="49">
+      <c r="O176" s="40">
         <f t="shared" si="25"/>
         <v>127.87200000000001</v>
       </c>
-      <c r="P176" s="49">
+      <c r="P176" s="40">
         <f t="shared" si="26"/>
         <v>511.48800000000006</v>
       </c>
@@ -10786,11 +10762,11 @@
         <f t="shared" si="24"/>
         <v>512.76</v>
       </c>
-      <c r="O177" s="49">
+      <c r="O177" s="40">
         <f t="shared" si="25"/>
         <v>102.55200000000001</v>
       </c>
-      <c r="P177" s="49">
+      <c r="P177" s="40">
         <f t="shared" si="26"/>
         <v>410.20800000000003</v>
       </c>
@@ -10840,11 +10816,11 @@
         <f t="shared" si="24"/>
         <v>153.9</v>
       </c>
-      <c r="O178" s="49">
+      <c r="O178" s="40">
         <f t="shared" si="25"/>
         <v>30.78</v>
       </c>
-      <c r="P178" s="49">
+      <c r="P178" s="40">
         <f t="shared" si="26"/>
         <v>123.12</v>
       </c>
@@ -10894,11 +10870,11 @@
         <f t="shared" si="24"/>
         <v>491.40000000000003</v>
       </c>
-      <c r="O179" s="49">
+      <c r="O179" s="40">
         <f t="shared" si="25"/>
         <v>98.280000000000015</v>
       </c>
-      <c r="P179" s="49">
+      <c r="P179" s="40">
         <f t="shared" si="26"/>
         <v>393.12000000000006</v>
       </c>
@@ -10948,11 +10924,11 @@
         <f t="shared" si="24"/>
         <v>317.08800000000002</v>
       </c>
-      <c r="O180" s="49">
+      <c r="O180" s="40">
         <f t="shared" si="25"/>
         <v>63.417600000000007</v>
       </c>
-      <c r="P180" s="49">
+      <c r="P180" s="40">
         <f t="shared" si="26"/>
         <v>253.67040000000003</v>
       </c>
@@ -11002,11 +10978,11 @@
         <f t="shared" si="24"/>
         <v>306.28800000000001</v>
       </c>
-      <c r="O181" s="49">
+      <c r="O181" s="40">
         <f t="shared" si="25"/>
         <v>61.257600000000004</v>
       </c>
-      <c r="P181" s="49">
+      <c r="P181" s="40">
         <f t="shared" si="26"/>
         <v>245.03040000000001</v>
       </c>
@@ -11056,11 +11032,11 @@
         <f t="shared" si="24"/>
         <v>512.76</v>
       </c>
-      <c r="O182" s="49">
+      <c r="O182" s="40">
         <f t="shared" si="25"/>
         <v>102.55200000000001</v>
       </c>
-      <c r="P182" s="49">
+      <c r="P182" s="40">
         <f t="shared" si="26"/>
         <v>410.20800000000003</v>
       </c>
@@ -11110,11 +11086,11 @@
         <f t="shared" si="24"/>
         <v>330.91199999999998</v>
       </c>
-      <c r="O183" s="49">
+      <c r="O183" s="40">
         <f t="shared" si="25"/>
         <v>66.182400000000001</v>
       </c>
-      <c r="P183" s="49">
+      <c r="P183" s="40">
         <f t="shared" si="26"/>
         <v>264.7296</v>
       </c>
@@ -11164,11 +11140,11 @@
         <f t="shared" si="24"/>
         <v>319.68</v>
       </c>
-      <c r="O184" s="49">
+      <c r="O184" s="40">
         <f t="shared" si="25"/>
         <v>63.936000000000007</v>
       </c>
-      <c r="P184" s="49">
+      <c r="P184" s="40">
         <f t="shared" si="26"/>
         <v>255.74400000000003</v>
       </c>
@@ -11218,11 +11194,11 @@
         <f t="shared" si="24"/>
         <v>319.68</v>
       </c>
-      <c r="O185" s="49">
+      <c r="O185" s="40">
         <f t="shared" si="25"/>
         <v>63.936000000000007</v>
       </c>
-      <c r="P185" s="49">
+      <c r="P185" s="40">
         <f t="shared" si="26"/>
         <v>255.74400000000003</v>
       </c>
@@ -11272,11 +11248,11 @@
         <f t="shared" si="24"/>
         <v>1417.5</v>
       </c>
-      <c r="O186" s="49">
+      <c r="O186" s="40">
         <f t="shared" si="25"/>
         <v>283.5</v>
       </c>
-      <c r="P186" s="49">
+      <c r="P186" s="40">
         <f t="shared" si="26"/>
         <v>1134</v>
       </c>
@@ -11326,11 +11302,11 @@
         <f t="shared" si="24"/>
         <v>615.6</v>
       </c>
-      <c r="O187" s="49">
+      <c r="O187" s="40">
         <f t="shared" si="25"/>
         <v>123.12</v>
       </c>
-      <c r="P187" s="49">
+      <c r="P187" s="40">
         <f t="shared" si="26"/>
         <v>492.48</v>
       </c>
@@ -11380,11 +11356,11 @@
         <f t="shared" si="24"/>
         <v>1064.7</v>
       </c>
-      <c r="O188" s="49">
+      <c r="O188" s="40">
         <f t="shared" si="25"/>
         <v>212.94000000000003</v>
       </c>
-      <c r="P188" s="49">
+      <c r="P188" s="40">
         <f t="shared" si="26"/>
         <v>851.7600000000001</v>
       </c>
@@ -11434,11 +11410,11 @@
         <f t="shared" si="24"/>
         <v>532.35</v>
       </c>
-      <c r="O189" s="49">
+      <c r="O189" s="40">
         <f t="shared" si="25"/>
         <v>106.47000000000001</v>
       </c>
-      <c r="P189" s="49">
+      <c r="P189" s="40">
         <f t="shared" si="26"/>
         <v>425.88000000000005</v>
       </c>
@@ -11488,11 +11464,11 @@
         <f t="shared" si="24"/>
         <v>321.98399999999998</v>
       </c>
-      <c r="O190" s="49">
+      <c r="O190" s="40">
         <f t="shared" si="25"/>
         <v>64.396799999999999</v>
       </c>
-      <c r="P190" s="49">
+      <c r="P190" s="40">
         <f t="shared" si="26"/>
         <v>257.5872</v>
       </c>
@@ -11542,11 +11518,11 @@
         <f t="shared" si="24"/>
         <v>965.952</v>
       </c>
-      <c r="O191" s="49">
+      <c r="O191" s="40">
         <f t="shared" si="25"/>
         <v>193.19040000000001</v>
       </c>
-      <c r="P191" s="49">
+      <c r="P191" s="40">
         <f t="shared" si="26"/>
         <v>772.76160000000004</v>
       </c>
@@ -11596,11 +11572,11 @@
         <f t="shared" ref="N192:N206" si="27">M192*H192</f>
         <v>2475.8999999999996</v>
       </c>
-      <c r="O192" s="49">
+      <c r="O192" s="40">
         <f t="shared" ref="O192:O206" si="28">0.2*N192</f>
         <v>495.17999999999995</v>
       </c>
-      <c r="P192" s="49">
+      <c r="P192" s="40">
         <f t="shared" ref="P192:P206" si="29">0.8*N192</f>
         <v>1980.7199999999998</v>
       </c>
@@ -11650,11 +11626,11 @@
         <f t="shared" si="27"/>
         <v>333.71999999999997</v>
       </c>
-      <c r="O193" s="49">
+      <c r="O193" s="40">
         <f t="shared" si="28"/>
         <v>66.744</v>
       </c>
-      <c r="P193" s="49">
+      <c r="P193" s="40">
         <f t="shared" si="29"/>
         <v>266.976</v>
       </c>
@@ -11704,11 +11680,11 @@
         <f t="shared" si="27"/>
         <v>517.60799999999995</v>
       </c>
-      <c r="O194" s="49">
+      <c r="O194" s="40">
         <f t="shared" si="28"/>
         <v>103.52159999999999</v>
       </c>
-      <c r="P194" s="49">
+      <c r="P194" s="40">
         <f t="shared" si="29"/>
         <v>414.08639999999997</v>
       </c>
@@ -11758,11 +11734,11 @@
         <f t="shared" si="27"/>
         <v>532.35</v>
       </c>
-      <c r="O195" s="49">
+      <c r="O195" s="40">
         <f t="shared" si="28"/>
         <v>106.47000000000001</v>
       </c>
-      <c r="P195" s="49">
+      <c r="P195" s="40">
         <f t="shared" si="29"/>
         <v>425.88000000000005</v>
       </c>
@@ -11812,11 +11788,11 @@
         <f t="shared" si="27"/>
         <v>179.38799999999998</v>
       </c>
-      <c r="O196" s="49">
+      <c r="O196" s="40">
         <f t="shared" si="28"/>
         <v>35.877599999999994</v>
       </c>
-      <c r="P196" s="49">
+      <c r="P196" s="40">
         <f t="shared" si="29"/>
         <v>143.51039999999998</v>
       </c>
@@ -11866,11 +11842,11 @@
         <f t="shared" si="27"/>
         <v>358.77599999999995</v>
       </c>
-      <c r="O197" s="49">
+      <c r="O197" s="40">
         <f t="shared" si="28"/>
         <v>71.755199999999988</v>
       </c>
-      <c r="P197" s="49">
+      <c r="P197" s="40">
         <f t="shared" si="29"/>
         <v>287.02079999999995</v>
       </c>
@@ -11920,11 +11896,11 @@
         <f t="shared" si="27"/>
         <v>333.71999999999997</v>
       </c>
-      <c r="O198" s="49">
+      <c r="O198" s="40">
         <f t="shared" si="28"/>
         <v>66.744</v>
       </c>
-      <c r="P198" s="49">
+      <c r="P198" s="40">
         <f t="shared" si="29"/>
         <v>266.976</v>
       </c>
@@ -11974,11 +11950,11 @@
         <f t="shared" si="27"/>
         <v>517.60799999999995</v>
       </c>
-      <c r="O199" s="49">
+      <c r="O199" s="40">
         <f t="shared" si="28"/>
         <v>103.52159999999999</v>
       </c>
-      <c r="P199" s="49">
+      <c r="P199" s="40">
         <f t="shared" si="29"/>
         <v>414.08639999999997</v>
       </c>
@@ -12028,11 +12004,11 @@
         <f t="shared" si="27"/>
         <v>555.44999999999993</v>
       </c>
-      <c r="O200" s="49">
+      <c r="O200" s="40">
         <f t="shared" si="28"/>
         <v>111.08999999999999</v>
       </c>
-      <c r="P200" s="49">
+      <c r="P200" s="40">
         <f t="shared" si="29"/>
         <v>444.35999999999996</v>
       </c>
@@ -12082,11 +12058,11 @@
         <f t="shared" si="27"/>
         <v>1808.1</v>
       </c>
-      <c r="O201" s="49">
+      <c r="O201" s="40">
         <f t="shared" si="28"/>
         <v>361.62</v>
       </c>
-      <c r="P201" s="49">
+      <c r="P201" s="40">
         <f t="shared" si="29"/>
         <v>1446.48</v>
       </c>
@@ -12136,11 +12112,11 @@
         <f t="shared" si="27"/>
         <v>555.44999999999993</v>
       </c>
-      <c r="O202" s="49">
+      <c r="O202" s="40">
         <f t="shared" si="28"/>
         <v>111.08999999999999</v>
       </c>
-      <c r="P202" s="49">
+      <c r="P202" s="40">
         <f t="shared" si="29"/>
         <v>444.35999999999996</v>
       </c>
@@ -12190,11 +12166,11 @@
         <f t="shared" si="27"/>
         <v>370.3</v>
       </c>
-      <c r="O203" s="49">
+      <c r="O203" s="40">
         <f t="shared" si="28"/>
         <v>74.06</v>
       </c>
-      <c r="P203" s="49">
+      <c r="P203" s="40">
         <f t="shared" si="29"/>
         <v>296.24</v>
       </c>
@@ -12244,11 +12220,11 @@
         <f t="shared" si="27"/>
         <v>532.35</v>
       </c>
-      <c r="O204" s="49">
+      <c r="O204" s="40">
         <f t="shared" si="28"/>
         <v>106.47000000000001</v>
       </c>
-      <c r="P204" s="49">
+      <c r="P204" s="40">
         <f t="shared" si="29"/>
         <v>425.88000000000005</v>
       </c>
@@ -12298,11 +12274,11 @@
         <f t="shared" si="27"/>
         <v>1388.625</v>
       </c>
-      <c r="O205" s="49">
+      <c r="O205" s="40">
         <f t="shared" si="28"/>
         <v>277.72500000000002</v>
       </c>
-      <c r="P205" s="49">
+      <c r="P205" s="40">
         <f t="shared" si="29"/>
         <v>1110.9000000000001</v>
       </c>
@@ -12352,11 +12328,11 @@
         <f t="shared" si="27"/>
         <v>179.38799999999998</v>
       </c>
-      <c r="O206" s="49">
+      <c r="O206" s="40">
         <f t="shared" si="28"/>
         <v>35.877599999999994</v>
       </c>
-      <c r="P206" s="49">
+      <c r="P206" s="40">
         <f t="shared" si="29"/>
         <v>143.51039999999998</v>
       </c>
@@ -12403,66 +12379,70 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N207" s="11">
-        <f t="shared" ref="N207:N210" si="30">M207*H207</f>
+        <f t="shared" ref="N207:N209" si="30">M207*H207</f>
         <v>294.52499999999998</v>
       </c>
-      <c r="O207" s="49">
-        <f t="shared" ref="O207:O210" si="31">0.2*N207</f>
+      <c r="O207" s="40">
+        <f t="shared" ref="O207:O209" si="31">0.2*N207</f>
         <v>58.905000000000001</v>
       </c>
-      <c r="P207" s="49">
-        <f t="shared" ref="P207:P210" si="32">0.8*N207</f>
+      <c r="P207" s="40">
+        <f t="shared" ref="P207:P209" si="32">0.8*N207</f>
         <v>235.62</v>
       </c>
     </row>
     <row r="208" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A208" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B208" s="34">
-        <v>152</v>
-      </c>
-      <c r="C208" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D208" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E208" s="33" t="s">
+      <c r="A208" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B208" s="16">
+        <v>153</v>
+      </c>
+      <c r="C208" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D208" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E208" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F208" s="35">
-        <v>1400</v>
-      </c>
-      <c r="G208" s="36">
+      <c r="F208" s="10">
+        <v>700</v>
+      </c>
+      <c r="G208" s="11">
         <v>26.45</v>
       </c>
-      <c r="H208" s="37">
+      <c r="H208" s="12">
         <f t="shared" si="20"/>
-        <v>37030</v>
-      </c>
-      <c r="I208" s="38">
-        <v>45705</v>
-      </c>
-      <c r="J208" s="39"/>
-      <c r="K208" s="33" t="s">
+        <v>18515</v>
+      </c>
+      <c r="I208" s="29">
+        <v>45706</v>
+      </c>
+      <c r="J208" s="25">
+        <v>45706</v>
+      </c>
+      <c r="K208" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L208" s="38"/>
-      <c r="M208" s="40">
+      <c r="L208" s="29">
+        <v>45856</v>
+      </c>
+      <c r="M208" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N208" s="36">
+      <c r="N208" s="11">
         <f t="shared" si="30"/>
-        <v>555.44999999999993</v>
-      </c>
-      <c r="O208" s="36">
+        <v>277.72499999999997</v>
+      </c>
+      <c r="O208" s="40">
         <f t="shared" si="31"/>
-        <v>111.08999999999999</v>
-      </c>
-      <c r="P208" s="36">
+        <v>55.544999999999995</v>
+      </c>
+      <c r="P208" s="40">
         <f t="shared" si="32"/>
-        <v>444.35999999999996</v>
+        <v>222.17999999999998</v>
       </c>
     </row>
     <row r="209" spans="1:16" x14ac:dyDescent="0.2">
@@ -12470,53 +12450,53 @@
         <v>14</v>
       </c>
       <c r="B209" s="16">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C209" s="9" t="s">
-        <v>99</v>
+        <v>40</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>112</v>
+        <v>19</v>
       </c>
       <c r="E209" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F209" s="10">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="G209" s="11">
-        <v>26.45</v>
+        <v>24.6</v>
       </c>
       <c r="H209" s="12">
         <f t="shared" si="20"/>
-        <v>18515</v>
+        <v>34440</v>
       </c>
       <c r="I209" s="29">
         <v>45706</v>
       </c>
       <c r="J209" s="25">
-        <v>45706</v>
+        <v>45729</v>
       </c>
       <c r="K209" s="9" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="L209" s="29">
-        <v>45856</v>
+        <v>45760</v>
       </c>
       <c r="M209" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N209" s="11">
         <f t="shared" si="30"/>
-        <v>277.72499999999997</v>
-      </c>
-      <c r="O209" s="49">
+        <v>516.6</v>
+      </c>
+      <c r="O209" s="40">
         <f t="shared" si="31"/>
-        <v>55.544999999999995</v>
-      </c>
-      <c r="P209" s="49">
+        <v>103.32000000000001</v>
+      </c>
+      <c r="P209" s="40">
         <f t="shared" si="32"/>
-        <v>222.17999999999998</v>
+        <v>413.28000000000003</v>
       </c>
     </row>
     <row r="210" spans="1:16" x14ac:dyDescent="0.2">
@@ -12524,13 +12504,13 @@
         <v>14</v>
       </c>
       <c r="B210" s="16">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C210" s="9" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="D210" s="9" t="s">
-        <v>19</v>
+        <v>112</v>
       </c>
       <c r="E210" s="9" t="s">
         <v>39</v>
@@ -12539,38 +12519,38 @@
         <v>1400</v>
       </c>
       <c r="G210" s="11">
-        <v>24.6</v>
+        <v>26.45</v>
       </c>
       <c r="H210" s="12">
-        <f t="shared" si="20"/>
-        <v>34440</v>
+        <f t="shared" ref="H210:H222" si="33">F210*G210</f>
+        <v>37030</v>
       </c>
       <c r="I210" s="29">
-        <v>45706</v>
+        <v>45708</v>
       </c>
       <c r="J210" s="25">
-        <v>45729</v>
+        <v>45727</v>
       </c>
       <c r="K210" s="9" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="L210" s="29">
-        <v>45760</v>
+        <v>45880</v>
       </c>
       <c r="M210" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N210" s="11">
-        <f t="shared" si="30"/>
-        <v>516.6</v>
-      </c>
-      <c r="O210" s="49">
-        <f t="shared" si="31"/>
-        <v>103.32000000000001</v>
-      </c>
-      <c r="P210" s="49">
-        <f t="shared" si="32"/>
-        <v>413.28000000000003</v>
+        <f t="shared" ref="N210:N222" si="34">M210*H210</f>
+        <v>555.44999999999993</v>
+      </c>
+      <c r="O210" s="40">
+        <f t="shared" ref="O210:O222" si="35">0.2*N210</f>
+        <v>111.08999999999999</v>
+      </c>
+      <c r="P210" s="40">
+        <f t="shared" ref="P210:P222" si="36">0.8*N210</f>
+        <v>444.35999999999996</v>
       </c>
     </row>
     <row r="211" spans="1:16" x14ac:dyDescent="0.2">
@@ -12578,53 +12558,53 @@
         <v>14</v>
       </c>
       <c r="B211" s="16">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C211" s="9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="E211" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F211" s="10">
-        <v>1400</v>
+        <v>1260</v>
       </c>
       <c r="G211" s="11">
-        <v>26.45</v>
+        <v>42.25</v>
       </c>
       <c r="H211" s="12">
-        <f t="shared" ref="H211:H223" si="33">F211*G211</f>
-        <v>37030</v>
+        <f t="shared" si="33"/>
+        <v>53235</v>
       </c>
       <c r="I211" s="29">
-        <v>45708</v>
+        <v>45735</v>
       </c>
       <c r="J211" s="25">
-        <v>45727</v>
+        <v>45750</v>
       </c>
       <c r="K211" s="9" t="s">
         <v>71</v>
       </c>
       <c r="L211" s="29">
-        <v>45880</v>
+        <v>45900</v>
       </c>
       <c r="M211" s="13">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N211" s="11">
-        <f t="shared" ref="N211:N223" si="34">M211*H211</f>
-        <v>555.44999999999993</v>
-      </c>
-      <c r="O211" s="49">
-        <f t="shared" ref="O211:O223" si="35">0.2*N211</f>
-        <v>111.08999999999999</v>
-      </c>
-      <c r="P211" s="49">
-        <f t="shared" ref="P211:P223" si="36">0.8*N211</f>
-        <v>444.35999999999996</v>
+        <f t="shared" si="34"/>
+        <v>1064.7</v>
+      </c>
+      <c r="O211" s="40">
+        <f t="shared" si="35"/>
+        <v>212.94000000000003</v>
+      </c>
+      <c r="P211" s="40">
+        <f t="shared" si="36"/>
+        <v>851.7600000000001</v>
       </c>
     </row>
     <row r="212" spans="1:16" x14ac:dyDescent="0.2">
@@ -12632,26 +12612,26 @@
         <v>14</v>
       </c>
       <c r="B212" s="16">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C212" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D212" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E212" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F212" s="10">
-        <v>1260</v>
+        <v>720</v>
       </c>
       <c r="G212" s="11">
-        <v>42.25</v>
+        <v>44.72</v>
       </c>
       <c r="H212" s="12">
         <f t="shared" si="33"/>
-        <v>53235</v>
+        <v>32198.399999999998</v>
       </c>
       <c r="I212" s="29">
         <v>45735</v>
@@ -12670,15 +12650,15 @@
       </c>
       <c r="N212" s="11">
         <f t="shared" si="34"/>
-        <v>1064.7</v>
-      </c>
-      <c r="O212" s="49">
+        <v>643.96799999999996</v>
+      </c>
+      <c r="O212" s="40">
         <f t="shared" si="35"/>
-        <v>212.94000000000003</v>
-      </c>
-      <c r="P212" s="49">
+        <v>128.7936</v>
+      </c>
+      <c r="P212" s="40">
         <f t="shared" si="36"/>
-        <v>851.7600000000001</v>
+        <v>515.17439999999999</v>
       </c>
     </row>
     <row r="213" spans="1:16" x14ac:dyDescent="0.2">
@@ -12695,17 +12675,17 @@
         <v>83</v>
       </c>
       <c r="E213" s="9" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F213" s="10">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="G213" s="11">
-        <v>44.72</v>
+        <v>26.45</v>
       </c>
       <c r="H213" s="12">
         <f t="shared" si="33"/>
-        <v>32198.399999999998</v>
+        <v>18515</v>
       </c>
       <c r="I213" s="29">
         <v>45735</v>
@@ -12720,19 +12700,19 @@
         <v>45900</v>
       </c>
       <c r="M213" s="13">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N213" s="11">
         <f t="shared" si="34"/>
-        <v>643.96799999999996</v>
-      </c>
-      <c r="O213" s="49">
+        <v>277.72499999999997</v>
+      </c>
+      <c r="O213" s="40">
         <f t="shared" si="35"/>
-        <v>128.7936</v>
-      </c>
-      <c r="P213" s="49">
+        <v>55.544999999999995</v>
+      </c>
+      <c r="P213" s="40">
         <f t="shared" si="36"/>
-        <v>515.17439999999999</v>
+        <v>222.17999999999998</v>
       </c>
     </row>
     <row r="214" spans="1:16" x14ac:dyDescent="0.2">
@@ -12740,13 +12720,13 @@
         <v>14</v>
       </c>
       <c r="B214" s="16">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C214" s="9" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D214" s="9" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="E214" s="9" t="s">
         <v>39</v>
@@ -12762,7 +12742,7 @@
         <v>18515</v>
       </c>
       <c r="I214" s="29">
-        <v>45735</v>
+        <v>45737</v>
       </c>
       <c r="J214" s="25">
         <v>45750</v>
@@ -12780,11 +12760,11 @@
         <f t="shared" si="34"/>
         <v>277.72499999999997</v>
       </c>
-      <c r="O214" s="49">
+      <c r="O214" s="40">
         <f t="shared" si="35"/>
         <v>55.544999999999995</v>
       </c>
-      <c r="P214" s="49">
+      <c r="P214" s="40">
         <f t="shared" si="36"/>
         <v>222.17999999999998</v>
       </c>
@@ -12803,17 +12783,17 @@
         <v>112</v>
       </c>
       <c r="E215" s="9" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F215" s="10">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="G215" s="11">
-        <v>26.45</v>
+        <v>33.22</v>
       </c>
       <c r="H215" s="12">
         <f t="shared" si="33"/>
-        <v>18515</v>
+        <v>23918.399999999998</v>
       </c>
       <c r="I215" s="29">
         <v>45737</v>
@@ -12832,71 +12812,71 @@
       </c>
       <c r="N215" s="11">
         <f t="shared" si="34"/>
+        <v>358.77599999999995</v>
+      </c>
+      <c r="O215" s="40">
+        <f t="shared" si="35"/>
+        <v>71.755199999999988</v>
+      </c>
+      <c r="P215" s="40">
+        <f t="shared" si="36"/>
+        <v>287.02079999999995</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A216" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B216" s="16">
+        <v>159</v>
+      </c>
+      <c r="C216" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D216" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="E216" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F216" s="10">
+        <v>700</v>
+      </c>
+      <c r="G216" s="11">
+        <v>26.45</v>
+      </c>
+      <c r="H216" s="12">
+        <f t="shared" si="33"/>
+        <v>18515</v>
+      </c>
+      <c r="I216" s="29">
+        <v>45740</v>
+      </c>
+      <c r="J216" s="25">
+        <v>45750</v>
+      </c>
+      <c r="K216" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="L216" s="29">
+        <v>45900</v>
+      </c>
+      <c r="M216" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N216" s="11">
+        <f t="shared" si="34"/>
         <v>277.72499999999997</v>
       </c>
-      <c r="O215" s="49">
+      <c r="O216" s="40">
         <f t="shared" si="35"/>
         <v>55.544999999999995</v>
       </c>
-      <c r="P215" s="49">
+      <c r="P216" s="40">
         <f t="shared" si="36"/>
         <v>222.17999999999998</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A216" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B216" s="16">
-        <v>158</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D216" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E216" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F216" s="10">
-        <v>720</v>
-      </c>
-      <c r="G216" s="11">
-        <v>33.22</v>
-      </c>
-      <c r="H216" s="12">
-        <f t="shared" si="33"/>
-        <v>23918.399999999998</v>
-      </c>
-      <c r="I216" s="29">
-        <v>45737</v>
-      </c>
-      <c r="J216" s="25">
-        <v>45750</v>
-      </c>
-      <c r="K216" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="L216" s="29">
-        <v>45900</v>
-      </c>
-      <c r="M216" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N216" s="11">
-        <f t="shared" si="34"/>
-        <v>358.77599999999995</v>
-      </c>
-      <c r="O216" s="49">
-        <f t="shared" si="35"/>
-        <v>71.755199999999988</v>
-      </c>
-      <c r="P216" s="49">
-        <f t="shared" si="36"/>
-        <v>287.02079999999995</v>
-      </c>
-    </row>
     <row r="217" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A217" s="9" t="s">
         <v>14</v>
@@ -12911,17 +12891,17 @@
         <v>114</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F217" s="10">
-        <v>700</v>
+        <v>360</v>
       </c>
       <c r="G217" s="11">
-        <v>26.45</v>
+        <v>33.22</v>
       </c>
       <c r="H217" s="12">
         <f t="shared" si="33"/>
-        <v>18515</v>
+        <v>11959.199999999999</v>
       </c>
       <c r="I217" s="29">
         <v>45740</v>
@@ -12940,15 +12920,15 @@
       </c>
       <c r="N217" s="11">
         <f t="shared" si="34"/>
-        <v>277.72499999999997</v>
-      </c>
-      <c r="O217" s="49">
+        <v>179.38799999999998</v>
+      </c>
+      <c r="O217" s="40">
         <f t="shared" si="35"/>
-        <v>55.544999999999995</v>
-      </c>
-      <c r="P217" s="49">
+        <v>35.877599999999994</v>
+      </c>
+      <c r="P217" s="40">
         <f t="shared" si="36"/>
-        <v>222.17999999999998</v>
+        <v>143.51039999999998</v>
       </c>
     </row>
     <row r="218" spans="1:16" x14ac:dyDescent="0.2">
@@ -12956,53 +12936,53 @@
         <v>14</v>
       </c>
       <c r="B218" s="16">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C218" s="9" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="D218" s="9" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E218" s="9" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="F218" s="10">
-        <v>360</v>
+        <v>630</v>
       </c>
       <c r="G218" s="11">
-        <v>33.22</v>
+        <v>41.08</v>
       </c>
       <c r="H218" s="12">
         <f t="shared" si="33"/>
-        <v>11959.199999999999</v>
+        <v>25880.399999999998</v>
       </c>
       <c r="I218" s="29">
-        <v>45740</v>
+        <v>45748</v>
       </c>
       <c r="J218" s="25">
-        <v>45750</v>
+        <v>45757</v>
       </c>
       <c r="K218" s="9" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="L218" s="29">
-        <v>45900</v>
+        <v>45869</v>
       </c>
       <c r="M218" s="13">
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N218" s="11">
         <f t="shared" si="34"/>
-        <v>179.38799999999998</v>
-      </c>
-      <c r="O218" s="49">
+        <v>517.60799999999995</v>
+      </c>
+      <c r="O218" s="40">
         <f t="shared" si="35"/>
-        <v>35.877599999999994</v>
-      </c>
-      <c r="P218" s="49">
+        <v>103.52159999999999</v>
+      </c>
+      <c r="P218" s="40">
         <f t="shared" si="36"/>
-        <v>143.51039999999998</v>
+        <v>414.08639999999997</v>
       </c>
     </row>
     <row r="219" spans="1:16" x14ac:dyDescent="0.2">
@@ -13010,53 +12990,53 @@
         <v>14</v>
       </c>
       <c r="B219" s="16">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C219" s="9" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="D219" s="9" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="E219" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F219" s="10">
-        <v>630</v>
+        <v>3150</v>
       </c>
       <c r="G219" s="11">
-        <v>41.08</v>
+        <v>39.299999999999997</v>
       </c>
       <c r="H219" s="12">
         <f t="shared" si="33"/>
-        <v>25880.399999999998</v>
+        <v>123794.99999999999</v>
       </c>
       <c r="I219" s="29">
-        <v>45748</v>
+        <v>45750</v>
       </c>
       <c r="J219" s="25">
         <v>45757</v>
       </c>
       <c r="K219" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L219" s="29">
-        <v>45869</v>
+        <v>45787</v>
       </c>
       <c r="M219" s="13">
         <v>0.02</v>
       </c>
       <c r="N219" s="11">
         <f t="shared" si="34"/>
-        <v>517.60799999999995</v>
-      </c>
-      <c r="O219" s="49">
+        <v>2475.8999999999996</v>
+      </c>
+      <c r="O219" s="40">
         <f t="shared" si="35"/>
-        <v>103.52159999999999</v>
-      </c>
-      <c r="P219" s="49">
+        <v>495.17999999999995</v>
+      </c>
+      <c r="P219" s="40">
         <f t="shared" si="36"/>
-        <v>414.08639999999997</v>
+        <v>1980.7199999999998</v>
       </c>
     </row>
     <row r="220" spans="1:16" x14ac:dyDescent="0.2">
@@ -13064,13 +13044,13 @@
         <v>14</v>
       </c>
       <c r="B220" s="16">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D220" s="9" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="E220" s="9" t="s">
         <v>20</v>
@@ -13079,38 +13059,38 @@
         <v>3150</v>
       </c>
       <c r="G220" s="11">
-        <v>39.299999999999997</v>
+        <v>38.76</v>
       </c>
       <c r="H220" s="12">
         <f t="shared" si="33"/>
-        <v>123794.99999999999</v>
+        <v>122094</v>
       </c>
       <c r="I220" s="29">
-        <v>45750</v>
+        <v>45762</v>
       </c>
       <c r="J220" s="25">
-        <v>45757</v>
+        <v>45771</v>
       </c>
       <c r="K220" s="9" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="L220" s="29">
-        <v>45787</v>
+        <v>45899</v>
       </c>
       <c r="M220" s="13">
         <v>0.02</v>
       </c>
       <c r="N220" s="11">
         <f t="shared" si="34"/>
-        <v>2475.8999999999996</v>
-      </c>
-      <c r="O220" s="49">
+        <v>2441.88</v>
+      </c>
+      <c r="O220" s="40">
         <f t="shared" si="35"/>
-        <v>495.17999999999995</v>
-      </c>
-      <c r="P220" s="49">
+        <v>488.37600000000003</v>
+      </c>
+      <c r="P220" s="40">
         <f t="shared" si="36"/>
-        <v>1980.7199999999998</v>
+        <v>1953.5040000000001</v>
       </c>
     </row>
     <row r="221" spans="1:16" x14ac:dyDescent="0.2">
@@ -13118,29 +13098,29 @@
         <v>14</v>
       </c>
       <c r="B221" s="16">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D221" s="9" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="E221" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F221" s="10">
-        <v>3150</v>
+        <v>2520</v>
       </c>
       <c r="G221" s="11">
         <v>38.76</v>
       </c>
       <c r="H221" s="12">
         <f t="shared" si="33"/>
-        <v>122094</v>
+        <v>97675.199999999997</v>
       </c>
       <c r="I221" s="29">
-        <v>45762</v>
+        <v>45763</v>
       </c>
       <c r="J221" s="25">
         <v>45771</v>
@@ -13156,15 +13136,15 @@
       </c>
       <c r="N221" s="11">
         <f t="shared" si="34"/>
-        <v>2441.88</v>
-      </c>
-      <c r="O221" s="49">
+        <v>1953.5039999999999</v>
+      </c>
+      <c r="O221" s="40">
         <f t="shared" si="35"/>
-        <v>488.37600000000003</v>
-      </c>
-      <c r="P221" s="49">
+        <v>390.70080000000002</v>
+      </c>
+      <c r="P221" s="40">
         <f t="shared" si="36"/>
-        <v>1953.5040000000001</v>
+        <v>1562.8032000000001</v>
       </c>
     </row>
     <row r="222" spans="1:16" x14ac:dyDescent="0.2">
@@ -13172,13 +13152,13 @@
         <v>14</v>
       </c>
       <c r="B222" s="16">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C222" s="9" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E222" s="9" t="s">
         <v>20</v>
@@ -13194,10 +13174,10 @@
         <v>97675.199999999997</v>
       </c>
       <c r="I222" s="29">
-        <v>45763</v>
+        <v>45784</v>
       </c>
       <c r="J222" s="25">
-        <v>45771</v>
+        <v>45789</v>
       </c>
       <c r="K222" s="9" t="s">
         <v>18</v>
@@ -13212,11 +13192,11 @@
         <f t="shared" si="34"/>
         <v>1953.5039999999999</v>
       </c>
-      <c r="O222" s="49">
+      <c r="O222" s="40">
         <f t="shared" si="35"/>
         <v>390.70080000000002</v>
       </c>
-      <c r="P222" s="49">
+      <c r="P222" s="40">
         <f t="shared" si="36"/>
         <v>1562.8032000000001</v>
       </c>
@@ -13226,53 +13206,53 @@
         <v>14</v>
       </c>
       <c r="B223" s="16">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C223" s="9" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F223" s="10">
-        <v>2520</v>
+        <v>1800</v>
       </c>
       <c r="G223" s="11">
-        <v>38.76</v>
+        <v>38</v>
       </c>
       <c r="H223" s="12">
-        <f t="shared" si="33"/>
-        <v>97675.199999999997</v>
+        <f t="shared" si="20"/>
+        <v>68400</v>
       </c>
       <c r="I223" s="29">
-        <v>45784</v>
+        <v>45811</v>
       </c>
       <c r="J223" s="25">
-        <v>45789</v>
+        <v>45821</v>
       </c>
       <c r="K223" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L223" s="29">
-        <v>45899</v>
+        <v>45960</v>
       </c>
       <c r="M223" s="13">
         <v>0.02</v>
       </c>
       <c r="N223" s="11">
-        <f t="shared" si="34"/>
-        <v>1953.5039999999999</v>
-      </c>
-      <c r="O223" s="49">
-        <f t="shared" si="35"/>
-        <v>390.70080000000002</v>
-      </c>
-      <c r="P223" s="49">
-        <f t="shared" si="36"/>
-        <v>1562.8032000000001</v>
+        <f t="shared" ref="N223" si="37">M223*H223</f>
+        <v>1368</v>
+      </c>
+      <c r="O223" s="11">
+        <f t="shared" ref="O223" si="38">0.2*N223</f>
+        <v>273.60000000000002</v>
+      </c>
+      <c r="P223" s="40">
+        <f t="shared" ref="P223" si="39">0.8*N223</f>
+        <v>1094.4000000000001</v>
       </c>
     </row>
     <row r="224" spans="1:16" x14ac:dyDescent="0.2">
@@ -13280,32 +13260,32 @@
         <v>14</v>
       </c>
       <c r="B224" s="16">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C224" s="9" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="D224" s="9" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="E224" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F224" s="10">
-        <v>1800</v>
+        <v>2520</v>
       </c>
       <c r="G224" s="11">
-        <v>38</v>
+        <v>38.76</v>
       </c>
       <c r="H224" s="12">
         <f t="shared" si="20"/>
-        <v>68400</v>
+        <v>97675.199999999997</v>
       </c>
       <c r="I224" s="29">
         <v>45811</v>
       </c>
       <c r="J224" s="25">
-        <v>45821</v>
+        <v>45813</v>
       </c>
       <c r="K224" s="9" t="s">
         <v>18</v>
@@ -13317,16 +13297,16 @@
         <v>0.02</v>
       </c>
       <c r="N224" s="11">
-        <f t="shared" ref="N224" si="37">M224*H224</f>
-        <v>1368</v>
+        <f t="shared" ref="N224:N228" si="40">M224*H224</f>
+        <v>1953.5039999999999</v>
       </c>
       <c r="O224" s="11">
-        <f t="shared" ref="O224" si="38">0.2*N224</f>
-        <v>273.60000000000002</v>
-      </c>
-      <c r="P224" s="49">
-        <f t="shared" ref="P224" si="39">0.8*N224</f>
-        <v>1094.4000000000001</v>
+        <f t="shared" ref="O224:O228" si="41">0.2*N224</f>
+        <v>390.70080000000002</v>
+      </c>
+      <c r="P224" s="40">
+        <f t="shared" ref="P224:P228" si="42">0.8*N224</f>
+        <v>1562.8032000000001</v>
       </c>
     </row>
     <row r="225" spans="1:16" x14ac:dyDescent="0.2">
@@ -13334,32 +13314,32 @@
         <v>14</v>
       </c>
       <c r="B225" s="16">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C225" s="9" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="D225" s="9" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="E225" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F225" s="10">
-        <v>2520</v>
+        <v>1800</v>
       </c>
       <c r="G225" s="11">
-        <v>38.76</v>
+        <v>38</v>
       </c>
       <c r="H225" s="12">
         <f t="shared" si="20"/>
-        <v>97675.199999999997</v>
+        <v>68400</v>
       </c>
       <c r="I225" s="29">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="J225" s="25">
-        <v>45813</v>
+        <v>45821</v>
       </c>
       <c r="K225" s="9" t="s">
         <v>18</v>
@@ -13371,16 +13351,16 @@
         <v>0.02</v>
       </c>
       <c r="N225" s="11">
-        <f t="shared" ref="N225:N229" si="40">M225*H225</f>
-        <v>1953.5039999999999</v>
+        <f t="shared" si="40"/>
+        <v>1368</v>
       </c>
       <c r="O225" s="11">
-        <f t="shared" ref="O225:O229" si="41">0.2*N225</f>
-        <v>390.70080000000002</v>
-      </c>
-      <c r="P225" s="49">
-        <f t="shared" ref="P225:P229" si="42">0.8*N225</f>
-        <v>1562.8032000000001</v>
+        <f t="shared" si="41"/>
+        <v>273.60000000000002</v>
+      </c>
+      <c r="P225" s="40">
+        <f t="shared" si="42"/>
+        <v>1094.4000000000001</v>
       </c>
     </row>
     <row r="226" spans="1:16" x14ac:dyDescent="0.2">
@@ -13388,7 +13368,7 @@
         <v>14</v>
       </c>
       <c r="B226" s="16">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C226" s="9" t="s">
         <v>79</v>
@@ -13400,17 +13380,17 @@
         <v>21</v>
       </c>
       <c r="F226" s="10">
-        <v>1800</v>
+        <v>720</v>
       </c>
       <c r="G226" s="11">
         <v>38</v>
       </c>
       <c r="H226" s="12">
         <f t="shared" si="20"/>
-        <v>68400</v>
+        <v>27360</v>
       </c>
       <c r="I226" s="29">
-        <v>45812</v>
+        <v>45818</v>
       </c>
       <c r="J226" s="25">
         <v>45821</v>
@@ -13426,15 +13406,15 @@
       </c>
       <c r="N226" s="11">
         <f t="shared" si="40"/>
-        <v>1368</v>
+        <v>547.20000000000005</v>
       </c>
       <c r="O226" s="11">
         <f t="shared" si="41"/>
-        <v>273.60000000000002</v>
-      </c>
-      <c r="P226" s="49">
+        <v>109.44000000000001</v>
+      </c>
+      <c r="P226" s="40">
         <f t="shared" si="42"/>
-        <v>1094.4000000000001</v>
+        <v>437.76000000000005</v>
       </c>
     </row>
     <row r="227" spans="1:16" x14ac:dyDescent="0.2">
@@ -13442,32 +13422,32 @@
         <v>14</v>
       </c>
       <c r="B227" s="16">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C227" s="9" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D227" s="9" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>21</v>
       </c>
       <c r="F227" s="10">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="G227" s="11">
         <v>38</v>
       </c>
       <c r="H227" s="12">
         <f t="shared" si="20"/>
-        <v>27360</v>
+        <v>41040</v>
       </c>
       <c r="I227" s="29">
-        <v>45818</v>
-      </c>
-      <c r="J227" s="25">
-        <v>45821</v>
+        <v>45858</v>
+      </c>
+      <c r="J227" s="29">
+        <v>45862</v>
       </c>
       <c r="K227" s="9" t="s">
         <v>18</v>
@@ -13480,15 +13460,15 @@
       </c>
       <c r="N227" s="11">
         <f t="shared" si="40"/>
-        <v>547.20000000000005</v>
-      </c>
-      <c r="O227" s="11">
+        <v>820.80000000000007</v>
+      </c>
+      <c r="O227" s="40">
         <f t="shared" si="41"/>
-        <v>109.44000000000001</v>
-      </c>
-      <c r="P227" s="49">
+        <v>164.16000000000003</v>
+      </c>
+      <c r="P227" s="40">
         <f t="shared" si="42"/>
-        <v>437.76000000000005</v>
+        <v>656.6400000000001</v>
       </c>
     </row>
     <row r="228" spans="1:16" x14ac:dyDescent="0.2">
@@ -13505,22 +13485,22 @@
         <v>94</v>
       </c>
       <c r="E228" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F228" s="10">
-        <v>1080</v>
+        <v>1715</v>
       </c>
       <c r="G228" s="11">
-        <v>38</v>
+        <v>38.76</v>
       </c>
       <c r="H228" s="12">
         <f t="shared" si="20"/>
-        <v>41040</v>
+        <v>66473.399999999994</v>
       </c>
       <c r="I228" s="29">
         <v>45858</v>
       </c>
-      <c r="J228" s="29">
+      <c r="J228" s="25">
         <v>45862</v>
       </c>
       <c r="K228" s="9" t="s">
@@ -13534,15 +13514,15 @@
       </c>
       <c r="N228" s="11">
         <f t="shared" si="40"/>
-        <v>820.80000000000007</v>
-      </c>
-      <c r="O228" s="49">
+        <v>1329.4679999999998</v>
+      </c>
+      <c r="O228" s="40">
         <f t="shared" si="41"/>
-        <v>164.16000000000003</v>
-      </c>
-      <c r="P228" s="49">
+        <v>265.89359999999999</v>
+      </c>
+      <c r="P228" s="40">
         <f t="shared" si="42"/>
-        <v>656.6400000000001</v>
+        <v>1063.5744</v>
       </c>
     </row>
     <row r="229" spans="1:16" x14ac:dyDescent="0.2">
@@ -13562,14 +13542,14 @@
         <v>20</v>
       </c>
       <c r="F229" s="10">
-        <v>1715</v>
+        <v>805</v>
       </c>
       <c r="G229" s="11">
         <v>38.76</v>
       </c>
       <c r="H229" s="12">
         <f t="shared" si="20"/>
-        <v>66473.399999999994</v>
+        <v>31201.8</v>
       </c>
       <c r="I229" s="29">
         <v>45858</v>
@@ -13587,16 +13567,16 @@
         <v>0.02</v>
       </c>
       <c r="N229" s="11">
-        <f t="shared" si="40"/>
-        <v>1329.4679999999998</v>
-      </c>
-      <c r="O229" s="49">
-        <f t="shared" si="41"/>
-        <v>265.89359999999999</v>
-      </c>
-      <c r="P229" s="49">
-        <f t="shared" si="42"/>
-        <v>1063.5744</v>
+        <f>M229*H229</f>
+        <v>624.03599999999994</v>
+      </c>
+      <c r="O229" s="40">
+        <f t="shared" ref="O229" si="43">0.2*N229</f>
+        <v>124.80719999999999</v>
+      </c>
+      <c r="P229" s="40">
+        <f t="shared" ref="P229" si="44">0.8*N229</f>
+        <v>499.22879999999998</v>
       </c>
     </row>
     <row r="230" spans="1:16" x14ac:dyDescent="0.2">
@@ -13604,53 +13584,53 @@
         <v>14</v>
       </c>
       <c r="B230" s="16">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C230" s="9" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D230" s="9" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E230" s="9" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F230" s="10">
-        <v>805</v>
+        <v>2160</v>
       </c>
       <c r="G230" s="11">
-        <v>38.76</v>
+        <v>28.6</v>
       </c>
       <c r="H230" s="12">
         <f t="shared" si="20"/>
-        <v>31201.8</v>
+        <v>61776</v>
       </c>
       <c r="I230" s="29">
-        <v>45858</v>
+        <v>45870</v>
       </c>
       <c r="J230" s="25">
-        <v>45862</v>
+        <v>45880</v>
       </c>
       <c r="K230" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L230" s="29">
-        <v>45960</v>
+        <v>46142</v>
       </c>
       <c r="M230" s="13">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N230" s="11">
-        <f>M230*H230</f>
-        <v>624.03599999999994</v>
-      </c>
-      <c r="O230" s="49">
-        <f t="shared" ref="O230" si="43">0.2*N230</f>
-        <v>124.80719999999999</v>
-      </c>
-      <c r="P230" s="49">
-        <f t="shared" ref="P230" si="44">0.8*N230</f>
-        <v>499.22879999999998</v>
+        <f t="shared" ref="N230:N239" si="45">M230*H230</f>
+        <v>926.64</v>
+      </c>
+      <c r="O230" s="11">
+        <f t="shared" ref="O230:O239" si="46">0.2*N230</f>
+        <v>185.328</v>
+      </c>
+      <c r="P230" s="11">
+        <f t="shared" ref="P230:P239" si="47">0.8*N230</f>
+        <v>741.31200000000001</v>
       </c>
     </row>
     <row r="231" spans="1:16" x14ac:dyDescent="0.2">
@@ -13658,13 +13638,13 @@
         <v>14</v>
       </c>
       <c r="B231" s="16">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C231" s="9" t="s">
-        <v>82</v>
+        <v>40</v>
       </c>
       <c r="D231" s="9" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="E231" s="9" t="s">
         <v>87</v>
@@ -13680,10 +13660,10 @@
         <v>61776</v>
       </c>
       <c r="I231" s="29">
-        <v>45870</v>
+        <v>45876</v>
       </c>
       <c r="J231" s="25">
-        <v>45880</v>
+        <v>45884</v>
       </c>
       <c r="K231" s="9" t="s">
         <v>18</v>
@@ -13695,15 +13675,15 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N231" s="11">
-        <f t="shared" ref="N231:N240" si="45">M231*H231</f>
+        <f t="shared" si="45"/>
         <v>926.64</v>
       </c>
       <c r="O231" s="11">
-        <f t="shared" ref="O231:O240" si="46">0.2*N231</f>
+        <f t="shared" si="46"/>
         <v>185.328</v>
       </c>
       <c r="P231" s="11">
-        <f t="shared" ref="P231:P240" si="47">0.8*N231</f>
+        <f t="shared" si="47"/>
         <v>741.31200000000001</v>
       </c>
     </row>
@@ -13712,26 +13692,26 @@
         <v>14</v>
       </c>
       <c r="B232" s="16">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C232" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D232" s="9" t="s">
-        <v>19</v>
+        <v>102</v>
       </c>
       <c r="E232" s="9" t="s">
         <v>87</v>
       </c>
       <c r="F232" s="10">
-        <v>2160</v>
+        <v>1080</v>
       </c>
       <c r="G232" s="11">
         <v>28.6</v>
       </c>
       <c r="H232" s="12">
-        <f t="shared" si="20"/>
-        <v>61776</v>
+        <f t="shared" ref="H232:H300" si="48">F232*G232</f>
+        <v>30888</v>
       </c>
       <c r="I232" s="29">
         <v>45876</v>
@@ -13750,15 +13730,15 @@
       </c>
       <c r="N232" s="11">
         <f t="shared" si="45"/>
-        <v>926.64</v>
+        <v>463.32</v>
       </c>
       <c r="O232" s="11">
         <f t="shared" si="46"/>
-        <v>185.328</v>
+        <v>92.664000000000001</v>
       </c>
       <c r="P232" s="11">
         <f t="shared" si="47"/>
-        <v>741.31200000000001</v>
+        <v>370.65600000000001</v>
       </c>
     </row>
     <row r="233" spans="1:16" x14ac:dyDescent="0.2">
@@ -13766,26 +13746,26 @@
         <v>14</v>
       </c>
       <c r="B233" s="16">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C233" s="9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D233" s="9" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="E233" s="9" t="s">
         <v>87</v>
       </c>
       <c r="F233" s="10">
-        <v>1080</v>
+        <v>2160</v>
       </c>
       <c r="G233" s="11">
         <v>28.6</v>
       </c>
       <c r="H233" s="12">
-        <f t="shared" ref="H233:H305" si="48">F233*G233</f>
-        <v>30888</v>
+        <f t="shared" si="48"/>
+        <v>61776</v>
       </c>
       <c r="I233" s="29">
         <v>45876</v>
@@ -13804,137 +13784,137 @@
       </c>
       <c r="N233" s="11">
         <f t="shared" si="45"/>
+        <v>926.64</v>
+      </c>
+      <c r="O233" s="40">
+        <f t="shared" si="46"/>
+        <v>185.328</v>
+      </c>
+      <c r="P233" s="40">
+        <f t="shared" si="47"/>
+        <v>741.31200000000001</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A234" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B234" s="16">
+        <v>175</v>
+      </c>
+      <c r="C234" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D234" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="E234" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F234" s="10">
+        <v>1080</v>
+      </c>
+      <c r="G234" s="11">
+        <v>28.6</v>
+      </c>
+      <c r="H234" s="12">
+        <f t="shared" si="48"/>
+        <v>30888</v>
+      </c>
+      <c r="I234" s="29">
+        <v>45876</v>
+      </c>
+      <c r="J234" s="25">
+        <v>45884</v>
+      </c>
+      <c r="K234" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L234" s="29">
+        <v>46142</v>
+      </c>
+      <c r="M234" s="13">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N234" s="11">
+        <f t="shared" si="45"/>
         <v>463.32</v>
       </c>
-      <c r="O233" s="11">
+      <c r="O234" s="11">
         <f t="shared" si="46"/>
         <v>92.664000000000001</v>
       </c>
-      <c r="P233" s="11">
+      <c r="P234" s="11">
         <f t="shared" si="47"/>
         <v>370.65600000000001</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A234" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B234" s="16">
-        <v>174</v>
-      </c>
-      <c r="C234" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D234" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E234" s="9" t="s">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A235" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B235" s="16">
+        <v>176</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="E235" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F234" s="10">
+      <c r="F235" s="10">
         <v>2160</v>
       </c>
-      <c r="G234" s="11">
+      <c r="G235" s="11">
         <v>28.6</v>
       </c>
-      <c r="H234" s="12">
+      <c r="H235" s="12">
         <f t="shared" si="48"/>
         <v>61776</v>
       </c>
-      <c r="I234" s="29">
+      <c r="I235" s="29">
         <v>45876</v>
       </c>
-      <c r="J234" s="25">
+      <c r="J235" s="25">
         <v>45884</v>
       </c>
-      <c r="K234" s="9" t="s">
+      <c r="K235" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L234" s="29">
+      <c r="L235" s="29">
         <v>46142</v>
       </c>
-      <c r="M234" s="13">
+      <c r="M235" s="13">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N234" s="11">
+      <c r="N235" s="11">
         <f t="shared" si="45"/>
         <v>926.64</v>
       </c>
-      <c r="O234" s="49">
+      <c r="O235" s="11">
         <f t="shared" si="46"/>
         <v>185.328</v>
       </c>
-      <c r="P234" s="49">
+      <c r="P235" s="11">
         <f t="shared" si="47"/>
         <v>741.31200000000001</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A235" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B235" s="16">
-        <v>175</v>
-      </c>
-      <c r="C235" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D235" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E235" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="F235" s="10">
-        <v>1080</v>
-      </c>
-      <c r="G235" s="11">
-        <v>28.6</v>
-      </c>
-      <c r="H235" s="12">
-        <f t="shared" si="48"/>
-        <v>30888</v>
-      </c>
-      <c r="I235" s="29">
-        <v>45876</v>
-      </c>
-      <c r="J235" s="25">
-        <v>45884</v>
-      </c>
-      <c r="K235" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L235" s="29">
-        <v>46142</v>
-      </c>
-      <c r="M235" s="13">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N235" s="11">
-        <f t="shared" si="45"/>
-        <v>463.32</v>
-      </c>
-      <c r="O235" s="11">
-        <f t="shared" si="46"/>
-        <v>92.664000000000001</v>
-      </c>
-      <c r="P235" s="11">
-        <f t="shared" si="47"/>
-        <v>370.65600000000001</v>
-      </c>
-    </row>
     <row r="236" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A236" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B236" s="16">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C236" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D236" s="9" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="E236" s="9" t="s">
         <v>87</v>
@@ -13982,13 +13962,13 @@
         <v>14</v>
       </c>
       <c r="B237" s="16">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C237" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D237" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E237" s="9" t="s">
         <v>87</v>
@@ -14036,26 +14016,26 @@
         <v>14</v>
       </c>
       <c r="B238" s="16">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C238" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D238" s="9" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E238" s="9" t="s">
         <v>87</v>
       </c>
       <c r="F238" s="10">
-        <v>2160</v>
+        <v>1080</v>
       </c>
       <c r="G238" s="11">
         <v>28.6</v>
       </c>
       <c r="H238" s="12">
         <f t="shared" si="48"/>
-        <v>61776</v>
+        <v>30888</v>
       </c>
       <c r="I238" s="29">
         <v>45876</v>
@@ -14074,15 +14054,15 @@
       </c>
       <c r="N238" s="11">
         <f t="shared" si="45"/>
-        <v>926.64</v>
+        <v>463.32</v>
       </c>
       <c r="O238" s="11">
         <f t="shared" si="46"/>
-        <v>185.328</v>
+        <v>92.664000000000001</v>
       </c>
       <c r="P238" s="11">
         <f t="shared" si="47"/>
-        <v>741.31200000000001</v>
+        <v>370.65600000000001</v>
       </c>
     </row>
     <row r="239" spans="1:16" x14ac:dyDescent="0.2">
@@ -14090,13 +14070,13 @@
         <v>14</v>
       </c>
       <c r="B239" s="16">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C239" s="9" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D239" s="9" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E239" s="9" t="s">
         <v>87</v>
@@ -14112,10 +14092,10 @@
         <v>30888</v>
       </c>
       <c r="I239" s="29">
-        <v>45876</v>
+        <v>45884</v>
       </c>
       <c r="J239" s="25">
-        <v>45884</v>
+        <v>45911</v>
       </c>
       <c r="K239" s="9" t="s">
         <v>18</v>
@@ -14130,7 +14110,7 @@
         <f t="shared" si="45"/>
         <v>463.32</v>
       </c>
-      <c r="O239" s="11">
+      <c r="O239" s="40">
         <f t="shared" si="46"/>
         <v>92.664000000000001</v>
       </c>
@@ -14144,32 +14124,32 @@
         <v>14</v>
       </c>
       <c r="B240" s="16">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C240" s="9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D240" s="9" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="E240" s="9" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="F240" s="10">
-        <v>1080</v>
+        <v>2050</v>
       </c>
       <c r="G240" s="11">
-        <v>28.6</v>
+        <v>25.48</v>
       </c>
       <c r="H240" s="12">
         <f t="shared" si="48"/>
-        <v>30888</v>
+        <v>52234</v>
       </c>
       <c r="I240" s="29">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="J240" s="25">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="K240" s="9" t="s">
         <v>18</v>
@@ -14178,19 +14158,20 @@
         <v>46142</v>
       </c>
       <c r="M240" s="13">
+        <f>VLOOKUP(E240,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N240" s="11">
-        <f t="shared" si="45"/>
-        <v>463.32</v>
-      </c>
-      <c r="O240" s="49">
-        <f t="shared" si="46"/>
-        <v>92.664000000000001</v>
+        <f t="shared" ref="N240:N251" si="49">M240*H240</f>
+        <v>783.51</v>
+      </c>
+      <c r="O240" s="40">
+        <f t="shared" ref="O240:O251" si="50">0.2*N240</f>
+        <v>156.702</v>
       </c>
       <c r="P240" s="11">
-        <f t="shared" si="47"/>
-        <v>370.65600000000001</v>
+        <f t="shared" ref="P240:P251" si="51">0.8*N240</f>
+        <v>626.80799999999999</v>
       </c>
     </row>
     <row r="241" spans="1:16" x14ac:dyDescent="0.2">
@@ -14207,45 +14188,45 @@
         <v>63</v>
       </c>
       <c r="E241" s="9" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="F241" s="10">
-        <v>2050</v>
+        <v>2880</v>
       </c>
       <c r="G241" s="11">
         <v>25.48</v>
       </c>
       <c r="H241" s="12">
         <f t="shared" si="48"/>
-        <v>52234</v>
+        <v>73382.399999999994</v>
       </c>
       <c r="I241" s="29">
         <v>45896</v>
       </c>
       <c r="J241" s="25">
-        <v>45912</v>
+        <v>45917</v>
       </c>
       <c r="K241" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L241" s="29">
-        <v>46142</v>
+        <v>45777</v>
       </c>
       <c r="M241" s="13">
         <f>VLOOKUP(E241,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N241" s="11">
-        <f t="shared" ref="N241:N253" si="49">M241*H241</f>
-        <v>783.51</v>
-      </c>
-      <c r="O241" s="49">
-        <f t="shared" ref="O241:O253" si="50">0.2*N241</f>
-        <v>156.702</v>
+        <f t="shared" si="49"/>
+        <v>1100.7359999999999</v>
+      </c>
+      <c r="O241" s="40">
+        <f t="shared" si="50"/>
+        <v>220.1472</v>
       </c>
       <c r="P241" s="11">
-        <f t="shared" ref="P241:P253" si="51">0.8*N241</f>
-        <v>626.80799999999999</v>
+        <f t="shared" si="51"/>
+        <v>880.58879999999999</v>
       </c>
     </row>
     <row r="242" spans="1:16" x14ac:dyDescent="0.2">
@@ -14262,17 +14243,17 @@
         <v>63</v>
       </c>
       <c r="E242" s="9" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F242" s="10">
-        <v>2880</v>
+        <v>4900</v>
       </c>
       <c r="G242" s="11">
         <v>25.48</v>
       </c>
       <c r="H242" s="12">
         <f t="shared" si="48"/>
-        <v>73382.399999999994</v>
+        <v>124852</v>
       </c>
       <c r="I242" s="29">
         <v>45896</v>
@@ -14284,7 +14265,7 @@
         <v>18</v>
       </c>
       <c r="L242" s="29">
-        <v>45777</v>
+        <v>46142</v>
       </c>
       <c r="M242" s="13">
         <f>VLOOKUP(E242,tabela_produto[],2,FALSE)</f>
@@ -14292,15 +14273,15 @@
       </c>
       <c r="N242" s="11">
         <f t="shared" si="49"/>
-        <v>1100.7359999999999</v>
-      </c>
-      <c r="O242" s="49">
+        <v>1872.78</v>
+      </c>
+      <c r="O242" s="40">
         <f t="shared" si="50"/>
-        <v>220.1472</v>
+        <v>374.55600000000004</v>
       </c>
       <c r="P242" s="11">
         <f t="shared" si="51"/>
-        <v>880.58879999999999</v>
+        <v>1498.2240000000002</v>
       </c>
     </row>
     <row r="243" spans="1:16" x14ac:dyDescent="0.2">
@@ -14308,32 +14289,32 @@
         <v>14</v>
       </c>
       <c r="B243" s="16">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C243" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D243" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E243" s="9" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="F243" s="10">
-        <v>4900</v>
+        <v>7700</v>
       </c>
       <c r="G243" s="11">
         <v>25.48</v>
       </c>
       <c r="H243" s="12">
         <f t="shared" si="48"/>
-        <v>124852</v>
+        <v>196196</v>
       </c>
       <c r="I243" s="29">
         <v>45896</v>
       </c>
       <c r="J243" s="25">
-        <v>45917</v>
+        <v>45905</v>
       </c>
       <c r="K243" s="9" t="s">
         <v>18</v>
@@ -14347,15 +14328,15 @@
       </c>
       <c r="N243" s="11">
         <f t="shared" si="49"/>
-        <v>1872.78</v>
-      </c>
-      <c r="O243" s="49">
+        <v>2942.94</v>
+      </c>
+      <c r="O243" s="40">
         <f t="shared" si="50"/>
-        <v>374.55600000000004</v>
+        <v>588.58800000000008</v>
       </c>
       <c r="P243" s="11">
         <f t="shared" si="51"/>
-        <v>1498.2240000000002</v>
+        <v>2354.3520000000003</v>
       </c>
     </row>
     <row r="244" spans="1:16" x14ac:dyDescent="0.2">
@@ -14372,23 +14353,23 @@
         <v>61</v>
       </c>
       <c r="E244" s="9" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="F244" s="10">
-        <v>7700</v>
+        <v>3780</v>
       </c>
       <c r="G244" s="11">
         <v>25.48</v>
       </c>
       <c r="H244" s="12">
         <f t="shared" si="48"/>
-        <v>196196</v>
+        <v>96314.400000000009</v>
       </c>
       <c r="I244" s="29">
         <v>45896</v>
       </c>
       <c r="J244" s="25">
-        <v>45905</v>
+        <v>45918</v>
       </c>
       <c r="K244" s="9" t="s">
         <v>18</v>
@@ -14402,15 +14383,15 @@
       </c>
       <c r="N244" s="11">
         <f t="shared" si="49"/>
-        <v>2942.94</v>
-      </c>
-      <c r="O244" s="49">
+        <v>1444.7160000000001</v>
+      </c>
+      <c r="O244" s="40">
         <f t="shared" si="50"/>
-        <v>588.58800000000008</v>
+        <v>288.94320000000005</v>
       </c>
       <c r="P244" s="11">
         <f t="shared" si="51"/>
-        <v>2354.3520000000003</v>
+        <v>1155.7728000000002</v>
       </c>
     </row>
     <row r="245" spans="1:16" x14ac:dyDescent="0.2">
@@ -14418,32 +14399,32 @@
         <v>14</v>
       </c>
       <c r="B245" s="16">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C245" s="9" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D245" s="9" t="s">
-        <v>61</v>
+        <v>15</v>
       </c>
       <c r="E245" s="9" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="F245" s="10">
-        <v>3780</v>
+        <v>1890</v>
       </c>
       <c r="G245" s="11">
         <v>25.48</v>
       </c>
       <c r="H245" s="12">
         <f t="shared" si="48"/>
-        <v>96314.400000000009</v>
+        <v>48157.200000000004</v>
       </c>
       <c r="I245" s="29">
-        <v>45896</v>
+        <v>45897</v>
       </c>
       <c r="J245" s="25">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="K245" s="9" t="s">
         <v>18</v>
@@ -14457,68 +14438,70 @@
       </c>
       <c r="N245" s="11">
         <f t="shared" si="49"/>
-        <v>1444.7160000000001</v>
-      </c>
-      <c r="O245" s="49">
+        <v>722.35800000000006</v>
+      </c>
+      <c r="O245" s="40">
         <f t="shared" si="50"/>
-        <v>288.94320000000005</v>
+        <v>144.47160000000002</v>
       </c>
       <c r="P245" s="11">
         <f t="shared" si="51"/>
-        <v>1155.7728000000002</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" s="47" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B246" s="34">
-        <v>184</v>
-      </c>
-      <c r="C246" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="D246" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E246" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F246" s="35">
-        <v>3920</v>
-      </c>
-      <c r="G246" s="36">
-        <v>25.48</v>
-      </c>
-      <c r="H246" s="37">
+        <v>577.88640000000009</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A246" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B246" s="16">
+        <v>187</v>
+      </c>
+      <c r="C246" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D246" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E246" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="F246" s="10">
+        <v>1080</v>
+      </c>
+      <c r="G246" s="11">
+        <v>28.6</v>
+      </c>
+      <c r="H246" s="12">
         <f t="shared" si="48"/>
-        <v>99881.600000000006</v>
-      </c>
-      <c r="I246" s="38">
-        <v>45896</v>
-      </c>
-      <c r="J246" s="39"/>
-      <c r="K246" s="33" t="s">
+        <v>30888</v>
+      </c>
+      <c r="I246" s="29">
+        <v>45905</v>
+      </c>
+      <c r="J246" s="25">
+        <v>45917</v>
+      </c>
+      <c r="K246" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L246" s="38">
+      <c r="L246" s="29">
         <v>46142</v>
       </c>
-      <c r="M246" s="40">
+      <c r="M246" s="13">
         <f>VLOOKUP(E246,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N246" s="36">
+      <c r="N246" s="11">
         <f t="shared" si="49"/>
-        <v>1498.2239999999999</v>
-      </c>
-      <c r="O246" s="36">
+        <v>463.32</v>
+      </c>
+      <c r="O246" s="40">
         <f t="shared" si="50"/>
-        <v>299.64479999999998</v>
-      </c>
-      <c r="P246" s="36">
+        <v>92.664000000000001</v>
+      </c>
+      <c r="P246" s="11">
         <f t="shared" si="51"/>
-        <v>1198.5791999999999</v>
+        <v>370.65600000000001</v>
       </c>
     </row>
     <row r="247" spans="1:16" x14ac:dyDescent="0.2">
@@ -14526,32 +14509,32 @@
         <v>14</v>
       </c>
       <c r="B247" s="16">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C247" s="9" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D247" s="9" t="s">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="E247" s="9" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="F247" s="10">
-        <v>1890</v>
+        <v>1260</v>
       </c>
       <c r="G247" s="11">
         <v>25.48</v>
       </c>
       <c r="H247" s="12">
         <f t="shared" si="48"/>
-        <v>48157.200000000004</v>
+        <v>32104.799999999999</v>
       </c>
       <c r="I247" s="29">
-        <v>45897</v>
+        <v>45911</v>
       </c>
       <c r="J247" s="25">
-        <v>45919</v>
+        <v>45925</v>
       </c>
       <c r="K247" s="9" t="s">
         <v>18</v>
@@ -14565,15 +14548,15 @@
       </c>
       <c r="N247" s="11">
         <f t="shared" si="49"/>
-        <v>722.35800000000006</v>
-      </c>
-      <c r="O247" s="49">
+        <v>481.57199999999995</v>
+      </c>
+      <c r="O247" s="40">
         <f t="shared" si="50"/>
-        <v>144.47160000000002</v>
+        <v>96.314399999999992</v>
       </c>
       <c r="P247" s="11">
         <f t="shared" si="51"/>
-        <v>577.88640000000009</v>
+        <v>385.25759999999997</v>
       </c>
     </row>
     <row r="248" spans="1:16" x14ac:dyDescent="0.2">
@@ -14581,32 +14564,32 @@
         <v>14</v>
       </c>
       <c r="B248" s="16">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C248" s="9" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="D248" s="9" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="E248" s="9" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="F248" s="10">
-        <v>1080</v>
+        <v>1260</v>
       </c>
       <c r="G248" s="11">
-        <v>28.6</v>
+        <v>25.48</v>
       </c>
       <c r="H248" s="12">
         <f t="shared" si="48"/>
-        <v>30888</v>
+        <v>32104.799999999999</v>
       </c>
       <c r="I248" s="29">
-        <v>45905</v>
+        <v>45915</v>
       </c>
       <c r="J248" s="25">
-        <v>45917</v>
+        <v>45925</v>
       </c>
       <c r="K248" s="9" t="s">
         <v>18</v>
@@ -14620,15 +14603,15 @@
       </c>
       <c r="N248" s="11">
         <f t="shared" si="49"/>
-        <v>463.32</v>
-      </c>
-      <c r="O248" s="49">
+        <v>481.57199999999995</v>
+      </c>
+      <c r="O248" s="40">
         <f t="shared" si="50"/>
-        <v>92.664000000000001</v>
+        <v>96.314399999999992</v>
       </c>
       <c r="P248" s="11">
         <f t="shared" si="51"/>
-        <v>370.65600000000001</v>
+        <v>385.25759999999997</v>
       </c>
     </row>
     <row r="249" spans="1:16" x14ac:dyDescent="0.2">
@@ -14636,29 +14619,29 @@
         <v>14</v>
       </c>
       <c r="B249" s="16">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C249" s="9" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D249" s="9" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="E249" s="9" t="s">
         <v>105</v>
       </c>
       <c r="F249" s="10">
-        <v>1260</v>
+        <v>1890</v>
       </c>
       <c r="G249" s="11">
         <v>25.48</v>
       </c>
       <c r="H249" s="12">
         <f t="shared" si="48"/>
-        <v>32104.799999999999</v>
+        <v>48157.200000000004</v>
       </c>
       <c r="I249" s="29">
-        <v>45911</v>
+        <v>45918</v>
       </c>
       <c r="J249" s="25">
         <v>45925</v>
@@ -14675,15 +14658,15 @@
       </c>
       <c r="N249" s="11">
         <f t="shared" si="49"/>
-        <v>481.57199999999995</v>
-      </c>
-      <c r="O249" s="49">
+        <v>722.35800000000006</v>
+      </c>
+      <c r="O249" s="40">
         <f t="shared" si="50"/>
-        <v>96.314399999999992</v>
+        <v>144.47160000000002</v>
       </c>
       <c r="P249" s="11">
         <f t="shared" si="51"/>
-        <v>385.25759999999997</v>
+        <v>577.88640000000009</v>
       </c>
     </row>
     <row r="250" spans="1:16" x14ac:dyDescent="0.2">
@@ -14691,29 +14674,29 @@
         <v>14</v>
       </c>
       <c r="B250" s="16">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C250" s="9" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D250" s="9" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="E250" s="9" t="s">
         <v>105</v>
       </c>
       <c r="F250" s="10">
-        <v>1260</v>
+        <v>2520</v>
       </c>
       <c r="G250" s="11">
         <v>25.48</v>
       </c>
       <c r="H250" s="12">
         <f t="shared" si="48"/>
-        <v>32104.799999999999</v>
+        <v>64209.599999999999</v>
       </c>
       <c r="I250" s="29">
-        <v>45915</v>
+        <v>45923</v>
       </c>
       <c r="J250" s="25">
         <v>45925</v>
@@ -14730,15 +14713,15 @@
       </c>
       <c r="N250" s="11">
         <f t="shared" si="49"/>
-        <v>481.57199999999995</v>
-      </c>
-      <c r="O250" s="49">
+        <v>963.14399999999989</v>
+      </c>
+      <c r="O250" s="40">
         <f t="shared" si="50"/>
-        <v>96.314399999999992</v>
+        <v>192.62879999999998</v>
       </c>
       <c r="P250" s="11">
         <f t="shared" si="51"/>
-        <v>385.25759999999997</v>
+        <v>770.51519999999994</v>
       </c>
     </row>
     <row r="251" spans="1:16" x14ac:dyDescent="0.2">
@@ -14746,29 +14729,29 @@
         <v>14</v>
       </c>
       <c r="B251" s="16">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C251" s="9" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D251" s="9" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>105</v>
       </c>
       <c r="F251" s="10">
-        <v>1890</v>
+        <v>5040</v>
       </c>
       <c r="G251" s="11">
         <v>25.48</v>
       </c>
       <c r="H251" s="12">
         <f t="shared" si="48"/>
-        <v>48157.200000000004</v>
+        <v>128419.2</v>
       </c>
       <c r="I251" s="29">
-        <v>45918</v>
+        <v>45923</v>
       </c>
       <c r="J251" s="25">
         <v>45925</v>
@@ -14785,15 +14768,15 @@
       </c>
       <c r="N251" s="11">
         <f t="shared" si="49"/>
-        <v>722.35800000000006</v>
-      </c>
-      <c r="O251" s="49">
+        <v>1926.2879999999998</v>
+      </c>
+      <c r="O251" s="40">
         <f t="shared" si="50"/>
-        <v>144.47160000000002</v>
+        <v>385.25759999999997</v>
       </c>
       <c r="P251" s="11">
         <f t="shared" si="51"/>
-        <v>577.88640000000009</v>
+        <v>1541.0303999999999</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.2">
@@ -14801,32 +14784,32 @@
         <v>14</v>
       </c>
       <c r="B252" s="16">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C252" s="9" t="s">
         <v>40</v>
       </c>
       <c r="D252" s="9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E252" s="9" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="F252" s="10">
-        <v>2520</v>
+        <v>3500</v>
       </c>
       <c r="G252" s="11">
         <v>25.48</v>
       </c>
       <c r="H252" s="12">
         <f t="shared" si="48"/>
-        <v>64209.599999999999</v>
+        <v>89180</v>
       </c>
       <c r="I252" s="29">
-        <v>45923</v>
+        <v>45939</v>
       </c>
       <c r="J252" s="25">
-        <v>45925</v>
+        <v>45954</v>
       </c>
       <c r="K252" s="9" t="s">
         <v>18</v>
@@ -14839,16 +14822,16 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N252" s="11">
-        <f t="shared" si="49"/>
-        <v>963.14399999999989</v>
-      </c>
-      <c r="O252" s="49">
-        <f t="shared" si="50"/>
-        <v>192.62879999999998</v>
+        <f t="shared" ref="N252" si="52">M252*H252</f>
+        <v>1337.7</v>
+      </c>
+      <c r="O252" s="40">
+        <f t="shared" ref="O252" si="53">0.2*N252</f>
+        <v>267.54000000000002</v>
       </c>
       <c r="P252" s="11">
-        <f t="shared" si="51"/>
-        <v>770.51519999999994</v>
+        <f t="shared" ref="P252" si="54">0.8*N252</f>
+        <v>1070.1600000000001</v>
       </c>
     </row>
     <row r="253" spans="1:16" x14ac:dyDescent="0.2">
@@ -14856,54 +14839,54 @@
         <v>14</v>
       </c>
       <c r="B253" s="16">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C253" s="9" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D253" s="9" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="E253" s="9" t="s">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="F253" s="10">
-        <v>5040</v>
+        <v>1260</v>
       </c>
       <c r="G253" s="11">
-        <v>25.48</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H253" s="12">
         <f t="shared" si="48"/>
-        <v>128419.2</v>
+        <v>48888</v>
       </c>
       <c r="I253" s="29">
-        <v>45923</v>
-      </c>
-      <c r="J253" s="25">
-        <v>45925</v>
+        <v>45945</v>
+      </c>
+      <c r="J253" s="29">
+        <v>45946</v>
       </c>
       <c r="K253" s="9" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="L253" s="29">
-        <v>46142</v>
+        <v>46096</v>
       </c>
       <c r="M253" s="13">
         <f>VLOOKUP(E253,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N253" s="11">
-        <f t="shared" si="49"/>
-        <v>1926.2879999999998</v>
-      </c>
-      <c r="O253" s="49">
-        <f t="shared" si="50"/>
-        <v>385.25759999999997</v>
-      </c>
-      <c r="P253" s="11">
-        <f t="shared" si="51"/>
-        <v>1541.0303999999999</v>
+        <f t="shared" ref="N253:N255" si="55">M253*H253</f>
+        <v>977.76</v>
+      </c>
+      <c r="O253" s="40">
+        <f t="shared" ref="O253:O255" si="56">0.2*N253</f>
+        <v>195.55200000000002</v>
+      </c>
+      <c r="P253" s="40">
+        <f t="shared" ref="P253:P255" si="57">0.8*N253</f>
+        <v>782.20800000000008</v>
       </c>
     </row>
     <row r="254" spans="1:16" x14ac:dyDescent="0.2">
@@ -14911,54 +14894,54 @@
         <v>14</v>
       </c>
       <c r="B254" s="16">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C254" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D254" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E254" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F254" s="10">
-        <v>3500</v>
+        <v>1260</v>
       </c>
       <c r="G254" s="11">
-        <v>25.48</v>
+        <v>38.799999999999997</v>
       </c>
       <c r="H254" s="12">
         <f t="shared" si="48"/>
-        <v>89180</v>
+        <v>48888</v>
       </c>
       <c r="I254" s="29">
-        <v>45939</v>
-      </c>
-      <c r="J254" s="25">
-        <v>45954</v>
+        <v>45945</v>
+      </c>
+      <c r="J254" s="29">
+        <v>45946</v>
       </c>
       <c r="K254" s="9" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="L254" s="29">
-        <v>46142</v>
+        <v>46096</v>
       </c>
       <c r="M254" s="13">
         <f>VLOOKUP(E254,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N254" s="11">
-        <f t="shared" ref="N254" si="52">M254*H254</f>
-        <v>1337.7</v>
-      </c>
-      <c r="O254" s="49">
-        <f t="shared" ref="O254" si="53">0.2*N254</f>
-        <v>267.54000000000002</v>
-      </c>
-      <c r="P254" s="11">
-        <f t="shared" ref="P254" si="54">0.8*N254</f>
-        <v>1070.1600000000001</v>
+        <f t="shared" si="55"/>
+        <v>977.76</v>
+      </c>
+      <c r="O254" s="40">
+        <f t="shared" si="56"/>
+        <v>195.55200000000002</v>
+      </c>
+      <c r="P254" s="40">
+        <f t="shared" si="57"/>
+        <v>782.20800000000008</v>
       </c>
     </row>
     <row r="255" spans="1:16" x14ac:dyDescent="0.2">
@@ -14966,54 +14949,54 @@
         <v>14</v>
       </c>
       <c r="B255" s="16">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C255" s="9" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D255" s="9" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E255" s="9" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F255" s="10">
-        <v>1260</v>
+        <v>1800</v>
       </c>
       <c r="G255" s="11">
-        <v>38.799999999999997</v>
+        <v>28.6</v>
       </c>
       <c r="H255" s="12">
         <f t="shared" si="48"/>
-        <v>48888</v>
+        <v>51480</v>
       </c>
       <c r="I255" s="29">
-        <v>45945</v>
-      </c>
-      <c r="J255" s="29">
-        <v>45946</v>
+        <v>45950</v>
+      </c>
+      <c r="J255" s="25">
+        <v>45957</v>
       </c>
       <c r="K255" s="9" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="L255" s="29">
-        <v>46096</v>
+        <v>46142</v>
       </c>
       <c r="M255" s="13">
         <f>VLOOKUP(E255,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N255" s="11">
-        <f t="shared" ref="N255:N257" si="55">M255*H255</f>
-        <v>977.76</v>
-      </c>
-      <c r="O255" s="49">
-        <f t="shared" ref="O255:O257" si="56">0.2*N255</f>
-        <v>195.55200000000002</v>
-      </c>
-      <c r="P255" s="49">
-        <f t="shared" ref="P255:P257" si="57">0.8*N255</f>
-        <v>782.20800000000008</v>
+        <f t="shared" si="55"/>
+        <v>772.19999999999993</v>
+      </c>
+      <c r="O255" s="40">
+        <f t="shared" si="56"/>
+        <v>154.44</v>
+      </c>
+      <c r="P255" s="11">
+        <f t="shared" si="57"/>
+        <v>617.76</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.2">
@@ -15021,13 +15004,13 @@
         <v>14</v>
       </c>
       <c r="B256" s="16">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C256" s="9" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="D256" s="9" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="E256" s="9" t="s">
         <v>20</v>
@@ -15036,39 +15019,39 @@
         <v>1260</v>
       </c>
       <c r="G256" s="11">
-        <v>38.799999999999997</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="H256" s="12">
         <f t="shared" si="48"/>
-        <v>48888</v>
+        <v>46960.200000000004</v>
       </c>
       <c r="I256" s="29">
-        <v>45945</v>
-      </c>
-      <c r="J256" s="29">
-        <v>45946</v>
+        <v>45957</v>
+      </c>
+      <c r="J256" s="25">
+        <v>45966</v>
       </c>
       <c r="K256" s="9" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="L256" s="29">
-        <v>46096</v>
+        <v>46081</v>
       </c>
       <c r="M256" s="13">
         <f>VLOOKUP(E256,tabela_produto[],2,FALSE)</f>
         <v>0.02</v>
       </c>
       <c r="N256" s="11">
-        <f t="shared" si="55"/>
-        <v>977.76</v>
-      </c>
-      <c r="O256" s="49">
-        <f t="shared" si="56"/>
-        <v>195.55200000000002</v>
-      </c>
-      <c r="P256" s="49">
-        <f t="shared" si="57"/>
-        <v>782.20800000000008</v>
+        <f t="shared" ref="N256:N262" si="58">M256*H256</f>
+        <v>939.20400000000006</v>
+      </c>
+      <c r="O256" s="40">
+        <f t="shared" ref="O256:O262" si="59">0.2*N256</f>
+        <v>187.84080000000003</v>
+      </c>
+      <c r="P256" s="40">
+        <f t="shared" ref="P256:P262" si="60">0.8*N256</f>
+        <v>751.36320000000012</v>
       </c>
     </row>
     <row r="257" spans="1:16" x14ac:dyDescent="0.2">
@@ -15076,54 +15059,54 @@
         <v>14</v>
       </c>
       <c r="B257" s="16">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C257" s="9" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D257" s="9" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E257" s="9" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="F257" s="10">
-        <v>1800</v>
+        <v>720</v>
       </c>
       <c r="G257" s="11">
-        <v>28.6</v>
+        <v>39.9</v>
       </c>
       <c r="H257" s="12">
         <f t="shared" si="48"/>
-        <v>51480</v>
+        <v>28728</v>
       </c>
       <c r="I257" s="29">
-        <v>45950</v>
+        <v>45958</v>
       </c>
       <c r="J257" s="25">
-        <v>45957</v>
+        <v>45966</v>
       </c>
       <c r="K257" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L257" s="29">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="M257" s="13">
         <f>VLOOKUP(E257,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N257" s="11">
-        <f t="shared" si="55"/>
-        <v>772.19999999999993</v>
-      </c>
-      <c r="O257" s="49">
-        <f t="shared" si="56"/>
-        <v>154.44</v>
-      </c>
-      <c r="P257" s="11">
-        <f t="shared" si="57"/>
-        <v>617.76</v>
+        <f t="shared" si="58"/>
+        <v>574.56000000000006</v>
+      </c>
+      <c r="O257" s="40">
+        <f t="shared" si="59"/>
+        <v>114.91200000000002</v>
+      </c>
+      <c r="P257" s="40">
+        <f t="shared" si="60"/>
+        <v>459.64800000000008</v>
       </c>
     </row>
     <row r="258" spans="1:16" x14ac:dyDescent="0.2">
@@ -15131,29 +15114,29 @@
         <v>14</v>
       </c>
       <c r="B258" s="16">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C258" s="9" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D258" s="9" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E258" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F258" s="10">
-        <v>1260</v>
+        <v>2520</v>
       </c>
       <c r="G258" s="11">
         <v>37.270000000000003</v>
       </c>
       <c r="H258" s="12">
         <f t="shared" si="48"/>
-        <v>46960.200000000004</v>
+        <v>93920.400000000009</v>
       </c>
       <c r="I258" s="29">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="J258" s="25">
         <v>45966</v>
@@ -15169,16 +15152,16 @@
         <v>0.02</v>
       </c>
       <c r="N258" s="11">
-        <f t="shared" ref="N258:N264" si="58">M258*H258</f>
-        <v>939.20400000000006</v>
-      </c>
-      <c r="O258" s="49">
-        <f t="shared" ref="O258:O264" si="59">0.2*N258</f>
-        <v>187.84080000000003</v>
-      </c>
-      <c r="P258" s="49">
-        <f t="shared" ref="P258:P264" si="60">0.8*N258</f>
-        <v>751.36320000000012</v>
+        <f t="shared" si="58"/>
+        <v>1878.4080000000001</v>
+      </c>
+      <c r="O258" s="40">
+        <f t="shared" si="59"/>
+        <v>375.68160000000006</v>
+      </c>
+      <c r="P258" s="40">
+        <f t="shared" si="60"/>
+        <v>1502.7264000000002</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.2">
@@ -15186,7 +15169,7 @@
         <v>14</v>
       </c>
       <c r="B259" s="16">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C259" s="9" t="s">
         <v>79</v>
@@ -15195,17 +15178,17 @@
         <v>80</v>
       </c>
       <c r="E259" s="9" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F259" s="10">
-        <v>720</v>
+        <v>1400</v>
       </c>
       <c r="G259" s="11">
-        <v>39.9</v>
+        <v>25.68</v>
       </c>
       <c r="H259" s="12">
         <f t="shared" si="48"/>
-        <v>28728</v>
+        <v>35952</v>
       </c>
       <c r="I259" s="29">
         <v>45958</v>
@@ -15217,23 +15200,23 @@
         <v>18</v>
       </c>
       <c r="L259" s="29">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="M259" s="13">
         <f>VLOOKUP(E259,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N259" s="11">
         <f t="shared" si="58"/>
-        <v>574.56000000000006</v>
-      </c>
-      <c r="O259" s="49">
+        <v>539.28</v>
+      </c>
+      <c r="O259" s="40">
         <f t="shared" si="59"/>
-        <v>114.91200000000002</v>
-      </c>
-      <c r="P259" s="49">
+        <v>107.85599999999999</v>
+      </c>
+      <c r="P259" s="11">
         <f t="shared" si="60"/>
-        <v>459.64800000000008</v>
+        <v>431.42399999999998</v>
       </c>
     </row>
     <row r="260" spans="1:16" x14ac:dyDescent="0.2">
@@ -15241,29 +15224,29 @@
         <v>14</v>
       </c>
       <c r="B260" s="16">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C260" s="9" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D260" s="9" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E260" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F260" s="10">
-        <v>2520</v>
+        <v>3150</v>
       </c>
       <c r="G260" s="11">
         <v>37.270000000000003</v>
       </c>
       <c r="H260" s="12">
         <f t="shared" si="48"/>
-        <v>93920.400000000009</v>
+        <v>117400.50000000001</v>
       </c>
       <c r="I260" s="29">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="J260" s="25">
         <v>45966</v>
@@ -15280,15 +15263,15 @@
       </c>
       <c r="N260" s="11">
         <f t="shared" si="58"/>
-        <v>1878.4080000000001</v>
-      </c>
-      <c r="O260" s="49">
+        <v>2348.0100000000002</v>
+      </c>
+      <c r="O260" s="40">
         <f t="shared" si="59"/>
-        <v>375.68160000000006</v>
-      </c>
-      <c r="P260" s="49">
+        <v>469.60200000000009</v>
+      </c>
+      <c r="P260" s="40">
         <f t="shared" si="60"/>
-        <v>1502.7264000000002</v>
+        <v>1878.4080000000004</v>
       </c>
     </row>
     <row r="261" spans="1:16" x14ac:dyDescent="0.2">
@@ -15296,29 +15279,29 @@
         <v>14</v>
       </c>
       <c r="B261" s="16">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C261" s="9" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D261" s="9" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E261" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F261" s="10">
-        <v>1400</v>
+        <v>630</v>
       </c>
       <c r="G261" s="11">
-        <v>25.68</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="H261" s="12">
         <f t="shared" si="48"/>
-        <v>35952</v>
+        <v>23480.100000000002</v>
       </c>
       <c r="I261" s="29">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="J261" s="25">
         <v>45966</v>
@@ -15327,133 +15310,133 @@
         <v>18</v>
       </c>
       <c r="L261" s="29">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="M261" s="13">
         <f>VLOOKUP(E261,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N261" s="11">
         <f t="shared" si="58"/>
+        <v>469.60200000000003</v>
+      </c>
+      <c r="O261" s="40">
+        <f t="shared" si="59"/>
+        <v>93.920400000000015</v>
+      </c>
+      <c r="P261" s="40">
+        <f t="shared" si="60"/>
+        <v>375.68160000000006</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A262" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B262" s="16">
+        <v>203</v>
+      </c>
+      <c r="C262" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D262" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="E262" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F262" s="10">
+        <v>1400</v>
+      </c>
+      <c r="G262" s="11">
+        <v>25.68</v>
+      </c>
+      <c r="H262" s="12">
+        <f t="shared" si="48"/>
+        <v>35952</v>
+      </c>
+      <c r="I262" s="29">
+        <v>45960</v>
+      </c>
+      <c r="J262" s="25">
+        <v>45966</v>
+      </c>
+      <c r="K262" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L262" s="29">
+        <v>46142</v>
+      </c>
+      <c r="M262" s="13">
+        <f>VLOOKUP(E262,tabela_produto[],2,FALSE)</f>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N262" s="11">
+        <f t="shared" si="58"/>
         <v>539.28</v>
       </c>
-      <c r="O261" s="49">
+      <c r="O262" s="40">
         <f t="shared" si="59"/>
         <v>107.85599999999999</v>
       </c>
-      <c r="P261" s="11">
+      <c r="P262" s="11">
         <f t="shared" si="60"/>
         <v>431.42399999999998</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A262" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B262" s="16">
-        <v>201</v>
-      </c>
-      <c r="C262" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D262" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E262" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F262" s="10">
-        <v>3150</v>
-      </c>
-      <c r="G262" s="11">
-        <v>37.270000000000003</v>
-      </c>
-      <c r="H262" s="12">
-        <f t="shared" si="48"/>
-        <v>117400.50000000001</v>
-      </c>
-      <c r="I262" s="29">
-        <v>45959</v>
-      </c>
-      <c r="J262" s="25">
-        <v>45966</v>
-      </c>
-      <c r="K262" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L262" s="29">
-        <v>46081</v>
-      </c>
-      <c r="M262" s="13">
-        <f>VLOOKUP(E262,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
-      </c>
-      <c r="N262" s="11">
-        <f t="shared" si="58"/>
-        <v>2348.0100000000002</v>
-      </c>
-      <c r="O262" s="49">
-        <f t="shared" si="59"/>
-        <v>469.60200000000009</v>
-      </c>
-      <c r="P262" s="49">
-        <f t="shared" si="60"/>
-        <v>1878.4080000000004</v>
-      </c>
-    </row>
     <row r="263" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A263" s="9" t="s">
         <v>14</v>
       </c>
       <c r="B263" s="16">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C263" s="9" t="s">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="D263" s="9" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="E263" s="9" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F263" s="10">
-        <v>630</v>
+        <v>1440</v>
       </c>
       <c r="G263" s="11">
-        <v>37.270000000000003</v>
+        <v>27.6</v>
       </c>
       <c r="H263" s="12">
         <f t="shared" si="48"/>
-        <v>23480.100000000002</v>
+        <v>39744</v>
       </c>
       <c r="I263" s="29">
-        <v>45960</v>
+        <v>45981</v>
       </c>
       <c r="J263" s="25">
-        <v>45966</v>
+        <v>45987</v>
       </c>
       <c r="K263" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L263" s="29">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="M263" s="13">
         <f>VLOOKUP(E263,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N263" s="11">
-        <f t="shared" si="58"/>
-        <v>469.60200000000003</v>
-      </c>
-      <c r="O263" s="49">
-        <f t="shared" si="59"/>
-        <v>93.920400000000015</v>
-      </c>
-      <c r="P263" s="49">
-        <f t="shared" si="60"/>
-        <v>375.68160000000006</v>
+        <f t="shared" ref="N263:N266" si="61">M263*H263</f>
+        <v>596.16</v>
+      </c>
+      <c r="O263" s="40">
+        <f t="shared" ref="O263:O266" si="62">0.2*N263</f>
+        <v>119.232</v>
+      </c>
+      <c r="P263" s="11">
+        <f t="shared" ref="P263:P266" si="63">0.8*N263</f>
+        <v>476.928</v>
       </c>
     </row>
     <row r="264" spans="1:16" x14ac:dyDescent="0.2">
@@ -15461,54 +15444,54 @@
         <v>14</v>
       </c>
       <c r="B264" s="16">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C264" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D264" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E264" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F264" s="10">
-        <v>1400</v>
+        <v>1260</v>
       </c>
       <c r="G264" s="11">
-        <v>25.68</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="H264" s="12">
         <f t="shared" si="48"/>
-        <v>35952</v>
+        <v>46960.200000000004</v>
       </c>
       <c r="I264" s="29">
-        <v>45960</v>
+        <v>45986</v>
       </c>
       <c r="J264" s="25">
-        <v>45966</v>
+        <v>45987</v>
       </c>
       <c r="K264" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L264" s="29">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="M264" s="13">
         <f>VLOOKUP(E264,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N264" s="11">
-        <f t="shared" si="58"/>
-        <v>539.28</v>
-      </c>
-      <c r="O264" s="49">
-        <f t="shared" si="59"/>
-        <v>107.85599999999999</v>
-      </c>
-      <c r="P264" s="11">
-        <f t="shared" si="60"/>
-        <v>431.42399999999998</v>
+        <f t="shared" si="61"/>
+        <v>939.20400000000006</v>
+      </c>
+      <c r="O264" s="40">
+        <f t="shared" si="62"/>
+        <v>187.84080000000003</v>
+      </c>
+      <c r="P264" s="40">
+        <f t="shared" si="63"/>
+        <v>751.36320000000012</v>
       </c>
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.2">
@@ -15516,54 +15499,54 @@
         <v>14</v>
       </c>
       <c r="B265" s="16">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C265" s="9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D265" s="9" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="E265" s="9" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="F265" s="10">
-        <v>1440</v>
+        <v>1890</v>
       </c>
       <c r="G265" s="11">
-        <v>27.6</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="H265" s="12">
         <f t="shared" si="48"/>
-        <v>39744</v>
+        <v>70440.3</v>
       </c>
       <c r="I265" s="29">
-        <v>45981</v>
+        <v>45987</v>
       </c>
       <c r="J265" s="25">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="K265" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L265" s="29">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="M265" s="13">
         <f>VLOOKUP(E265,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N265" s="11">
-        <f t="shared" ref="N265:N268" si="61">M265*H265</f>
-        <v>596.16</v>
-      </c>
-      <c r="O265" s="49">
-        <f t="shared" ref="O265:O268" si="62">0.2*N265</f>
-        <v>119.232</v>
-      </c>
-      <c r="P265" s="11">
-        <f t="shared" ref="P265:P268" si="63">0.8*N265</f>
-        <v>476.928</v>
+        <f t="shared" si="61"/>
+        <v>1408.806</v>
+      </c>
+      <c r="O265" s="40">
+        <f t="shared" si="62"/>
+        <v>281.76120000000003</v>
+      </c>
+      <c r="P265" s="40">
+        <f t="shared" si="63"/>
+        <v>1127.0448000000001</v>
       </c>
     </row>
     <row r="266" spans="1:16" x14ac:dyDescent="0.2">
@@ -15571,54 +15554,54 @@
         <v>14</v>
       </c>
       <c r="B266" s="16">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C266" s="9" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D266" s="9" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E266" s="9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F266" s="10">
-        <v>1260</v>
+        <v>700</v>
       </c>
       <c r="G266" s="11">
-        <v>37.270000000000003</v>
+        <v>25.68</v>
       </c>
       <c r="H266" s="12">
         <f t="shared" si="48"/>
-        <v>46960.200000000004</v>
+        <v>17976</v>
       </c>
       <c r="I266" s="29">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="J266" s="25">
-        <v>45987</v>
+        <v>45995</v>
       </c>
       <c r="K266" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L266" s="29">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="M266" s="13">
         <f>VLOOKUP(E266,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N266" s="11">
         <f t="shared" si="61"/>
-        <v>939.20400000000006</v>
-      </c>
-      <c r="O266" s="49">
+        <v>269.64</v>
+      </c>
+      <c r="O266" s="40">
         <f t="shared" si="62"/>
-        <v>187.84080000000003</v>
-      </c>
-      <c r="P266" s="49">
+        <v>53.927999999999997</v>
+      </c>
+      <c r="P266" s="40">
         <f t="shared" si="63"/>
-        <v>751.36320000000012</v>
+        <v>215.71199999999999</v>
       </c>
     </row>
     <row r="267" spans="1:16" x14ac:dyDescent="0.2">
@@ -15626,7 +15609,7 @@
         <v>14</v>
       </c>
       <c r="B267" s="16">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C267" s="9" t="s">
         <v>32</v>
@@ -15635,20 +15618,20 @@
         <v>33</v>
       </c>
       <c r="E267" s="9" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="F267" s="10">
-        <v>1890</v>
+        <v>360</v>
       </c>
       <c r="G267" s="11">
-        <v>37.270000000000003</v>
+        <v>28.6</v>
       </c>
       <c r="H267" s="12">
         <f t="shared" si="48"/>
-        <v>70440.3</v>
+        <v>10296</v>
       </c>
       <c r="I267" s="29">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="J267" s="25">
         <v>45995</v>
@@ -15657,23 +15640,23 @@
         <v>18</v>
       </c>
       <c r="L267" s="29">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="M267" s="13">
         <f>VLOOKUP(E267,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N267" s="11">
-        <f t="shared" si="61"/>
-        <v>1408.806</v>
-      </c>
-      <c r="O267" s="49">
-        <f t="shared" si="62"/>
-        <v>281.76120000000003</v>
-      </c>
-      <c r="P267" s="49">
-        <f t="shared" si="63"/>
-        <v>1127.0448000000001</v>
+        <f t="shared" ref="N267:N270" si="64">M267*H267</f>
+        <v>154.44</v>
+      </c>
+      <c r="O267" s="40">
+        <f t="shared" ref="O267:O270" si="65">0.2*N267</f>
+        <v>30.888000000000002</v>
+      </c>
+      <c r="P267" s="40">
+        <f t="shared" ref="P267:P270" si="66">0.8*N267</f>
+        <v>123.55200000000001</v>
       </c>
     </row>
     <row r="268" spans="1:16" x14ac:dyDescent="0.2">
@@ -15681,54 +15664,54 @@
         <v>14</v>
       </c>
       <c r="B268" s="16">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C268" s="9" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D268" s="9" t="s">
-        <v>33</v>
+        <v>117</v>
       </c>
       <c r="E268" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F268" s="10">
-        <v>700</v>
+        <v>5600</v>
       </c>
       <c r="G268" s="11">
-        <v>25.68</v>
+        <v>27</v>
       </c>
       <c r="H268" s="12">
         <f t="shared" si="48"/>
-        <v>17976</v>
+        <v>151200</v>
       </c>
       <c r="I268" s="29">
-        <v>45987</v>
+        <v>45993</v>
       </c>
       <c r="J268" s="25">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="K268" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L268" s="29">
-        <v>46142</v>
+        <v>46295</v>
       </c>
       <c r="M268" s="13">
         <f>VLOOKUP(E268,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N268" s="11">
-        <f t="shared" si="61"/>
-        <v>269.64</v>
-      </c>
-      <c r="O268" s="49">
-        <f t="shared" si="62"/>
-        <v>53.927999999999997</v>
-      </c>
-      <c r="P268" s="49">
-        <f t="shared" si="63"/>
-        <v>215.71199999999999</v>
+        <f t="shared" si="64"/>
+        <v>2268</v>
+      </c>
+      <c r="O268" s="40">
+        <f t="shared" si="65"/>
+        <v>453.6</v>
+      </c>
+      <c r="P268" s="11">
+        <f t="shared" si="66"/>
+        <v>1814.4</v>
       </c>
     </row>
     <row r="269" spans="1:16" x14ac:dyDescent="0.2">
@@ -15736,54 +15719,54 @@
         <v>14</v>
       </c>
       <c r="B269" s="16">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C269" s="9" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D269" s="9" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="E269" s="9" t="s">
-        <v>87</v>
+        <v>43</v>
       </c>
       <c r="F269" s="10">
-        <v>360</v>
+        <v>5600</v>
       </c>
       <c r="G269" s="11">
-        <v>28.6</v>
+        <v>27</v>
       </c>
       <c r="H269" s="12">
         <f t="shared" si="48"/>
-        <v>10296</v>
+        <v>151200</v>
       </c>
       <c r="I269" s="29">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="J269" s="25">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="K269" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L269" s="29">
-        <v>46142</v>
+        <v>46295</v>
       </c>
       <c r="M269" s="13">
         <f>VLOOKUP(E269,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N269" s="11">
-        <f t="shared" ref="N269:N272" si="64">M269*H269</f>
-        <v>154.44</v>
-      </c>
-      <c r="O269" s="49">
-        <f t="shared" ref="O269:O272" si="65">0.2*N269</f>
-        <v>30.888000000000002</v>
-      </c>
-      <c r="P269" s="49">
-        <f t="shared" ref="P269:P272" si="66">0.8*N269</f>
-        <v>123.55200000000001</v>
+        <f t="shared" si="64"/>
+        <v>2268</v>
+      </c>
+      <c r="O269" s="40">
+        <f t="shared" si="65"/>
+        <v>453.6</v>
+      </c>
+      <c r="P269" s="11">
+        <f t="shared" si="66"/>
+        <v>1814.4</v>
       </c>
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.2">
@@ -15791,54 +15774,54 @@
         <v>14</v>
       </c>
       <c r="B270" s="16">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C270" s="9" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D270" s="9" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="E270" s="9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F270" s="10">
-        <v>5600</v>
+        <v>1260</v>
       </c>
       <c r="G270" s="11">
-        <v>27</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="H270" s="12">
         <f t="shared" si="48"/>
-        <v>151200</v>
+        <v>46960.200000000004</v>
       </c>
       <c r="I270" s="29">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="J270" s="25">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="K270" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L270" s="29">
-        <v>46295</v>
+        <v>46081</v>
       </c>
       <c r="M270" s="13">
         <f>VLOOKUP(E270,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N270" s="11">
         <f t="shared" si="64"/>
-        <v>2268</v>
-      </c>
-      <c r="O270" s="49">
+        <v>939.20400000000006</v>
+      </c>
+      <c r="O270" s="40">
         <f t="shared" si="65"/>
-        <v>453.6</v>
-      </c>
-      <c r="P270" s="11">
+        <v>187.84080000000003</v>
+      </c>
+      <c r="P270" s="40">
         <f t="shared" si="66"/>
-        <v>1814.4</v>
+        <v>751.36320000000012</v>
       </c>
     </row>
     <row r="271" spans="1:16" x14ac:dyDescent="0.2">
@@ -15846,54 +15829,54 @@
         <v>14</v>
       </c>
       <c r="B271" s="16">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C271" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E271" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F271" s="10">
-        <v>5600</v>
+        <v>700</v>
       </c>
       <c r="G271" s="11">
-        <v>27</v>
+        <v>25.68</v>
       </c>
       <c r="H271" s="12">
         <f t="shared" si="48"/>
-        <v>151200</v>
+        <v>17976</v>
       </c>
       <c r="I271" s="29">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="J271" s="25">
-        <v>45996</v>
+        <v>46007</v>
       </c>
       <c r="K271" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L271" s="29">
-        <v>46295</v>
+        <v>46142</v>
       </c>
       <c r="M271" s="13">
         <f>VLOOKUP(E271,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N271" s="11">
-        <f t="shared" si="64"/>
-        <v>2268</v>
-      </c>
-      <c r="O271" s="49">
-        <f t="shared" si="65"/>
-        <v>453.6</v>
+        <f t="shared" ref="N271:N273" si="67">M271*H271</f>
+        <v>269.64</v>
+      </c>
+      <c r="O271" s="40">
+        <f t="shared" ref="O271:O273" si="68">0.2*N271</f>
+        <v>53.927999999999997</v>
       </c>
       <c r="P271" s="11">
-        <f t="shared" si="66"/>
-        <v>1814.4</v>
+        <f t="shared" ref="P271:P273" si="69">0.8*N271</f>
+        <v>215.71199999999999</v>
       </c>
     </row>
     <row r="272" spans="1:16" x14ac:dyDescent="0.2">
@@ -15901,32 +15884,32 @@
         <v>14</v>
       </c>
       <c r="B272" s="16">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C272" s="9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="E272" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F272" s="10">
-        <v>1260</v>
+        <v>1080</v>
       </c>
       <c r="G272" s="11">
-        <v>37.270000000000003</v>
+        <v>38</v>
       </c>
       <c r="H272" s="12">
         <f t="shared" si="48"/>
-        <v>46960.200000000004</v>
+        <v>41040</v>
       </c>
       <c r="I272" s="29">
-        <v>45995</v>
+        <v>46002</v>
       </c>
       <c r="J272" s="25">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="K272" s="9" t="s">
         <v>18</v>
@@ -15939,16 +15922,16 @@
         <v>0.02</v>
       </c>
       <c r="N272" s="11">
-        <f t="shared" si="64"/>
-        <v>939.20400000000006</v>
-      </c>
-      <c r="O272" s="49">
-        <f t="shared" si="65"/>
-        <v>187.84080000000003</v>
-      </c>
-      <c r="P272" s="49">
-        <f t="shared" si="66"/>
-        <v>751.36320000000012</v>
+        <f t="shared" si="67"/>
+        <v>820.80000000000007</v>
+      </c>
+      <c r="O272" s="40">
+        <f t="shared" si="68"/>
+        <v>164.16000000000003</v>
+      </c>
+      <c r="P272" s="40">
+        <f t="shared" si="69"/>
+        <v>656.6400000000001</v>
       </c>
     </row>
     <row r="273" spans="1:16" x14ac:dyDescent="0.2">
@@ -15956,7 +15939,7 @@
         <v>14</v>
       </c>
       <c r="B273" s="16">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C273" s="9" t="s">
         <v>46</v>
@@ -15965,17 +15948,17 @@
         <v>114</v>
       </c>
       <c r="E273" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F273" s="10">
-        <v>700</v>
+        <v>1260</v>
       </c>
       <c r="G273" s="11">
-        <v>25.68</v>
+        <v>37.270000000000003</v>
       </c>
       <c r="H273" s="12">
         <f t="shared" si="48"/>
-        <v>17976</v>
+        <v>46960.200000000004</v>
       </c>
       <c r="I273" s="29">
         <v>46002</v>
@@ -15987,23 +15970,23 @@
         <v>18</v>
       </c>
       <c r="L273" s="29">
-        <v>46142</v>
+        <v>46081</v>
       </c>
       <c r="M273" s="13">
         <f>VLOOKUP(E273,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N273" s="11">
-        <f t="shared" ref="N273:N275" si="67">M273*H273</f>
-        <v>269.64</v>
-      </c>
-      <c r="O273" s="49">
-        <f t="shared" ref="O273:O275" si="68">0.2*N273</f>
-        <v>53.927999999999997</v>
-      </c>
-      <c r="P273" s="11">
-        <f t="shared" ref="P273:P275" si="69">0.8*N273</f>
-        <v>215.71199999999999</v>
+        <f t="shared" si="67"/>
+        <v>939.20400000000006</v>
+      </c>
+      <c r="O273" s="40">
+        <f t="shared" si="68"/>
+        <v>187.84080000000003</v>
+      </c>
+      <c r="P273" s="40">
+        <f t="shared" si="69"/>
+        <v>751.36320000000012</v>
       </c>
     </row>
     <row r="274" spans="1:16" x14ac:dyDescent="0.2">
@@ -16011,54 +15994,54 @@
         <v>14</v>
       </c>
       <c r="B274" s="16">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C274" s="9" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D274" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E274" s="9" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="F274" s="10">
-        <v>1080</v>
+        <v>720</v>
       </c>
       <c r="G274" s="11">
-        <v>38</v>
+        <v>28.6</v>
       </c>
       <c r="H274" s="12">
         <f t="shared" si="48"/>
-        <v>41040</v>
+        <v>20592</v>
       </c>
       <c r="I274" s="29">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="J274" s="25">
-        <v>46007</v>
+        <v>46036</v>
       </c>
       <c r="K274" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L274" s="29">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="M274" s="13">
         <f>VLOOKUP(E274,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N274" s="11">
-        <f t="shared" si="67"/>
-        <v>820.80000000000007</v>
-      </c>
-      <c r="O274" s="49">
-        <f t="shared" si="68"/>
-        <v>164.16000000000003</v>
-      </c>
-      <c r="P274" s="49">
-        <f t="shared" si="69"/>
-        <v>656.6400000000001</v>
+        <f t="shared" ref="N274:N275" si="70">M274*H274</f>
+        <v>308.88</v>
+      </c>
+      <c r="O274" s="40">
+        <f t="shared" ref="O274:O275" si="71">0.2*N274</f>
+        <v>61.776000000000003</v>
+      </c>
+      <c r="P274" s="11">
+        <f t="shared" ref="P274:P275" si="72">0.8*N274</f>
+        <v>247.10400000000001</v>
       </c>
     </row>
     <row r="275" spans="1:16" x14ac:dyDescent="0.2">
@@ -16066,54 +16049,54 @@
         <v>14</v>
       </c>
       <c r="B275" s="16">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C275" s="9" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="D275" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E275" s="9" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="F275" s="10">
-        <v>1260</v>
+        <v>700</v>
       </c>
       <c r="G275" s="11">
-        <v>37.270000000000003</v>
+        <v>25.68</v>
       </c>
       <c r="H275" s="12">
         <f t="shared" si="48"/>
-        <v>46960.200000000004</v>
+        <v>17976</v>
       </c>
       <c r="I275" s="29">
-        <v>46002</v>
+        <v>46007</v>
       </c>
       <c r="J275" s="25">
-        <v>46007</v>
+        <v>46036</v>
       </c>
       <c r="K275" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L275" s="29">
-        <v>46081</v>
+        <v>46142</v>
       </c>
       <c r="M275" s="13">
         <f>VLOOKUP(E275,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N275" s="11">
-        <f t="shared" si="67"/>
-        <v>939.20400000000006</v>
-      </c>
-      <c r="O275" s="49">
-        <f t="shared" si="68"/>
-        <v>187.84080000000003</v>
-      </c>
-      <c r="P275" s="49">
-        <f t="shared" si="69"/>
-        <v>751.36320000000012</v>
+        <f t="shared" si="70"/>
+        <v>269.64</v>
+      </c>
+      <c r="O275" s="40">
+        <f t="shared" si="71"/>
+        <v>53.927999999999997</v>
+      </c>
+      <c r="P275" s="11">
+        <f t="shared" si="72"/>
+        <v>215.71199999999999</v>
       </c>
     </row>
     <row r="276" spans="1:16" x14ac:dyDescent="0.2">
@@ -16121,29 +16104,29 @@
         <v>14</v>
       </c>
       <c r="B276" s="16">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C276" s="9" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D276" s="9" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E276" s="9" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="F276" s="10">
-        <v>720</v>
+        <v>1400</v>
       </c>
       <c r="G276" s="11">
-        <v>28.6</v>
+        <v>21.03</v>
       </c>
       <c r="H276" s="12">
         <f t="shared" si="48"/>
-        <v>20592</v>
+        <v>29442</v>
       </c>
       <c r="I276" s="29">
-        <v>46007</v>
+        <v>46031</v>
       </c>
       <c r="J276" s="25">
         <v>46036</v>
@@ -16152,23 +16135,23 @@
         <v>18</v>
       </c>
       <c r="L276" s="29">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="M276" s="13">
         <f>VLOOKUP(E276,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N276" s="11">
-        <f t="shared" ref="N276:N277" si="70">M276*H276</f>
-        <v>308.88</v>
-      </c>
-      <c r="O276" s="49">
-        <f t="shared" ref="O276:O277" si="71">0.2*N276</f>
-        <v>61.776000000000003</v>
+        <f t="shared" ref="N276:N279" si="73">M276*H276</f>
+        <v>441.63</v>
+      </c>
+      <c r="O276" s="40">
+        <f t="shared" ref="O276:O279" si="74">0.2*N276</f>
+        <v>88.326000000000008</v>
       </c>
       <c r="P276" s="11">
-        <f t="shared" ref="P276:P277" si="72">0.8*N276</f>
-        <v>247.10400000000001</v>
+        <f t="shared" ref="P276:P279" si="75">0.8*N276</f>
+        <v>353.30400000000003</v>
       </c>
     </row>
     <row r="277" spans="1:16" x14ac:dyDescent="0.2">
@@ -16176,29 +16159,29 @@
         <v>14</v>
       </c>
       <c r="B277" s="16">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C277" s="9" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D277" s="9" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="E277" s="9" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F277" s="10">
-        <v>700</v>
+        <v>360</v>
       </c>
       <c r="G277" s="11">
-        <v>25.68</v>
+        <v>22.86</v>
       </c>
       <c r="H277" s="12">
         <f t="shared" si="48"/>
-        <v>17976</v>
+        <v>8229.6</v>
       </c>
       <c r="I277" s="29">
-        <v>46007</v>
+        <v>46031</v>
       </c>
       <c r="J277" s="25">
         <v>46036</v>
@@ -16207,23 +16190,23 @@
         <v>18</v>
       </c>
       <c r="L277" s="29">
-        <v>46142</v>
+        <v>46203</v>
       </c>
       <c r="M277" s="13">
         <f>VLOOKUP(E277,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N277" s="11">
-        <f t="shared" si="70"/>
-        <v>269.64</v>
-      </c>
-      <c r="O277" s="49">
-        <f t="shared" si="71"/>
-        <v>53.927999999999997</v>
+        <f t="shared" si="73"/>
+        <v>123.444</v>
+      </c>
+      <c r="O277" s="40">
+        <f t="shared" si="74"/>
+        <v>24.688800000000001</v>
       </c>
       <c r="P277" s="11">
-        <f t="shared" si="72"/>
-        <v>215.71199999999999</v>
+        <f t="shared" si="75"/>
+        <v>98.755200000000002</v>
       </c>
     </row>
     <row r="278" spans="1:16" x14ac:dyDescent="0.2">
@@ -16231,31 +16214,33 @@
         <v>14</v>
       </c>
       <c r="B278" s="16">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C278" s="9" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="D278" s="9" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="E278" s="9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F278" s="10">
-        <v>9800</v>
+        <v>630</v>
       </c>
       <c r="G278" s="11">
-        <v>22.65</v>
+        <v>34.01</v>
       </c>
       <c r="H278" s="12">
         <f t="shared" si="48"/>
-        <v>221970</v>
+        <v>21426.3</v>
       </c>
       <c r="I278" s="29">
         <v>46031</v>
       </c>
-      <c r="J278" s="25"/>
+      <c r="J278" s="25">
+        <v>46036</v>
+      </c>
       <c r="K278" s="9" t="s">
         <v>18</v>
       </c>
@@ -16264,19 +16249,19 @@
       </c>
       <c r="M278" s="13">
         <f>VLOOKUP(E278,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N278" s="11">
-        <f t="shared" ref="N278:N279" si="73">M278*H278</f>
-        <v>3329.5499999999997</v>
-      </c>
-      <c r="O278" s="11">
-        <f t="shared" ref="O278:O279" si="74">0.2*N278</f>
-        <v>665.91</v>
+        <f t="shared" si="73"/>
+        <v>428.52600000000001</v>
+      </c>
+      <c r="O278" s="40">
+        <f t="shared" si="74"/>
+        <v>85.705200000000005</v>
       </c>
       <c r="P278" s="11">
-        <f t="shared" ref="P278:P279" si="75">0.8*N278</f>
-        <v>2663.64</v>
+        <f t="shared" si="75"/>
+        <v>342.82080000000002</v>
       </c>
     </row>
     <row r="279" spans="1:16" x14ac:dyDescent="0.2">
@@ -16284,36 +16269,38 @@
         <v>14</v>
       </c>
       <c r="B279" s="16">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C279" s="9" t="s">
-        <v>60</v>
+        <v>109</v>
       </c>
       <c r="D279" s="9" t="s">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c r="E279" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F279" s="10">
-        <v>9800</v>
+        <v>4200</v>
       </c>
       <c r="G279" s="11">
-        <v>21.03</v>
+        <v>21</v>
       </c>
       <c r="H279" s="12">
         <f t="shared" si="48"/>
-        <v>206094</v>
+        <v>88200</v>
       </c>
       <c r="I279" s="29">
-        <v>46031</v>
-      </c>
-      <c r="J279" s="25"/>
+        <v>46034</v>
+      </c>
+      <c r="J279" s="25">
+        <v>46043</v>
+      </c>
       <c r="K279" s="9" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="L279" s="29">
-        <v>46203</v>
+        <v>46052</v>
       </c>
       <c r="M279" s="13">
         <f>VLOOKUP(E279,tabela_produto[],2,FALSE)</f>
@@ -16321,15 +16308,15 @@
       </c>
       <c r="N279" s="11">
         <f t="shared" si="73"/>
-        <v>3091.41</v>
-      </c>
-      <c r="O279" s="11">
+        <v>1323</v>
+      </c>
+      <c r="O279" s="40">
         <f t="shared" si="74"/>
-        <v>618.28200000000004</v>
-      </c>
-      <c r="P279" s="11">
+        <v>264.60000000000002</v>
+      </c>
+      <c r="P279" s="40">
         <f t="shared" si="75"/>
-        <v>2473.1280000000002</v>
+        <v>1058.4000000000001</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.2">
@@ -16337,32 +16324,32 @@
         <v>14</v>
       </c>
       <c r="B280" s="16">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C280" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D280" s="9" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E280" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F280" s="10">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="G280" s="11">
-        <v>21.03</v>
+        <v>22.65</v>
       </c>
       <c r="H280" s="12">
         <f t="shared" si="48"/>
-        <v>29442</v>
+        <v>47565</v>
       </c>
       <c r="I280" s="29">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="J280" s="25">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="K280" s="9" t="s">
         <v>18</v>
@@ -16376,15 +16363,15 @@
       </c>
       <c r="N280" s="11">
         <f t="shared" ref="N280:N283" si="76">M280*H280</f>
-        <v>441.63</v>
-      </c>
-      <c r="O280" s="49">
+        <v>713.47500000000002</v>
+      </c>
+      <c r="O280" s="40">
         <f t="shared" ref="O280:O283" si="77">0.2*N280</f>
-        <v>88.326000000000008</v>
+        <v>142.69500000000002</v>
       </c>
       <c r="P280" s="11">
         <f t="shared" ref="P280:P283" si="78">0.8*N280</f>
-        <v>353.30400000000003</v>
+        <v>570.78000000000009</v>
       </c>
     </row>
     <row r="281" spans="1:16" x14ac:dyDescent="0.2">
@@ -16392,13 +16379,13 @@
         <v>14</v>
       </c>
       <c r="B281" s="16">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C281" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D281" s="9" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E281" s="9" t="s">
         <v>87</v>
@@ -16414,10 +16401,10 @@
         <v>8229.6</v>
       </c>
       <c r="I281" s="29">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="J281" s="25">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="K281" s="9" t="s">
         <v>18</v>
@@ -16433,7 +16420,7 @@
         <f t="shared" si="76"/>
         <v>123.444</v>
       </c>
-      <c r="O281" s="49">
+      <c r="O281" s="40">
         <f t="shared" si="77"/>
         <v>24.688800000000001</v>
       </c>
@@ -16447,32 +16434,32 @@
         <v>14</v>
       </c>
       <c r="B282" s="16">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C282" s="9" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D282" s="9" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E282" s="9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F282" s="10">
-        <v>630</v>
+        <v>2100</v>
       </c>
       <c r="G282" s="11">
-        <v>34.01</v>
+        <v>21.03</v>
       </c>
       <c r="H282" s="12">
         <f t="shared" si="48"/>
-        <v>21426.3</v>
+        <v>44163</v>
       </c>
       <c r="I282" s="29">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="J282" s="25">
-        <v>46036</v>
+        <v>46041</v>
       </c>
       <c r="K282" s="9" t="s">
         <v>18</v>
@@ -16482,19 +16469,19 @@
       </c>
       <c r="M282" s="13">
         <f>VLOOKUP(E282,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N282" s="11">
         <f t="shared" si="76"/>
-        <v>428.52600000000001</v>
-      </c>
-      <c r="O282" s="49">
+        <v>662.44499999999994</v>
+      </c>
+      <c r="O282" s="40">
         <f t="shared" si="77"/>
-        <v>85.705200000000005</v>
+        <v>132.489</v>
       </c>
       <c r="P282" s="11">
         <f t="shared" si="78"/>
-        <v>342.82080000000002</v>
+        <v>529.95600000000002</v>
       </c>
     </row>
     <row r="283" spans="1:16" x14ac:dyDescent="0.2">
@@ -16502,54 +16489,54 @@
         <v>14</v>
       </c>
       <c r="B283" s="16">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C283" s="9" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="D283" s="9" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="E283" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F283" s="10">
-        <v>4200</v>
+        <v>2520</v>
       </c>
       <c r="G283" s="11">
-        <v>21</v>
+        <v>34.01</v>
       </c>
       <c r="H283" s="12">
         <f t="shared" si="48"/>
-        <v>88200</v>
+        <v>85705.2</v>
       </c>
       <c r="I283" s="29">
         <v>46034</v>
       </c>
       <c r="J283" s="25">
-        <v>46043</v>
+        <v>46041</v>
       </c>
       <c r="K283" s="9" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="L283" s="29">
-        <v>46052</v>
+        <v>46203</v>
       </c>
       <c r="M283" s="13">
         <f>VLOOKUP(E283,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N283" s="11">
         <f t="shared" si="76"/>
-        <v>1323</v>
-      </c>
-      <c r="O283" s="49">
+        <v>1714.104</v>
+      </c>
+      <c r="O283" s="40">
         <f t="shared" si="77"/>
-        <v>264.60000000000002</v>
-      </c>
-      <c r="P283" s="49">
+        <v>342.82080000000002</v>
+      </c>
+      <c r="P283" s="11">
         <f t="shared" si="78"/>
-        <v>1058.4000000000001</v>
+        <v>1371.2832000000001</v>
       </c>
     </row>
     <row r="284" spans="1:16" x14ac:dyDescent="0.2">
@@ -16557,32 +16544,32 @@
         <v>14</v>
       </c>
       <c r="B284" s="16">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C284" s="9" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D284" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E284" s="9" t="s">
         <v>43</v>
       </c>
       <c r="F284" s="10">
-        <v>2100</v>
+        <v>1400</v>
       </c>
       <c r="G284" s="11">
         <v>22.65</v>
       </c>
       <c r="H284" s="12">
         <f t="shared" si="48"/>
-        <v>47565</v>
+        <v>31709.999999999996</v>
       </c>
       <c r="I284" s="29">
-        <v>46034</v>
+        <v>46046</v>
       </c>
       <c r="J284" s="25">
-        <v>46041</v>
+        <v>46049</v>
       </c>
       <c r="K284" s="9" t="s">
         <v>18</v>
@@ -16595,16 +16582,16 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N284" s="11">
-        <f t="shared" ref="N284:N287" si="79">M284*H284</f>
-        <v>713.47500000000002</v>
-      </c>
-      <c r="O284" s="49">
-        <f t="shared" ref="O284:O287" si="80">0.2*N284</f>
-        <v>142.69500000000002</v>
+        <f t="shared" ref="N284:N288" si="79">M284*H284</f>
+        <v>475.64999999999992</v>
+      </c>
+      <c r="O284" s="40">
+        <f t="shared" ref="O284:O288" si="80">0.2*N284</f>
+        <v>95.13</v>
       </c>
       <c r="P284" s="11">
-        <f t="shared" ref="P284:P287" si="81">0.8*N284</f>
-        <v>570.78000000000009</v>
+        <f t="shared" ref="P284:P288" si="81">0.8*N284</f>
+        <v>380.52</v>
       </c>
     </row>
     <row r="285" spans="1:16" x14ac:dyDescent="0.2">
@@ -16612,32 +16599,32 @@
         <v>14</v>
       </c>
       <c r="B285" s="16">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C285" s="9" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="D285" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E285" s="9" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="F285" s="10">
-        <v>360</v>
+        <v>500</v>
       </c>
       <c r="G285" s="11">
-        <v>22.86</v>
+        <v>19.88</v>
       </c>
       <c r="H285" s="12">
         <f t="shared" si="48"/>
-        <v>8229.6</v>
+        <v>9940</v>
       </c>
       <c r="I285" s="29">
-        <v>46034</v>
+        <v>46046</v>
       </c>
       <c r="J285" s="25">
-        <v>46041</v>
+        <v>46049</v>
       </c>
       <c r="K285" s="9" t="s">
         <v>18</v>
@@ -16651,15 +16638,15 @@
       </c>
       <c r="N285" s="11">
         <f t="shared" si="79"/>
-        <v>123.444</v>
-      </c>
-      <c r="O285" s="49">
+        <v>149.1</v>
+      </c>
+      <c r="O285" s="40">
         <f t="shared" si="80"/>
-        <v>24.688800000000001</v>
+        <v>29.82</v>
       </c>
       <c r="P285" s="11">
         <f t="shared" si="81"/>
-        <v>98.755200000000002</v>
+        <v>119.28</v>
       </c>
     </row>
     <row r="286" spans="1:16" x14ac:dyDescent="0.2">
@@ -16667,32 +16654,32 @@
         <v>14</v>
       </c>
       <c r="B286" s="16">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D286" s="9" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E286" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F286" s="10">
-        <v>2100</v>
+        <v>700</v>
       </c>
       <c r="G286" s="11">
         <v>21.03</v>
       </c>
       <c r="H286" s="12">
         <f t="shared" si="48"/>
-        <v>44163</v>
+        <v>14721</v>
       </c>
       <c r="I286" s="29">
-        <v>46034</v>
+        <v>46049</v>
       </c>
       <c r="J286" s="25">
-        <v>46041</v>
+        <v>46049</v>
       </c>
       <c r="K286" s="9" t="s">
         <v>18</v>
@@ -16706,15 +16693,15 @@
       </c>
       <c r="N286" s="11">
         <f t="shared" si="79"/>
-        <v>662.44499999999994</v>
-      </c>
-      <c r="O286" s="49">
+        <v>220.815</v>
+      </c>
+      <c r="O286" s="40">
         <f t="shared" si="80"/>
-        <v>132.489</v>
+        <v>44.163000000000004</v>
       </c>
       <c r="P286" s="11">
         <f t="shared" si="81"/>
-        <v>529.95600000000002</v>
+        <v>176.65200000000002</v>
       </c>
     </row>
     <row r="287" spans="1:16" x14ac:dyDescent="0.2">
@@ -16722,32 +16709,32 @@
         <v>14</v>
       </c>
       <c r="B287" s="16">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C287" s="9" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="D287" s="9" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E287" s="9" t="s">
         <v>20</v>
       </c>
       <c r="F287" s="10">
-        <v>2520</v>
+        <v>630</v>
       </c>
       <c r="G287" s="11">
         <v>34.01</v>
       </c>
       <c r="H287" s="12">
         <f t="shared" si="48"/>
-        <v>85705.2</v>
+        <v>21426.3</v>
       </c>
       <c r="I287" s="29">
-        <v>46034</v>
+        <v>46049</v>
       </c>
       <c r="J287" s="25">
-        <v>46041</v>
+        <v>46049</v>
       </c>
       <c r="K287" s="9" t="s">
         <v>18</v>
@@ -16761,15 +16748,15 @@
       </c>
       <c r="N287" s="11">
         <f t="shared" si="79"/>
-        <v>1714.104</v>
-      </c>
-      <c r="O287" s="49">
+        <v>428.52600000000001</v>
+      </c>
+      <c r="O287" s="40">
         <f t="shared" si="80"/>
-        <v>342.82080000000002</v>
+        <v>85.705200000000005</v>
       </c>
       <c r="P287" s="11">
         <f t="shared" si="81"/>
-        <v>1371.2832000000001</v>
+        <v>342.82080000000002</v>
       </c>
     </row>
     <row r="288" spans="1:16" x14ac:dyDescent="0.2">
@@ -16777,54 +16764,54 @@
         <v>14</v>
       </c>
       <c r="B288" s="16">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="D288" s="9" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="E288" s="9" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F288" s="10">
-        <v>1400</v>
+        <v>1260</v>
       </c>
       <c r="G288" s="11">
-        <v>22.65</v>
+        <v>32.5</v>
       </c>
       <c r="H288" s="12">
         <f t="shared" si="48"/>
-        <v>31709.999999999996</v>
+        <v>40950</v>
       </c>
       <c r="I288" s="29">
-        <v>46046</v>
+        <v>46052</v>
       </c>
       <c r="J288" s="25">
-        <v>46049</v>
+        <v>46058</v>
       </c>
       <c r="K288" s="9" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="L288" s="29">
-        <v>46203</v>
+        <v>46054</v>
       </c>
       <c r="M288" s="13">
         <f>VLOOKUP(E288,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N288" s="11">
-        <f t="shared" ref="N288:N292" si="82">M288*H288</f>
-        <v>475.64999999999992</v>
-      </c>
-      <c r="O288" s="49">
-        <f t="shared" ref="O288:O292" si="83">0.2*N288</f>
-        <v>95.13</v>
-      </c>
-      <c r="P288" s="11">
-        <f t="shared" ref="P288:P292" si="84">0.8*N288</f>
-        <v>380.52</v>
+        <f t="shared" si="79"/>
+        <v>819</v>
+      </c>
+      <c r="O288" s="40">
+        <f t="shared" si="80"/>
+        <v>163.80000000000001</v>
+      </c>
+      <c r="P288" s="40">
+        <f t="shared" si="81"/>
+        <v>655.20000000000005</v>
       </c>
     </row>
     <row r="289" spans="1:16" x14ac:dyDescent="0.2">
@@ -16832,32 +16819,32 @@
         <v>14</v>
       </c>
       <c r="B289" s="16">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C289" s="9" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="D289" s="9" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E289" s="9" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="F289" s="10">
-        <v>500</v>
+        <v>1260</v>
       </c>
       <c r="G289" s="11">
-        <v>19.88</v>
+        <v>34.01</v>
       </c>
       <c r="H289" s="12">
         <f t="shared" si="48"/>
-        <v>9940</v>
+        <v>42852.6</v>
       </c>
       <c r="I289" s="29">
-        <v>46046</v>
+        <v>46052</v>
       </c>
       <c r="J289" s="25">
-        <v>46049</v>
+        <v>46058</v>
       </c>
       <c r="K289" s="9" t="s">
         <v>18</v>
@@ -16867,19 +16854,19 @@
       </c>
       <c r="M289" s="13">
         <f>VLOOKUP(E289,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N289" s="11">
-        <f t="shared" si="82"/>
-        <v>149.1</v>
-      </c>
-      <c r="O289" s="49">
-        <f t="shared" si="83"/>
-        <v>29.82</v>
+        <f t="shared" ref="N289" si="82">M289*H289</f>
+        <v>857.05200000000002</v>
+      </c>
+      <c r="O289" s="40">
+        <f t="shared" ref="O289" si="83">0.2*N289</f>
+        <v>171.41040000000001</v>
       </c>
       <c r="P289" s="11">
-        <f t="shared" si="84"/>
-        <v>119.28</v>
+        <f t="shared" ref="P289" si="84">0.8*N289</f>
+        <v>685.64160000000004</v>
       </c>
     </row>
     <row r="290" spans="1:16" x14ac:dyDescent="0.2">
@@ -16887,32 +16874,32 @@
         <v>14</v>
       </c>
       <c r="B290" s="16">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C290" s="9" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D290" s="9" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E290" s="9" t="s">
         <v>39</v>
       </c>
       <c r="F290" s="10">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="G290" s="11">
         <v>21.03</v>
       </c>
       <c r="H290" s="12">
         <f t="shared" si="48"/>
-        <v>14721</v>
+        <v>29442</v>
       </c>
       <c r="I290" s="29">
-        <v>46049</v>
+        <v>46056</v>
       </c>
       <c r="J290" s="25">
-        <v>46049</v>
+        <v>46064</v>
       </c>
       <c r="K290" s="9" t="s">
         <v>18</v>
@@ -16925,16 +16912,16 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N290" s="11">
-        <f t="shared" si="82"/>
-        <v>220.815</v>
-      </c>
-      <c r="O290" s="49">
-        <f t="shared" si="83"/>
-        <v>44.163000000000004</v>
+        <f t="shared" ref="N290:N291" si="85">M290*H290</f>
+        <v>441.63</v>
+      </c>
+      <c r="O290" s="40">
+        <f t="shared" ref="O290:O291" si="86">0.2*N290</f>
+        <v>88.326000000000008</v>
       </c>
       <c r="P290" s="11">
-        <f t="shared" si="84"/>
-        <v>176.65200000000002</v>
+        <f t="shared" ref="P290:P291" si="87">0.8*N290</f>
+        <v>353.30400000000003</v>
       </c>
     </row>
     <row r="291" spans="1:16" x14ac:dyDescent="0.2">
@@ -16942,54 +16929,54 @@
         <v>14</v>
       </c>
       <c r="B291" s="16">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C291" s="9" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D291" s="9" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="E291" s="9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F291" s="10">
-        <v>630</v>
+        <v>3500</v>
       </c>
       <c r="G291" s="11">
-        <v>34.01</v>
+        <v>22.01</v>
       </c>
       <c r="H291" s="12">
         <f t="shared" si="48"/>
-        <v>21426.3</v>
+        <v>77035</v>
       </c>
       <c r="I291" s="29">
-        <v>46049</v>
+        <v>46063</v>
       </c>
       <c r="J291" s="25">
-        <v>46049</v>
+        <v>46072</v>
       </c>
       <c r="K291" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L291" s="29">
-        <v>46203</v>
+        <v>46285</v>
       </c>
       <c r="M291" s="13">
         <f>VLOOKUP(E291,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N291" s="11">
-        <f t="shared" si="82"/>
-        <v>428.52600000000001</v>
-      </c>
-      <c r="O291" s="49">
-        <f t="shared" si="83"/>
-        <v>85.705200000000005</v>
+        <f t="shared" si="85"/>
+        <v>1155.5249999999999</v>
+      </c>
+      <c r="O291" s="40">
+        <f t="shared" si="86"/>
+        <v>231.10499999999999</v>
       </c>
       <c r="P291" s="11">
-        <f t="shared" si="84"/>
-        <v>342.82080000000002</v>
+        <f t="shared" si="87"/>
+        <v>924.42</v>
       </c>
     </row>
     <row r="292" spans="1:16" x14ac:dyDescent="0.2">
@@ -16997,54 +16984,54 @@
         <v>14</v>
       </c>
       <c r="B292" s="16">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C292" s="9" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E292" s="9" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F292" s="10">
-        <v>1260</v>
+        <v>700</v>
       </c>
       <c r="G292" s="11">
-        <v>32.5</v>
+        <v>21.03</v>
       </c>
       <c r="H292" s="12">
         <f t="shared" si="48"/>
-        <v>40950</v>
+        <v>14721</v>
       </c>
       <c r="I292" s="29">
-        <v>46052</v>
+        <v>46078</v>
       </c>
       <c r="J292" s="25">
-        <v>46058</v>
+        <v>46085</v>
       </c>
       <c r="K292" s="9" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="L292" s="29">
-        <v>46054</v>
+        <v>46203</v>
       </c>
       <c r="M292" s="13">
         <f>VLOOKUP(E292,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N292" s="11">
-        <f t="shared" si="82"/>
-        <v>819</v>
-      </c>
-      <c r="O292" s="49">
-        <f t="shared" si="83"/>
-        <v>163.80000000000001</v>
-      </c>
-      <c r="P292" s="49">
-        <f t="shared" si="84"/>
-        <v>655.20000000000005</v>
+        <f t="shared" ref="N292:N296" si="88">M292*H292</f>
+        <v>220.815</v>
+      </c>
+      <c r="O292" s="40">
+        <f t="shared" ref="O292:O296" si="89">0.2*N292</f>
+        <v>44.163000000000004</v>
+      </c>
+      <c r="P292" s="11">
+        <f t="shared" ref="P292:P296" si="90">0.8*N292</f>
+        <v>176.65200000000002</v>
       </c>
     </row>
     <row r="293" spans="1:16" x14ac:dyDescent="0.2">
@@ -17052,32 +17039,32 @@
         <v>14</v>
       </c>
       <c r="B293" s="16">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="D293" s="9" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="E293" s="9" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F293" s="10">
-        <v>1260</v>
+        <v>700</v>
       </c>
       <c r="G293" s="11">
-        <v>34.01</v>
+        <v>22.65</v>
       </c>
       <c r="H293" s="12">
         <f t="shared" si="48"/>
-        <v>42852.6</v>
+        <v>15854.999999999998</v>
       </c>
       <c r="I293" s="29">
-        <v>46052</v>
+        <v>46078</v>
       </c>
       <c r="J293" s="25">
-        <v>46058</v>
+        <v>46085</v>
       </c>
       <c r="K293" s="9" t="s">
         <v>18</v>
@@ -17087,19 +17074,19 @@
       </c>
       <c r="M293" s="13">
         <f>VLOOKUP(E293,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N293" s="11">
-        <f t="shared" ref="N293" si="85">M293*H293</f>
-        <v>857.05200000000002</v>
-      </c>
-      <c r="O293" s="49">
-        <f t="shared" ref="O293" si="86">0.2*N293</f>
-        <v>171.41040000000001</v>
+        <f t="shared" si="88"/>
+        <v>237.82499999999996</v>
+      </c>
+      <c r="O293" s="40">
+        <f t="shared" si="89"/>
+        <v>47.564999999999998</v>
       </c>
       <c r="P293" s="11">
-        <f t="shared" ref="P293" si="87">0.8*N293</f>
-        <v>685.64160000000004</v>
+        <f t="shared" si="90"/>
+        <v>190.26</v>
       </c>
     </row>
     <row r="294" spans="1:16" x14ac:dyDescent="0.2">
@@ -17107,13 +17094,13 @@
         <v>14</v>
       </c>
       <c r="B294" s="16">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D294" s="9" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="E294" s="9" t="s">
         <v>39</v>
@@ -17122,39 +17109,39 @@
         <v>1400</v>
       </c>
       <c r="G294" s="11">
-        <v>21.03</v>
+        <v>22.01</v>
       </c>
       <c r="H294" s="12">
         <f t="shared" si="48"/>
-        <v>29442</v>
+        <v>30814.000000000004</v>
       </c>
       <c r="I294" s="29">
-        <v>46056</v>
+        <v>46083</v>
       </c>
       <c r="J294" s="25">
-        <v>46064</v>
+        <v>46085</v>
       </c>
       <c r="K294" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L294" s="29">
-        <v>46203</v>
+        <v>46285</v>
       </c>
       <c r="M294" s="13">
         <f>VLOOKUP(E294,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N294" s="11">
-        <f t="shared" ref="N294:N295" si="88">M294*H294</f>
-        <v>441.63</v>
-      </c>
-      <c r="O294" s="49">
-        <f t="shared" ref="O294:O295" si="89">0.2*N294</f>
-        <v>88.326000000000008</v>
+        <f t="shared" si="88"/>
+        <v>462.21000000000004</v>
+      </c>
+      <c r="O294" s="40">
+        <f t="shared" si="89"/>
+        <v>92.442000000000007</v>
       </c>
       <c r="P294" s="11">
-        <f t="shared" ref="P294:P295" si="90">0.8*N294</f>
-        <v>353.30400000000003</v>
+        <f t="shared" si="90"/>
+        <v>369.76800000000003</v>
       </c>
     </row>
     <row r="295" spans="1:16" x14ac:dyDescent="0.2">
@@ -17162,32 +17149,32 @@
         <v>14</v>
       </c>
       <c r="B295" s="16">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C295" s="9" t="s">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="D295" s="9" t="s">
-        <v>63</v>
+        <v>112</v>
       </c>
       <c r="E295" s="9" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F295" s="10">
-        <v>3500</v>
+        <v>2520</v>
       </c>
       <c r="G295" s="11">
-        <v>22.01</v>
+        <v>34.01</v>
       </c>
       <c r="H295" s="12">
         <f t="shared" si="48"/>
-        <v>77035</v>
+        <v>85705.2</v>
       </c>
       <c r="I295" s="29">
-        <v>46063</v>
+        <v>46083</v>
       </c>
       <c r="J295" s="25">
-        <v>46072</v>
+        <v>46085</v>
       </c>
       <c r="K295" s="9" t="s">
         <v>18</v>
@@ -17197,25 +17184,27 @@
       </c>
       <c r="M295" s="13">
         <f>VLOOKUP(E295,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N295" s="11">
         <f t="shared" si="88"/>
-        <v>1155.5249999999999</v>
-      </c>
-      <c r="O295" s="49">
+        <v>1714.104</v>
+      </c>
+      <c r="O295" s="40">
         <f t="shared" si="89"/>
-        <v>231.10499999999999</v>
+        <v>342.82080000000002</v>
       </c>
       <c r="P295" s="11">
         <f t="shared" si="90"/>
-        <v>924.42</v>
+        <v>1371.2832000000001</v>
       </c>
     </row>
     <row r="296" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A296" s="9"/>
+      <c r="A296" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="B296" s="16">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C296" s="9" t="s">
         <v>32</v>
@@ -17227,126 +17216,130 @@
         <v>39</v>
       </c>
       <c r="F296" s="10">
-        <v>700</v>
+        <v>1260</v>
       </c>
       <c r="G296" s="11">
-        <v>21.03</v>
+        <v>22.01</v>
       </c>
       <c r="H296" s="12">
         <f t="shared" si="48"/>
-        <v>14721</v>
+        <v>27732.600000000002</v>
       </c>
       <c r="I296" s="29">
-        <v>46078</v>
+        <v>46091</v>
       </c>
       <c r="J296" s="25">
-        <v>46085</v>
+        <v>46119</v>
       </c>
       <c r="K296" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L296" s="29">
-        <v>46203</v>
+        <v>46285</v>
       </c>
       <c r="M296" s="13">
         <f>VLOOKUP(E296,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N296" s="11">
-        <f t="shared" ref="N296:N300" si="91">M296*H296</f>
-        <v>220.815</v>
-      </c>
-      <c r="O296" s="49">
-        <f t="shared" ref="O296:O300" si="92">0.2*N296</f>
-        <v>44.163000000000004</v>
+        <f t="shared" si="88"/>
+        <v>415.98900000000003</v>
+      </c>
+      <c r="O296" s="11">
+        <f t="shared" si="89"/>
+        <v>83.197800000000015</v>
       </c>
       <c r="P296" s="11">
-        <f t="shared" ref="P296:P300" si="93">0.8*N296</f>
-        <v>176.65200000000002</v>
+        <f t="shared" si="90"/>
+        <v>332.79120000000006</v>
       </c>
     </row>
     <row r="297" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A297" s="9"/>
+      <c r="A297" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="B297" s="16">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C297" s="9" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D297" s="9" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E297" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F297" s="10">
-        <v>700</v>
+        <v>2100</v>
       </c>
       <c r="G297" s="11">
-        <v>22.65</v>
+        <v>20.41</v>
       </c>
       <c r="H297" s="12">
         <f t="shared" si="48"/>
-        <v>15854.999999999998</v>
+        <v>42861</v>
       </c>
       <c r="I297" s="29">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="J297" s="25">
-        <v>46085</v>
+        <v>46128</v>
       </c>
       <c r="K297" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L297" s="29">
-        <v>46203</v>
+        <v>46142</v>
       </c>
       <c r="M297" s="13">
         <f>VLOOKUP(E297,tabela_produto[],2,FALSE)</f>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="N297" s="11">
-        <f t="shared" si="91"/>
-        <v>237.82499999999996</v>
-      </c>
-      <c r="O297" s="49">
-        <f t="shared" si="92"/>
-        <v>47.564999999999998</v>
+        <f t="shared" ref="N297:N298" si="91">M297*H297</f>
+        <v>642.91499999999996</v>
+      </c>
+      <c r="O297" s="11">
+        <f t="shared" ref="O297:O298" si="92">0.2*N297</f>
+        <v>128.583</v>
       </c>
       <c r="P297" s="11">
-        <f t="shared" si="93"/>
-        <v>190.26</v>
+        <f t="shared" ref="P297:P298" si="93">0.8*N297</f>
+        <v>514.33199999999999</v>
       </c>
     </row>
     <row r="298" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A298" s="9"/>
+      <c r="A298" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="B298" s="16">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="D298" s="9" t="s">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="E298" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F298" s="10">
-        <v>1400</v>
+        <v>2520</v>
       </c>
       <c r="G298" s="11">
-        <v>22.01</v>
+        <v>34.01</v>
       </c>
       <c r="H298" s="12">
         <f t="shared" si="48"/>
-        <v>30814.000000000004</v>
+        <v>85705.2</v>
       </c>
       <c r="I298" s="29">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="J298" s="25">
-        <v>46085</v>
+        <v>46099</v>
       </c>
       <c r="K298" s="9" t="s">
         <v>18</v>
@@ -17356,50 +17349,52 @@
       </c>
       <c r="M298" s="13">
         <f>VLOOKUP(E298,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N298" s="11">
         <f t="shared" si="91"/>
-        <v>462.21000000000004</v>
-      </c>
-      <c r="O298" s="49">
+        <v>1714.104</v>
+      </c>
+      <c r="O298" s="40">
         <f t="shared" si="92"/>
-        <v>92.442000000000007</v>
+        <v>342.82080000000002</v>
       </c>
       <c r="P298" s="11">
         <f t="shared" si="93"/>
-        <v>369.76800000000003</v>
+        <v>1371.2832000000001</v>
       </c>
     </row>
     <row r="299" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A299" s="9"/>
+      <c r="A299" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="B299" s="16">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D299" s="9" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="E299" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F299" s="10">
-        <v>2520</v>
+        <v>1890</v>
       </c>
       <c r="G299" s="11">
-        <v>34.01</v>
+        <v>36</v>
       </c>
       <c r="H299" s="12">
         <f t="shared" si="48"/>
-        <v>85705.2</v>
+        <v>68040</v>
       </c>
       <c r="I299" s="29">
-        <v>46083</v>
+        <v>46106</v>
       </c>
       <c r="J299" s="25">
-        <v>46085</v>
+        <v>46119</v>
       </c>
       <c r="K299" s="9" t="s">
         <v>18</v>
@@ -17412,22 +17407,24 @@
         <v>0.02</v>
       </c>
       <c r="N299" s="11">
-        <f t="shared" si="91"/>
-        <v>1714.104</v>
-      </c>
-      <c r="O299" s="49">
-        <f t="shared" si="92"/>
-        <v>342.82080000000002</v>
+        <f t="shared" ref="N299" si="94">M299*H299</f>
+        <v>1360.8</v>
+      </c>
+      <c r="O299" s="11">
+        <f t="shared" ref="O299" si="95">0.2*N299</f>
+        <v>272.16000000000003</v>
       </c>
       <c r="P299" s="11">
-        <f t="shared" si="93"/>
-        <v>1371.2832000000001</v>
+        <f t="shared" ref="P299" si="96">0.8*N299</f>
+        <v>1088.6400000000001</v>
       </c>
     </row>
     <row r="300" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A300" s="9"/>
+      <c r="A300" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="B300" s="16">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C300" s="9" t="s">
         <v>32</v>
@@ -17436,309 +17433,136 @@
         <v>33</v>
       </c>
       <c r="E300" s="9" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F300" s="10">
-        <v>1260</v>
+        <v>3150</v>
       </c>
       <c r="G300" s="11">
-        <v>22.01</v>
+        <v>34</v>
       </c>
       <c r="H300" s="12">
         <f t="shared" si="48"/>
-        <v>27732.600000000002</v>
+        <v>107100</v>
       </c>
       <c r="I300" s="29">
-        <v>46091</v>
+        <v>46136</v>
       </c>
       <c r="J300" s="25">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="K300" s="9" t="s">
         <v>18</v>
       </c>
       <c r="L300" s="29">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="M300" s="13">
         <f>VLOOKUP(E300,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="N300" s="11">
-        <f t="shared" si="91"/>
-        <v>415.98900000000003</v>
+        <f t="shared" ref="N300" si="97">M300*H300</f>
+        <v>2142</v>
       </c>
       <c r="O300" s="11">
-        <f t="shared" si="92"/>
-        <v>83.197800000000015</v>
+        <f t="shared" ref="O300" si="98">0.2*N300</f>
+        <v>428.40000000000003</v>
       </c>
       <c r="P300" s="11">
-        <f t="shared" si="93"/>
-        <v>332.79120000000006</v>
+        <f t="shared" ref="P300" si="99">0.8*N300</f>
+        <v>1713.6000000000001</v>
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A301" s="9"/>
-      <c r="B301" s="16">
-        <v>228</v>
-      </c>
-      <c r="C301" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D301" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E301" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="F301" s="10">
-        <v>2100</v>
-      </c>
-      <c r="G301" s="11">
-        <v>20.41</v>
-      </c>
-      <c r="H301" s="12">
-        <f t="shared" si="48"/>
-        <v>42861</v>
-      </c>
-      <c r="I301" s="29">
-        <v>46093</v>
-      </c>
-      <c r="J301" s="25">
-        <v>46128</v>
-      </c>
-      <c r="K301" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L301" s="29">
-        <v>46142</v>
-      </c>
-      <c r="M301" s="13">
-        <f>VLOOKUP(E301,tabela_produto[],2,FALSE)</f>
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N301" s="11">
-        <f t="shared" ref="N301:N302" si="94">M301*H301</f>
-        <v>642.91499999999996</v>
-      </c>
-      <c r="O301" s="11">
-        <f t="shared" ref="O301:O302" si="95">0.2*N301</f>
-        <v>128.583</v>
-      </c>
-      <c r="P301" s="11">
-        <f t="shared" ref="P301:P302" si="96">0.8*N301</f>
-        <v>514.33199999999999</v>
-      </c>
+      <c r="B301" s="16"/>
+      <c r="C301" s="9"/>
+      <c r="D301" s="9"/>
+      <c r="E301" s="9"/>
+      <c r="F301" s="10"/>
+      <c r="G301" s="11"/>
+      <c r="H301" s="12"/>
+      <c r="I301" s="29"/>
+      <c r="J301" s="25"/>
+      <c r="K301" s="9"/>
+      <c r="L301" s="29"/>
+      <c r="M301" s="13"/>
+      <c r="N301" s="11"/>
+      <c r="O301" s="11"/>
+      <c r="P301" s="11"/>
     </row>
     <row r="302" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A302" s="9"/>
-      <c r="B302" s="16">
-        <v>229</v>
-      </c>
-      <c r="C302" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D302" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E302" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F302" s="10">
-        <v>2520</v>
-      </c>
-      <c r="G302" s="11">
-        <v>34.01</v>
-      </c>
-      <c r="H302" s="12">
-        <f t="shared" si="48"/>
-        <v>85705.2</v>
-      </c>
-      <c r="I302" s="29">
-        <v>46093</v>
-      </c>
-      <c r="J302" s="25">
-        <v>46099</v>
-      </c>
-      <c r="K302" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L302" s="29">
-        <v>46285</v>
-      </c>
-      <c r="M302" s="13">
-        <f>VLOOKUP(E302,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
-      </c>
-      <c r="N302" s="11">
-        <f t="shared" si="94"/>
-        <v>1714.104</v>
-      </c>
-      <c r="O302" s="49">
-        <f t="shared" si="95"/>
-        <v>342.82080000000002</v>
-      </c>
-      <c r="P302" s="11">
-        <f t="shared" si="96"/>
-        <v>1371.2832000000001</v>
-      </c>
+      <c r="B302" s="16"/>
+      <c r="C302" s="9"/>
+      <c r="D302" s="9"/>
+      <c r="E302" s="9"/>
+      <c r="F302" s="10"/>
+      <c r="G302" s="11"/>
+      <c r="H302" s="12"/>
+      <c r="I302" s="29"/>
+      <c r="J302" s="25"/>
+      <c r="K302" s="9"/>
+      <c r="L302" s="29"/>
+      <c r="M302" s="13"/>
+      <c r="N302" s="11"/>
+      <c r="O302" s="11"/>
+      <c r="P302" s="11"/>
     </row>
     <row r="303" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A303" s="9"/>
-      <c r="B303" s="16">
-        <v>230</v>
-      </c>
-      <c r="C303" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D303" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E303" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F303" s="10">
-        <v>1890</v>
-      </c>
-      <c r="G303" s="11">
-        <v>36</v>
-      </c>
-      <c r="H303" s="12">
-        <f t="shared" si="48"/>
-        <v>68040</v>
-      </c>
-      <c r="I303" s="29">
-        <v>46106</v>
-      </c>
-      <c r="J303" s="25">
-        <v>46119</v>
-      </c>
-      <c r="K303" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L303" s="29">
-        <v>46285</v>
-      </c>
-      <c r="M303" s="13">
-        <f>VLOOKUP(E303,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
-      </c>
-      <c r="N303" s="11">
-        <f t="shared" ref="N303" si="97">M303*H303</f>
-        <v>1360.8</v>
-      </c>
-      <c r="O303" s="11">
-        <f t="shared" ref="O303" si="98">0.2*N303</f>
-        <v>272.16000000000003</v>
-      </c>
-      <c r="P303" s="11">
-        <f t="shared" ref="P303" si="99">0.8*N303</f>
-        <v>1088.6400000000001</v>
-      </c>
+      <c r="B303" s="16"/>
+      <c r="C303" s="9"/>
+      <c r="D303" s="9"/>
+      <c r="E303" s="9"/>
+      <c r="F303" s="10"/>
+      <c r="G303" s="11"/>
+      <c r="H303" s="12"/>
+      <c r="I303" s="29"/>
+      <c r="J303" s="25"/>
+      <c r="K303" s="9"/>
+      <c r="L303" s="29"/>
+      <c r="M303" s="13"/>
+      <c r="N303" s="11"/>
+      <c r="O303" s="11"/>
+      <c r="P303" s="11"/>
     </row>
     <row r="304" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A304" s="9"/>
-      <c r="B304" s="16">
-        <v>231</v>
-      </c>
-      <c r="C304" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D304" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E304" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F304" s="10">
-        <v>1260</v>
-      </c>
-      <c r="G304" s="11">
-        <v>38</v>
-      </c>
-      <c r="H304" s="12">
-        <f t="shared" si="48"/>
-        <v>47880</v>
-      </c>
-      <c r="I304" s="29">
-        <v>46126</v>
-      </c>
+      <c r="B304" s="16"/>
+      <c r="C304" s="9"/>
+      <c r="D304" s="9"/>
+      <c r="E304" s="9"/>
+      <c r="F304" s="10"/>
+      <c r="G304" s="11"/>
+      <c r="H304" s="12"/>
+      <c r="I304" s="29"/>
       <c r="J304" s="25"/>
-      <c r="K304" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L304" s="29">
-        <v>46285</v>
-      </c>
-      <c r="M304" s="13">
-        <f>VLOOKUP(E304,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
-      </c>
-      <c r="N304" s="11">
-        <f t="shared" ref="N304" si="100">M304*H304</f>
-        <v>957.6</v>
-      </c>
-      <c r="O304" s="11">
-        <f t="shared" ref="O304" si="101">0.2*N304</f>
-        <v>191.52</v>
-      </c>
-      <c r="P304" s="11">
-        <f t="shared" ref="P304" si="102">0.8*N304</f>
-        <v>766.08</v>
-      </c>
+      <c r="K304" s="9"/>
+      <c r="L304" s="29"/>
+      <c r="M304" s="13"/>
+      <c r="N304" s="11"/>
+      <c r="O304" s="11"/>
+      <c r="P304" s="11"/>
     </row>
     <row r="305" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A305" s="9"/>
-      <c r="B305" s="16">
-        <v>232</v>
-      </c>
-      <c r="C305" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D305" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E305" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F305" s="10">
-        <v>3150</v>
-      </c>
-      <c r="G305" s="11">
-        <v>34</v>
-      </c>
-      <c r="H305" s="12">
-        <f t="shared" si="48"/>
-        <v>107100</v>
-      </c>
-      <c r="I305" s="29">
-        <v>46136</v>
-      </c>
-      <c r="J305" s="25">
-        <v>46140</v>
-      </c>
-      <c r="K305" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L305" s="29">
-        <v>46295</v>
-      </c>
-      <c r="M305" s="13">
-        <f>VLOOKUP(E305,tabela_produto[],2,FALSE)</f>
-        <v>0.02</v>
-      </c>
-      <c r="N305" s="11">
-        <f t="shared" ref="N305" si="103">M305*H305</f>
-        <v>2142</v>
-      </c>
-      <c r="O305" s="11">
-        <f t="shared" ref="O305" si="104">0.2*N305</f>
-        <v>428.40000000000003</v>
-      </c>
-      <c r="P305" s="11">
-        <f t="shared" ref="P305" si="105">0.8*N305</f>
-        <v>1713.6000000000001</v>
-      </c>
+      <c r="B305" s="16"/>
+      <c r="C305" s="9"/>
+      <c r="D305" s="9"/>
+      <c r="E305" s="9"/>
+      <c r="F305" s="10"/>
+      <c r="G305" s="11"/>
+      <c r="H305" s="12"/>
+      <c r="I305" s="29"/>
+      <c r="J305" s="25"/>
+      <c r="K305" s="9"/>
+      <c r="L305" s="29"/>
+      <c r="M305" s="13"/>
+      <c r="N305" s="11"/>
+      <c r="O305" s="11"/>
+      <c r="P305" s="11"/>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A306" s="9"/>
@@ -17782,7 +17606,7 @@
       <c r="C308" s="9"/>
       <c r="D308" s="9"/>
       <c r="E308" s="9"/>
-      <c r="F308" s="50"/>
+      <c r="F308" s="10"/>
       <c r="G308" s="11"/>
       <c r="H308" s="12"/>
       <c r="I308" s="29"/>
@@ -17903,131 +17727,41 @@
       <c r="P314" s="11"/>
     </row>
     <row r="315" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A315" s="9"/>
-      <c r="B315" s="16"/>
-      <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
-      <c r="E315" s="9"/>
+      <c r="B315" s="23"/>
       <c r="F315" s="10"/>
-      <c r="G315" s="11"/>
-      <c r="H315" s="12"/>
-      <c r="I315" s="29"/>
-      <c r="J315" s="25"/>
-      <c r="K315" s="9"/>
-      <c r="L315" s="29"/>
-      <c r="M315" s="13"/>
-      <c r="N315" s="11"/>
-      <c r="O315" s="11"/>
-      <c r="P315" s="11"/>
     </row>
     <row r="316" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A316" s="9"/>
-      <c r="B316" s="16"/>
-      <c r="C316" s="9"/>
-      <c r="D316" s="9"/>
-      <c r="E316" s="9"/>
+      <c r="B316" s="23"/>
       <c r="F316" s="10"/>
-      <c r="G316" s="11"/>
-      <c r="H316" s="12"/>
-      <c r="I316" s="29"/>
-      <c r="J316" s="25"/>
-      <c r="K316" s="9"/>
-      <c r="L316" s="29"/>
-      <c r="M316" s="13"/>
-      <c r="N316" s="11"/>
-      <c r="O316" s="11"/>
-      <c r="P316" s="11"/>
     </row>
     <row r="317" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A317" s="9"/>
-      <c r="B317" s="16"/>
-      <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
-      <c r="E317" s="9"/>
+      <c r="B317" s="23"/>
       <c r="F317" s="10"/>
-      <c r="G317" s="11"/>
-      <c r="H317" s="12"/>
-      <c r="I317" s="29"/>
-      <c r="J317" s="25"/>
-      <c r="K317" s="9"/>
-      <c r="L317" s="29"/>
-      <c r="M317" s="13"/>
-      <c r="N317" s="11"/>
-      <c r="O317" s="11"/>
-      <c r="P317" s="11"/>
     </row>
     <row r="318" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A318" s="9"/>
-      <c r="B318" s="16"/>
-      <c r="C318" s="9"/>
-      <c r="D318" s="9"/>
-      <c r="E318" s="9"/>
+      <c r="B318" s="23"/>
       <c r="F318" s="10"/>
-      <c r="G318" s="11"/>
-      <c r="H318" s="12"/>
-      <c r="I318" s="29"/>
-      <c r="J318" s="25"/>
-      <c r="K318" s="9"/>
-      <c r="L318" s="29"/>
-      <c r="M318" s="13"/>
-      <c r="N318" s="11"/>
-      <c r="O318" s="11"/>
-      <c r="P318" s="11"/>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A319" s="9"/>
-      <c r="B319" s="16"/>
-      <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
-      <c r="E319" s="9"/>
-      <c r="F319" s="10"/>
-      <c r="G319" s="11"/>
-      <c r="H319" s="12"/>
-      <c r="I319" s="29"/>
-      <c r="J319" s="25"/>
-      <c r="K319" s="9"/>
-      <c r="L319" s="29"/>
-      <c r="M319" s="13"/>
-      <c r="N319" s="11"/>
-      <c r="O319" s="11"/>
-      <c r="P319" s="11"/>
+      <c r="B319" s="23"/>
     </row>
     <row r="320" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B320" s="23"/>
-      <c r="F320" s="10"/>
-    </row>
-    <row r="321" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="321" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B321" s="23"/>
-      <c r="F321" s="10"/>
-    </row>
-    <row r="322" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B322" s="23"/>
-      <c r="F322" s="10"/>
-    </row>
-    <row r="323" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="323" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B323" s="23"/>
-      <c r="F323" s="10"/>
-    </row>
-    <row r="324" spans="2:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="324" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B324" s="23"/>
     </row>
-    <row r="325" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B325" s="23"/>
-    </row>
-    <row r="326" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B326" s="23"/>
-    </row>
-    <row r="327" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B327" s="23"/>
-    </row>
-    <row r="328" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B328" s="23"/>
-    </row>
-    <row r="329" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B329" s="23"/>
-    </row>
   </sheetData>
-  <autoFilter ref="B1:P305" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B1:P300" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -18038,7 +17772,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A750F49-D618-4646-9E5E-574B531C84BF}">
           <x14:formula1>
             <xm:f>Planilha1!$B$1:$B$9</xm:f>
@@ -18061,80 +17795,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="36" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="2" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="34">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="42">
+      <c r="C3" s="34">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="C4" s="42">
+      <c r="C4" s="34">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="34">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="34">
         <v>0.02</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="34">
         <v>0.02</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="38">
         <v>0.02</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="C9" s="46">
+      <c r="C9" s="38">
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B10" s="45"/>
-      <c r="C10" s="46"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
     </row>
   </sheetData>
   <dataValidations count="1">
